--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wilcoxon" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Global" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_LLVIP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablacion_Fo" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -726,6 +727,18 @@
       <c r="B19" s="6" t="inlineStr">
         <is>
           <t>mAP de YOLOv8n reentrenado por método sobre LLVIP (evaluación orientada a tarea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ablacion_Fo</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Ablación de la función de aptitud: barridos con la Fo del libro FPUNA y comparación de óptimos</t>
         </is>
       </c>
     </row>
@@ -966,6 +979,190 @@
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Lectura: toda fusión supera al visible solo (+0,12 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones, en banda estrecha (0,926–0,949), la propuesta es competitiva (0,936) sin ser líder. La superioridad en calidad de imagen no se traslada automáticamente a la detección (H3 parcial).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ablación de la función de aptitud (pedido de la revisión de avances)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>El barrido 5×5 se repitió con la Fo del libro FPUNA (SSIM_avg + E_n + PSNR_n) y su rango m ∈ [0,3; 2,0], sobre la propuesta y sobre el operador clásico. En negrita el mejor por columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Resultado de los barridos con Fo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>En las 50 corridas (25 configuraciones × 2 operadores) el óptimo fue m* = 0,30, el piso del rango: los términos de fidelidad de Fo dominan a la entropía. Sobre la propuesta Fo eligió además r* = 1 (óptimo trivial); sobre el clásico, r* = 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Curva aptitud vs m (r = 25, sin restricciones): las tres curvas decrecen monótonamente en [0,5; 2,0] — ningún (n, T) puede converger allí — y el máximo real de Fo sobre la propuesta está en m ≈ 0,07, coincidente con el óptimo de F_apt (0,0703). Ver docs/figures/fig_aptitud_vs_m.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Variante (operador + aptitud)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Qabf ↑</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Nabf ↓</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>SSIM ↑</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>SCD ↑</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>VIF ↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Propuesta + F_apt (r=25; m=0,070)</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.368</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico + Fo (r=25; m=0,30)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.395</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Propuesta + Fo (r=1; m=0,30)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico manual (r=5; m=1)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0.334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Lectura: la propuesta con F_apt conserva el mejor perfil de limpieza y estructura (Nabf, SSIM); el óptimo de Fo sobre el clásico es competitivo en bordes y correlación al costo de 4,5× más artefactos; el de Fo sobre la propuesta confirma el óptimo trivial. La aptitud define el perfil del resultado (refuerza H2). Fuente: metrics_reports/fo_ablacion_comparativa.csv y pso_grid_search_fo_*.csv.</t>
         </is>
       </c>
     </row>

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Global" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_LLVIP" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablacion_Fo" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_M3FD" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -739,6 +740,18 @@
       <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Ablación de la función de aptitud: barridos con la Fo del libro FPUNA y comparación de óptimos</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Deteccion_M3FD</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Clases complementarias en M3FD: AP por clase con un detector único VIS+IR (People/IR, Lamp/VIS)</t>
         </is>
       </c>
     </row>
@@ -1163,6 +1176,284 @@
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Lectura: la propuesta con F_apt conserva el mejor perfil de limpieza y estructura (Nabf, SSIM); el óptimo de Fo sobre el clásico es competitivo en bordes y correlación al costo de 4,5× más artefactos; el de Fo sobre la propuesta confirma el óptimo trivial. La aptitud define el perfil del resultado (refuerza H2). Fuente: metrics_reports/fo_ablacion_comparativa.csv y pso_grid_search_fo_*.csv.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clases complementarias en M3FD — un detector único VIS+IR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOv8n entrenado con las imágenes de ambas modalidades mezcladas (4.000 imágenes, 40 épocas) y evaluado por inferencia sobre cada entrada. People domina en IR (térmica); Lamp solo se ve en VIS. En negrita el mejor por columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Entrada del detector</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>AP@0,5 People ↑</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>AP@0,5 Lamp ↑</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Promedio del par ↑</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>mAP@0,5 (6 clases) ↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>VIS (solo)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>IR (solo)</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Ratio Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.231</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0.228</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0.228</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico (r=5; m=1)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>PSO FPUNA (clásico + Fo; r=25; m=0,30)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.229</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Propuesta + Fo (r=1; m=0,30)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Propuesta + F_apt (r=25; m=0,070)</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0.239</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Lectura: complementariedad extrema (IR ciego a Lamp: 0,018; VIS débil en People). Las mejores fusiones superan en el promedio del par a ambas modalidades individuales (RP 0,165 y propuesta 0,162 vs VIS 0,157 e IR 0,119): detectan ambas clases en una sola imagen. La propuesta es la mejor fusión en mAP global (0,239) y en People (0,207), y F_apt supera a Fo en las dos clases clave. Fuente: metrics_reports/detection_m3fd_map.csv.</t>
         </is>
       </c>
     </row>

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>PROPUESTA NOVEDOSA (r=25, m=0,070)</t>
+          <t>Propuesta · F_apt (r=25, m=0,070)</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
@@ -988,8 +988,27 @@
         <v>0.8585</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Propuesta · Fo (r=1, m=0,30)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.9221</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.9344</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.8014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Lectura: toda fusión supera al visible solo (+0,12 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones, en banda estrecha (0,926–0,949), la propuesta es competitiva (0,936) sin ser líder. La superioridad en calidad de imagen no se traslada automáticamente a la detección (H3 parcial).</t>
         </is>

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Barrido de 25 configuraciones PSO (partículas 2-10 × iteraciones 10-50, Cuadro 1 de Ortega &amp; Espinoza 2025) sobre (r, m), r en [1,25]. Óptimo global: r = 25, m ≈ 0,07 (Fo = 1,7654), alcanzado consistentemente con n=10 y T&gt;=30; config operativa m = 0,0703.</t>
+          <t>Barrido de 25 configuraciones PSO (partículas 2-10 × iteraciones 10-50, Cuadro 1 de Ortega &amp; Espinoza 2025) sobre (r, m), r en [1,25]. El peso converge al piso del rango publicado (m* = 0,30) en las 25 configuraciones; el radio se fija en r = 25, que maximiza las nueve métricas de evaluación y activa el banco completo de cinco SE.</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>La propuesta alcanza la mayor SSIM del estudio (0,782), significativa frente a los cinco métodos del estado del arte, y es 2ª en información mutua (MI_ir 0,909); más conservadora en actividad (EN, SD, SF).</t>
+          <t>La propuesta lidera la entropía (6,9888) y el contenido de bordes (1,1045) del estudio y es 2ª en SD, MG y SF, con ventaja significativa sobre los cinco métodos del estado del arte en EN, FE, MG y SF; 2º lugar del ranking agregado (3,67).</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>YOLOv8n reentrenado por método. IR solo lidera (mAP@0,5=0,957); toda fusión supera al VIS solo; propuesta competitiva (0,936) sin liderar. Calidad de imagen ≠ detectabilidad (H3 parcial).</t>
+          <t>YOLOv8n reentrenado por método. IR solo lidera (mAP@0,5=0,957); toda fusión supera al VIS solo (0,808); la propuesta queda en el extremo inferior de la banda de fusiones (0,913): el realce que premian las métricas de actividad no mejora la detección (H3 no sostenida).</t>
         </is>
       </c>
     </row>
@@ -942,26 +942,26 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Propuesta Novedosa (r=25; m=0,070)</t>
+          <t>Propuesta Novedosa (r=25; m=0,30)</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>0.207</v>
+        <v>0.146</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>0.117</v>
+        <v>0.101</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>0.162</v>
+        <v>0.124</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>0.239</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Lectura: complementariedad extrema (IR ciego a Lamp: 0,018; VIS débil en People). Las mejores fusiones superan en el promedio del par a ambas modalidades individuales (RP 0,165 y propuesta 0,162 vs VIS 0,157 e IR 0,119): detectan ambas clases en una sola imagen. La propuesta es la mejor fusión en mAP global (0,239) y en People (0,207), manteniendo las luces cerca del visible. Fuente: metrics_reports/detection_m3fd_map.csv.</t>
+          <t>Lectura: complementariedad extrema (IR ciego a Lamp: 0,018; VIS débil en People). Las mejores fusiones superan en el promedio del par a ambas modalidades individuales: la Ratio Pyramid alcanza 0,165 frente a 0,157 del visible y 0,119 del infrarrojo. Todas las fusiones recuperan ambas clases en una sola imagen —algo que el infrarrojo no logra—, y la propuesta alcanza un promedio intermedio (0,124; People 0,146 y Lamp 0,101): el realce elevado no favorece al detector. Fuente: metrics_reports/detection_m3fd_map.csv.</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>r ∈ [1, 25] (rango del libro FPUNA) · m ∈ [0,05; 1,20] (ajustado al operador con suma)</t>
+          <t>r ∈ [1, 25] · m ∈ [0,30; 2,00] (ambos del libro FPUNA, sin modificaciones)</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>r* = 25 · m ≈ 0,07 (alcanzado por 3 de las 25 configuraciones; consistente con n=10 y T≥30); config operativa m = 0,0703</t>
+          <t>r* = 25 · m* = 0,30 (el peso al que convergen las 25 configuraciones con el rango publicado)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Fo = 1.7654</t>
+          <t>Fo = 1.7354</t>
         </is>
       </c>
     </row>
@@ -1122,14 +1122,14 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>metrics_reports/pso_grid_search_fo_propuesta_oficial.csv</t>
+          <t>metrics_reports/pso_grid_search_fo_propuesta.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Con la suma de ramas se inyecta más energía de detalle que con el máximo; el enjambre lo compensa con un peso de contraste bajo (m 0,070). El radio se ubica en el tope del rango del libro (r = 25): el operador aprovecha un vecindario amplio para capturar los objetivos térmicos completos.</t>
+          <t>Con la suma de ramas se inyecta más energía de detalle que con el máximo; el enjambre lo compensa con el peso del rango publicado (m = 0,30). El radio se ubica en el tope del rango del libro (r = 25): el operador aprovecha un vecindario amplio para capturar los objetivos térmicos completos.</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cada fila es una corrida PSO independiente (semilla propia). En negrita las configuraciones que alcanzan el óptimo global Fo = 1,7654.</t>
+          <t>Cada fila es una corrida PSO independiente (semilla propia). Las 25 configuraciones convergen al mismo peso óptimo, m* = 0,30; las diferencias de aptitud reflejan el radio hallado.</t>
         </is>
       </c>
     </row>
@@ -1218,39 +1218,39 @@
         <v>20</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>1.7622</v>
+        <v>1.6988</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>1.7556</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>8</v>
+      <c r="D6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1267,289 +1267,289 @@
         <v>25</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>48</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="13" t="n">
         <v>80</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>1.7556</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>15</v>
+      <c r="D8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>1.7572</v>
-      </c>
-      <c r="G9" s="11" t="n">
+      <c r="D9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="11" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="C11" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>1.7039</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C15" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>1.7633</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>0.07340000000000001</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>1.7654</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>160</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="11" t="n">
+      <c r="C18" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1.758</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>240</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>657</v>
+      <c r="D19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -1566,36 +1566,36 @@
         <v>25</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>384</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="13" t="n">
         <v>160</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>1.7558</v>
-      </c>
-      <c r="G21" s="11" t="n">
-        <v>85</v>
+      <c r="D21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1612,13 +1612,13 @@
         <v>25</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>731</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23">
@@ -1632,39 +1632,39 @@
         <v>320</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>0.0736</v>
+        <v>0.3</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1.7654</v>
+        <v>1.7354</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>244</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="13" t="n">
         <v>400</v>
       </c>
-      <c r="D24" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>325</v>
+      <c r="D24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="25">
@@ -1681,59 +1681,59 @@
         <v>25</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>248</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="D26" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>232</v>
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>1645</v>
+      <c r="D27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -1750,36 +1750,36 @@
         <v>25</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>1700</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n">
+      <c r="A29" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E29" s="14" t="n">
-        <v>0.0736</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>1.7654</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>1406</v>
+      <c r="E29" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1.7039</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>399</v>
       </c>
     </row>
     <row r="31">
@@ -1828,19 +1828,19 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>1.7622</v>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>1.7556</v>
+        <v>1.6988</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1.7354</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>1.7556</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>1.7572</v>
+        <v>1.7039</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1.7354</v>
       </c>
     </row>
     <row r="34">
@@ -1849,20 +1849,20 @@
           <t>n = 4</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
-        <v>1.7633</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1.7654</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>1.7642</v>
+      <c r="B34" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>1.7039</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1.7354</v>
       </c>
     </row>
     <row r="35">
@@ -1871,20 +1871,20 @@
           <t>n = 6</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>1.758</v>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>1.7642</v>
+      <c r="B35" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>1.7354</v>
       </c>
     </row>
     <row r="36">
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>1.7558</v>
+        <v>1.7039</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>1.7354</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>1.7654</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7354</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>1.7354</v>
       </c>
     </row>
     <row r="37">
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>1.7642</v>
+        <v>1.7039</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1.7354</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>1.7354</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.7642</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>1.7654</v>
+        <v>1.7039</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>1.7039</v>
       </c>
     </row>
     <row r="39">
@@ -2162,7 +2162,7 @@
       <c r="H8" s="16" t="n">
         <v>13.0266</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="17" t="n">
         <v>0.7386</v>
       </c>
       <c r="J8" s="16" t="n">
@@ -2209,13 +2209,13 @@
           <t>Top-Hat clásico</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="16" t="n">
         <v>6.9334</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0.1387</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <v>1.0961</v>
       </c>
       <c r="E10" s="17" t="n">
@@ -2240,35 +2240,35 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>PROPUESTA NOVEDOSA (r=25, m=0,070)</t>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
     </row>
   </sheetData>
@@ -2300,7 +2300,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Propuesta novedosa (r=25, m=0,070) — métricas en cada escena del TNO</t>
+          <t>Propuesta novedosa (r=25, m=0,30) — métricas en cada escena del TNO</t>
         </is>
       </c>
     </row>
@@ -2370,31 +2370,31 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>6.4937</v>
+        <v>6.8649</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1258</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>1.2066</v>
+        <v>1.2756</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0187</v>
+        <v>0.0339</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.987</v>
+        <v>0.5967</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.9734</v>
+        <v>0.9035</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>11.0954</v>
+        <v>19.0093</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>0.7896</v>
+        <v>0.6734</v>
       </c>
       <c r="J5" s="16" t="n">
-        <v>20.304</v>
+        <v>18.9702</v>
       </c>
     </row>
     <row r="6">
@@ -2404,31 +2404,31 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>6.7068</v>
+        <v>7.0457</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0.1124</v>
+        <v>0.1411</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1.1005</v>
+        <v>1.1561</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0185</v>
+        <v>0.0334</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>1.4994</v>
+        <v>1.0796</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.8768</v>
+        <v>0.7899</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>10.4541</v>
+        <v>18.7637</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>0.8344</v>
+        <v>0.71</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>21.4658</v>
+        <v>19.9204</v>
       </c>
     </row>
     <row r="7">
@@ -2438,31 +2438,31 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>6.9673</v>
+        <v>7.2951</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.1404</v>
+        <v>0.1705</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>1.0849</v>
+        <v>1.136</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0219</v>
+        <v>0.0408</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>1.7166</v>
+        <v>1.1978</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.8427</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>11.9938</v>
+        <v>22.1786</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>0.7972</v>
+        <v>0.6657</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>20.3565</v>
+        <v>18.7957</v>
       </c>
     </row>
     <row r="8">
@@ -2472,31 +2472,31 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>6.5521</v>
+        <v>6.9414</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.099</v>
+        <v>0.1329</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1.2009</v>
+        <v>1.2722</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.0319</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>1.1773</v>
+        <v>0.8806</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>1.3163</v>
+        <v>1.1302</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>10.3188</v>
+        <v>18.3285</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.7317</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>24.1854</v>
+        <v>21.2257</v>
       </c>
     </row>
     <row r="9">
@@ -2506,31 +2506,31 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>6.6916</v>
+        <v>6.9306</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.1208</v>
+        <v>0.1388</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1.1201</v>
+        <v>1.1601</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.0165</v>
+        <v>0.0292</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>1.3159</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>1.0846</v>
+        <v>0.8871</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>8.140000000000001</v>
+        <v>14.191</v>
       </c>
       <c r="I9" s="16" t="n">
-        <v>0.8417</v>
+        <v>0.7305</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>20.4192</v>
+        <v>19.4966</v>
       </c>
     </row>
     <row r="10">
@@ -2540,31 +2540,31 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>6.867</v>
+        <v>7.0819</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.1254</v>
+        <v>0.1444</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1.1937</v>
+        <v>1.2311</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.0172</v>
+        <v>0.0303</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>1.4893</v>
+        <v>0.9785</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.9984</v>
+        <v>0.7826</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>7.3766</v>
+        <v>12.8088</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.8138</v>
+        <v>0.7077</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>18.6136</v>
+        <v>17.9869</v>
       </c>
     </row>
     <row r="11">
@@ -2574,31 +2574,31 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>6.6183</v>
+        <v>7.0672</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.1029</v>
+        <v>0.1437</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>0.9558</v>
+        <v>1.0207</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.019</v>
+        <v>0.0338</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.8565</v>
+        <v>0.68</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.4892</v>
       </c>
       <c r="H11" s="16" t="n">
-        <v>8.7936</v>
+        <v>15.6543</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>0.7581</v>
+        <v>0.6664</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>15.8255</v>
+        <v>15.1694</v>
       </c>
     </row>
     <row r="12">
@@ -2608,31 +2608,31 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>5.6756</v>
+        <v>6.356</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>0.0495</v>
+        <v>0.0799</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>0.9043</v>
+        <v>1.0127</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.0174</v>
+        <v>0.0314</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.4545</v>
+        <v>0.4235</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.1551</v>
+        <v>0.142</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>7.2448</v>
+        <v>13.3431</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.6945</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>22.9607</v>
+        <v>21.6535</v>
       </c>
     </row>
     <row r="13">
@@ -2642,31 +2642,31 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>7.1018</v>
+        <v>7.0462</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.2056</v>
+        <v>0.2308</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1.0018</v>
+        <v>0.9939</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.0169</v>
+        <v>0.0254</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>3.5176</v>
+        <v>2.0804</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>3.5176</v>
+        <v>2.0804</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>6.83</v>
+        <v>10.4021</v>
       </c>
       <c r="I13" s="16" t="n">
-        <v>0.9853</v>
+        <v>0.8565</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>35.7347</v>
+        <v>24.0539</v>
       </c>
     </row>
     <row r="14">
@@ -2676,31 +2676,31 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>6.776</v>
+        <v>7.1353</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.1116</v>
+        <v>0.144</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.9444</v>
+        <v>0.9944</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.0362</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.7135</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.6877</v>
+        <v>0.544</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>9.025700000000001</v>
+        <v>16.4501</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>0.721</v>
+        <v>0.6148</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>16.096</v>
+        <v>15.4811</v>
       </c>
     </row>
     <row r="15">
@@ -2710,31 +2710,31 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>5.029</v>
+        <v>5.5101</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.042</v>
+        <v>0.0582</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1.0874</v>
+        <v>1.1915</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.0097</v>
+        <v>0.0184</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>1.1045</v>
+        <v>0.9182</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0.5533</v>
+        <v>0.4138</v>
       </c>
       <c r="H15" s="16" t="n">
-        <v>4.1581</v>
+        <v>7.913</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>18.5378</v>
+        <v>18.3341</v>
       </c>
     </row>
     <row r="16">
@@ -2744,31 +2744,31 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>6.6379</v>
+        <v>6.9289</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.1025</v>
+        <v>0.1294</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.9606</v>
+        <v>1.0027</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0169</v>
+        <v>0.0313</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>1.2305</v>
+        <v>0.7833</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.4095</v>
+        <v>0.2797</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>8.3872</v>
+        <v>14.595</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>0.7678</v>
+        <v>0.6532</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>16.9557</v>
+        <v>16.3503</v>
       </c>
     </row>
     <row r="17">
@@ -2778,31 +2778,31 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>6.9455</v>
+        <v>7.4009</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.1192</v>
+        <v>0.1717</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.9685</v>
+        <v>1.0321</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0246</v>
+        <v>0.0439</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.9045</v>
+        <v>0.7228</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.4986</v>
+        <v>0.2983</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>10.6961</v>
+        <v>18.9232</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>0.7095</v>
+        <v>0.615</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>15.4781</v>
+        <v>14.5655</v>
       </c>
     </row>
     <row r="18">
@@ -2812,31 +2812,31 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>7.0411</v>
+        <v>7.4075</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.1428</v>
+        <v>0.1754</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1.0357</v>
+        <v>1.0896</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0.0216</v>
+        <v>0.0393</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>1.2918</v>
+        <v>1.0198</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.5607</v>
+        <v>0.3148</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>9.7651</v>
+        <v>17.1852</v>
       </c>
       <c r="I18" s="16" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5835</v>
       </c>
       <c r="J18" s="16" t="n">
-        <v>13.6234</v>
+        <v>13.1802</v>
       </c>
     </row>
     <row r="19">
@@ -2846,31 +2846,31 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>6.9851</v>
+        <v>7.2242</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.1361</v>
+        <v>0.1572</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1.1246</v>
+        <v>1.163</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.0181</v>
+        <v>0.0319</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>1.3098</v>
+        <v>1.0326</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>0.8349</v>
+        <v>0.4759</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>9.116899999999999</v>
+        <v>15.2839</v>
       </c>
       <c r="I19" s="16" t="n">
-        <v>0.7017</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="J19" s="16" t="n">
-        <v>11.2448</v>
+        <v>11.1201</v>
       </c>
     </row>
     <row r="20">
@@ -2880,31 +2880,31 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>6.9654</v>
+        <v>7.3131</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>0.1235</v>
+        <v>0.1569</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>0.9956</v>
+        <v>1.0453</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.025</v>
+        <v>0.0467</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>1.2616</v>
+        <v>1.02</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>0.2823</v>
+        <v>0.2179</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>11.7115</v>
+        <v>21.5253</v>
       </c>
       <c r="I20" s="16" t="n">
-        <v>0.7005</v>
+        <v>0.5846</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>13.9113</v>
+        <v>13.553</v>
       </c>
     </row>
     <row r="21">
@@ -2914,31 +2914,31 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>6.658</v>
+        <v>6.9904</v>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.1035</v>
+        <v>0.1321</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>0.9709</v>
+        <v>1.0194</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.0192</v>
+        <v>0.0366</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>1.4608</v>
+        <v>1.0234</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0.5506</v>
+        <v>0.3795</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>9.936299999999999</v>
+        <v>18.107</v>
       </c>
       <c r="I21" s="16" t="n">
-        <v>0.7766</v>
+        <v>0.6431</v>
       </c>
       <c r="J21" s="16" t="n">
-        <v>16.7663</v>
+        <v>16.1917</v>
       </c>
     </row>
     <row r="22">
@@ -2948,31 +2948,31 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>6.4444</v>
+        <v>6.8685</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.0877</v>
+        <v>0.1211</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.9758</v>
+        <v>1.04</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0.0219</v>
+        <v>0.0438</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>1.6023</v>
+        <v>1.0178</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.2563</v>
+        <v>0.1924</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>10.8526</v>
+        <v>20.8475</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>19.536</v>
+        <v>18.4304</v>
       </c>
     </row>
     <row r="23">
@@ -2982,31 +2982,31 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>6.6343</v>
+        <v>6.9754</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.1948</v>
+        <v>0.2236</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1.1136</v>
+        <v>1.1708</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0162</v>
+        <v>0.0297</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1.1084</v>
+        <v>0.8874</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>1.6359</v>
+        <v>1.3119</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>10.3602</v>
+        <v>18.8666</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.7901</v>
+        <v>0.6853</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>15.7758</v>
+        <v>15.0098</v>
       </c>
     </row>
     <row r="24">
@@ -3016,31 +3016,31 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>7.0215</v>
+        <v>7.3926</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.131</v>
+        <v>0.1771</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>1.0279</v>
+        <v>1.0823</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0304</v>
+        <v>0.0585</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>1.5795</v>
+        <v>1.251</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>1.3104</v>
+        <v>0.9398</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>16.626</v>
+        <v>32.4941</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.6985</v>
+        <v>0.5682</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>16.8363</v>
+        <v>15.604</v>
       </c>
     </row>
     <row r="25">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>85.95999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>2.084367806121161e-16</v>
+        <v>1.851250734915931e-15</v>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>98.92</v>
+        <v>101.74</v>
       </c>
       <c r="C6" s="20" t="n">
-        <v>4.207960080687093e-19</v>
+        <v>1.088386607957448e-19</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>85.95999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="C7" s="20" t="n">
-        <v>2.084367806121161e-16</v>
+        <v>1.851250734915931e-15</v>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>94.97</v>
+        <v>101.19</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>2.798657155265822e-18</v>
+        <v>1.414652483800934e-19</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>75.83</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C9" s="20" t="n">
-        <v>2.592007939920261e-14</v>
+        <v>1.706123971832938e-13</v>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="B10" s="19" t="n">
-        <v>62.39</v>
+        <v>59.98</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>1.471433343483753e-11</v>
+        <v>4.546523434404776e-11</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>90.16</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="C11" s="20" t="n">
-        <v>2.803851732782458e-17</v>
+        <v>1.465042903035624e-18</v>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>96.52</v>
+        <v>99.58</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>1.332523872758985e-18</v>
+        <v>3.072490463062902e-19</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="B13" s="19" t="n">
-        <v>107.47</v>
+        <v>107.32</v>
       </c>
       <c r="C13" s="20" t="n">
-        <v>6.898817513071916e-21</v>
+        <v>7.42059728052933e-21</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -3459,19 +3459,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>6.6645</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>0.009435653686523399</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>0.0189</v>
+        <v>0</v>
       </c>
       <c r="I5" s="21" t="n">
-        <v>-0.65</v>
+        <v>0.99</v>
       </c>
       <c r="J5" s="15">
         <f>IF(H5&gt;=0.05,"≈",IF((E5-F5)*D5&gt;0,"mejor","peor"))</f>
@@ -3498,19 +3498,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>1.0529</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>0.0083084106445312</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>0.0166</v>
+        <v>0</v>
       </c>
       <c r="I6" s="21" t="n">
-        <v>-0.66</v>
+        <v>0.99</v>
       </c>
       <c r="J6" s="15">
         <f>IF(H6&gt;=0.05,"≈",IF((E6-F6)*D6&gt;0,"mejor","peor"))</f>
@@ -3537,19 +3537,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>0.0256</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J7" s="15">
         <f>IF(H7&gt;=0.05,"≈",IF((E7-F7)*D7&gt;0,"mejor","peor"))</f>
@@ -3576,19 +3576,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>0.8843</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>2.6702880859375e-05</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>0.0035</v>
+        <v>0.0002</v>
       </c>
       <c r="I8" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J8" s="15">
         <f>IF(H8&gt;=0.05,"≈",IF((E8-F8)*D8&gt;0,"mejor","peor"))</f>
@@ -3615,19 +3615,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>1.3038</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>5.7220458984375e-06</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.98</v>
       </c>
       <c r="J9" s="15">
         <f>IF(H9&gt;=0.05,"≈",IF((E9-F9)*D9&gt;0,"mejor","peor"))</f>
@@ -3654,19 +3654,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>22.8375</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J10" s="15">
         <f>IF(H10&gt;=0.05,"≈",IF((E10-F10)*D10&gt;0,"mejor","peor"))</f>
@@ -3693,19 +3693,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>0.1167</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.388376235961914</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>0.3884</v>
+        <v>0</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="J11" s="15">
         <f>IF(H11&gt;=0.05,"≈",IF((E11-F11)*D11&gt;0,"mejor","peor"))</f>
@@ -3732,19 +3732,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>13.151</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H12" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J12" s="15">
         <f>IF(H12&gt;=0.05,"≈",IF((E12-F12)*D12&gt;0,"mejor","peor"))</f>
@@ -3771,19 +3771,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>0.7305</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>0.99</v>
+        <v>-1</v>
       </c>
       <c r="J13" s="15">
         <f>IF(H13&gt;=0.05,"≈",IF((E13-F13)*D13&gt;0,"mejor","peor"))</f>
@@ -3810,19 +3810,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>6.706</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H14" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>-0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J14" s="15">
         <f>IF(H14&gt;=0.05,"≈",IF((E14-F14)*D14&gt;0,"mejor","peor"))</f>
@@ -3849,19 +3849,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1.0596</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>-0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J15" s="15">
         <f>IF(H15&gt;=0.05,"≈",IF((E15-F15)*D15&gt;0,"mejor","peor"))</f>
@@ -3888,19 +3888,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>0.0251</v>
       </c>
       <c r="G16" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H16" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J16" s="15">
         <f>IF(H16&gt;=0.05,"≈",IF((E16-F16)*D16&gt;0,"mejor","peor"))</f>
@@ -3927,19 +3927,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0.8908</v>
       </c>
       <c r="G17" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.33514404296875e-05</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>0.0035</v>
+        <v>0.0001</v>
       </c>
       <c r="I17" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="J17" s="15">
         <f>IF(H17&gt;=0.05,"≈",IF((E17-F17)*D17&gt;0,"mejor","peor"))</f>
@@ -3966,19 +3966,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1.2887</v>
       </c>
       <c r="G18" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="J18" s="15">
         <f>IF(H18&gt;=0.05,"≈",IF((E18-F18)*D18&gt;0,"mejor","peor"))</f>
@@ -4005,19 +4005,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22.7857</v>
       </c>
       <c r="G19" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J19" s="15">
         <f>IF(H19&gt;=0.05,"≈",IF((E19-F19)*D19&gt;0,"mejor","peor"))</f>
@@ -4044,19 +4044,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0.1205</v>
       </c>
       <c r="G20" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="J20" s="15">
         <f>IF(H20&gt;=0.05,"≈",IF((E20-F20)*D20&gt;0,"mejor","peor"))</f>
@@ -4083,19 +4083,19 @@
         <v>1</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13.0266</v>
       </c>
       <c r="G21" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H21" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J21" s="15">
         <f>IF(H21&gt;=0.05,"≈",IF((E21-F21)*D21&gt;0,"mejor","peor"))</f>
@@ -4122,19 +4122,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0.7386</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H22" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>0.99</v>
+        <v>-1</v>
       </c>
       <c r="J22" s="15">
         <f>IF(H22&gt;=0.05,"≈",IF((E22-F22)*D22&gt;0,"mejor","peor"))</f>
@@ -4161,19 +4161,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>6.7002</v>
       </c>
       <c r="G23" s="20" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H23" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>-0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J23" s="15">
         <f>IF(H23&gt;=0.05,"≈",IF((E23-F23)*D23&gt;0,"mejor","peor"))</f>
@@ -4200,19 +4200,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1.0586</v>
       </c>
       <c r="G24" s="20" t="n">
-        <v>5.7220458984375e-06</v>
+        <v>3.814697265625e-06</v>
       </c>
       <c r="H24" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>-0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J24" s="15">
         <f>IF(H24&gt;=0.05,"≈",IF((E24-F24)*D24&gt;0,"mejor","peor"))</f>
@@ -4239,19 +4239,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0.027</v>
       </c>
       <c r="G25" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H25" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J25" s="15">
         <f>IF(H25&gt;=0.05,"≈",IF((E25-F25)*D25&gt;0,"mejor","peor"))</f>
@@ -4278,19 +4278,19 @@
         <v>1</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0.8809</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>0.0001678466796875</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>0.0035</v>
+        <v>0.0005</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.88</v>
       </c>
       <c r="J26" s="15">
         <f>IF(H26&gt;=0.05,"≈",IF((E26-F26)*D26&gt;0,"mejor","peor"))</f>
@@ -4317,19 +4317,19 @@
         <v>1</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1.2846</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>5.7220458984375e-06</v>
       </c>
       <c r="H27" s="20" t="n">
-        <v>0.0028</v>
+        <v>0</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.98</v>
       </c>
       <c r="J27" s="15">
         <f>IF(H27&gt;=0.05,"≈",IF((E27-F27)*D27&gt;0,"mejor","peor"))</f>
@@ -4356,19 +4356,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>22.7767</v>
       </c>
       <c r="G28" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H28" s="20" t="n">
-        <v>0.0042</v>
+        <v>0</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="J28" s="15">
         <f>IF(H28&gt;=0.05,"≈",IF((E28-F28)*D28&gt;0,"mejor","peor"))</f>
@@ -4395,19 +4395,19 @@
         <v>1</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0.1199</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H29" s="20" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="J29" s="15">
         <f>IF(H29&gt;=0.05,"≈",IF((E29-F29)*D29&gt;0,"mejor","peor"))</f>
@@ -4434,19 +4434,19 @@
         <v>1</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>13.9341</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <f>IF(H30&gt;=0.05,"≈",IF((E30-F30)*D30&gt;0,"mejor","peor"))</f>
@@ -4473,19 +4473,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>0.7163</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>0.99</v>
+        <v>-1</v>
       </c>
       <c r="J31" s="15">
         <f>IF(H31&gt;=0.05,"≈",IF((E31-F31)*D31&gt;0,"mejor","peor"))</f>
@@ -4512,19 +4512,19 @@
         <v>1</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>6.835</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>0.0012092590332031</v>
+        <v>0.0072956085205078</v>
       </c>
       <c r="H32" s="20" t="n">
-        <v>0.0036</v>
+        <v>0.0146</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>-0.78</v>
+        <v>0.67</v>
       </c>
       <c r="J32" s="15">
         <f>IF(H32&gt;=0.05,"≈",IF((E32-F32)*D32&gt;0,"mejor","peor"))</f>
@@ -4551,19 +4551,19 @@
         <v>1</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>1.0792</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0.0014324188232421</v>
+        <v>0.0072956085205078</v>
       </c>
       <c r="H33" s="20" t="n">
-        <v>0.0043</v>
+        <v>0.0146</v>
       </c>
       <c r="I33" s="21" t="n">
-        <v>-0.77</v>
+        <v>0.67</v>
       </c>
       <c r="J33" s="15">
         <f>IF(H33&gt;=0.05,"≈",IF((E33-F33)*D33&gt;0,"mejor","peor"))</f>
@@ -4590,19 +4590,19 @@
         <v>1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0.0248</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J34" s="15">
         <f>IF(H34&gt;=0.05,"≈",IF((E34-F34)*D34&gt;0,"mejor","peor"))</f>
@@ -4629,19 +4629,19 @@
         <v>1</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1.0717</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0.0531692504882812</v>
+        <v>0.0003223419189453</v>
       </c>
       <c r="H35" s="20" t="n">
-        <v>0.1063</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I35" s="21" t="n">
-        <v>-0.49</v>
+        <v>-0.85</v>
       </c>
       <c r="J35" s="15">
         <f>IF(H35&gt;=0.05,"≈",IF((E35-F35)*D35&gt;0,"mejor","peor"))</f>
@@ -4668,19 +4668,19 @@
         <v>1</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>2.1183</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0.0003223419189453</v>
+        <v>2.6702880859375e-05</v>
       </c>
       <c r="H36" s="20" t="n">
-        <v>0.0019</v>
+        <v>0.0001</v>
       </c>
       <c r="I36" s="21" t="n">
-        <v>-0.85</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J36" s="15">
         <f>IF(H36&gt;=0.05,"≈",IF((E36-F36)*D36&gt;0,"mejor","peor"))</f>
@@ -4707,19 +4707,19 @@
         <v>1</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>20.2687</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>0.0008506774902343</v>
       </c>
       <c r="H37" s="20" t="n">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="I37" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J37" s="15">
         <f>IF(H37&gt;=0.05,"≈",IF((E37-F37)*D37&gt;0,"mejor","peor"))</f>
@@ -4746,19 +4746,19 @@
         <v>1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0.1548</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>1.33514404296875e-05</v>
+        <v>0.4980087280273437</v>
       </c>
       <c r="H38" s="20" t="n">
-        <v>0.0001</v>
+        <v>0.498</v>
       </c>
       <c r="I38" s="21" t="n">
-        <v>-0.96</v>
+        <v>-0.18</v>
       </c>
       <c r="J38" s="15">
         <f>IF(H38&gt;=0.05,"≈",IF((E38-F38)*D38&gt;0,"mejor","peor"))</f>
@@ -4785,19 +4785,19 @@
         <v>1</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>13.04</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J39" s="15">
         <f>IF(H39&gt;=0.05,"≈",IF((E39-F39)*D39&gt;0,"mejor","peor"))</f>
@@ -4824,19 +4824,19 @@
         <v>1</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0.7208</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="21" t="n">
-        <v>0.99</v>
+        <v>-1</v>
       </c>
       <c r="J40" s="15">
         <f>IF(H40&gt;=0.05,"≈",IF((E40-F40)*D40&gt;0,"mejor","peor"))</f>
@@ -4863,19 +4863,19 @@
         <v>1</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>6.6406</v>
+        <v>6.9888</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>6.8285</v>
       </c>
       <c r="G41" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>2.6702880859375e-05</v>
       </c>
       <c r="H41" s="20" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I41" s="21" t="n">
-        <v>-0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J41" s="15">
         <f>IF(H41&gt;=0.05,"≈",IF((E41-F41)*D41&gt;0,"mejor","peor"))</f>
@@ -4902,19 +4902,19 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>1.0487</v>
+        <v>1.1045</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>1.079</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>2.6702880859375e-05</v>
       </c>
       <c r="H42" s="20" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I42" s="21" t="n">
-        <v>-0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J42" s="15">
         <f>IF(H42&gt;=0.05,"≈",IF((E42-F42)*D42&gt;0,"mejor","peor"))</f>
@@ -4941,19 +4941,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.0194</v>
+        <v>0.0353</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0.0269</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H43" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J43" s="15">
         <f>IF(H43&gt;=0.05,"≈",IF((E43-F43)*D43&gt;0,"mejor","peor"))</f>
@@ -4980,19 +4980,19 @@
         <v>1</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6708</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>0.8807</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>0.1536464691162109</v>
+        <v>0.0239505767822265</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>0.1536</v>
+        <v>0.024</v>
       </c>
       <c r="I44" s="21" t="n">
-        <v>0.37</v>
+        <v>-0.57</v>
       </c>
       <c r="J44" s="15">
         <f>IF(H44&gt;=0.05,"≈",IF((E44-F44)*D44&gt;0,"mejor","peor"))</f>
@@ -5019,19 +5019,19 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>1.3422</v>
+        <v>0.9617</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>1.1698</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>0.0758514404296875</v>
       </c>
       <c r="H45" s="20" t="n">
-        <v>0.0028</v>
+        <v>0.0759</v>
       </c>
       <c r="I45" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="J45" s="15">
         <f>IF(H45&gt;=0.05,"≈",IF((E45-F45)*D45&gt;0,"mejor","peor"))</f>
@@ -5058,19 +5058,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>18.7313</v>
+        <v>17.2546</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>21.9655</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.0007076263427734</v>
+        <v>0.0001678466796875</v>
       </c>
       <c r="H46" s="20" t="n">
-        <v>0.0042</v>
+        <v>0.0007</v>
       </c>
       <c r="I46" s="21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.88</v>
       </c>
       <c r="J46" s="15">
         <f>IF(H46&gt;=0.05,"≈",IF((E46-F46)*D46&gt;0,"mejor","peor"))</f>
@@ -5097,19 +5097,19 @@
         <v>1</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1477</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>0.1304</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>2.6702880859375e-05</v>
+        <v>1.9073486328125e-05</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="I47" s="21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="J47" s="15">
         <f>IF(H47&gt;=0.05,"≈",IF((E47-F47)*D47&gt;0,"mejor","peor"))</f>
@@ -5136,19 +5136,19 @@
         <v>1</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>9.6441</v>
+        <v>17.3435</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>13.3376</v>
       </c>
       <c r="G48" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>1.9073486328125e-06</v>
       </c>
       <c r="H48" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="21" t="n">
-        <v>-0.99</v>
+        <v>1</v>
       </c>
       <c r="J48" s="15">
         <f>IF(H48&gt;=0.05,"≈",IF((E48-F48)*D48&gt;0,"mejor","peor"))</f>
@@ -5175,19 +5175,19 @@
         <v>1</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>0.7822</v>
+        <v>0.6677</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>0.7212</v>
       </c>
       <c r="G49" s="20" t="n">
-        <v>3.814697265625e-06</v>
+        <v>6.29425048828125e-05</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>0.99</v>
+        <v>-0.91</v>
       </c>
       <c r="J49" s="15">
         <f>IF(H49&gt;=0.05,"≈",IF((E49-F49)*D49&gt;0,"mejor","peor"))</f>
@@ -6393,7 +6393,7 @@
         <v>3.62396240234375e-05</v>
       </c>
       <c r="H80" s="20" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="I80" s="21" t="n">
         <v>-0.93</v>
@@ -6471,7 +6471,7 @@
         <v>0.0007076263427734</v>
       </c>
       <c r="H82" s="20" t="n">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="I82" s="21" t="n">
         <v>0.8100000000000001</v>
@@ -6627,7 +6627,7 @@
         <v>0.0008506774902343</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>0.0034</v>
+        <v>0.0026</v>
       </c>
       <c r="I86" s="21" t="n">
         <v>0.8</v>
@@ -6666,7 +6666,7 @@
         <v>0.0005855560302734</v>
       </c>
       <c r="H87" s="20" t="n">
-        <v>0.0023</v>
+        <v>0.0018</v>
       </c>
       <c r="I87" s="21" t="n">
         <v>0.82</v>
@@ -6744,7 +6744,7 @@
         <v>4.76837158203125e-05</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="I89" s="21" t="n">
         <v>-0.92</v>
@@ -6783,7 +6783,7 @@
         <v>0.0004825592041015</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>0.0024</v>
+        <v>0.001</v>
       </c>
       <c r="I90" s="21" t="n">
         <v>-0.83</v>
@@ -6822,7 +6822,7 @@
         <v>0.0003223419189453</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>0.0023</v>
+        <v>0.001</v>
       </c>
       <c r="I91" s="21" t="n">
         <v>-0.85</v>
@@ -6986,7 +6986,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rango 1 = mejor en esa métrica. La columna final promedia los nueve rangos con fórmula. La propuesta es 1ª en SSIM y 2ª en información mutua; las métricas de actividad (EN, SD, FE, MG, SF), que premian el realce agresivo (lideradas por el Top-Hat clásico), bajan su promedio global (7ª).</t>
+          <t>Rango 1 = mejor en esa métrica. La columna final promedia los nueve rangos con fórmula. La propuesta es 1ª en EN y FE y 2ª en SD, MG y SF; cede en las métricas de fidelidad a las fuentes (SSIM, PSNR) y en información mutua, lideradas por los métodos multiescala. Queda 2ª en el ranking global (3,67), tras la pirámide de Laplace (3,44).</t>
         </is>
       </c>
     </row>
@@ -7054,28 +7054,28 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>5</v>
-      </c>
       <c r="I5" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="19" t="n">
         <v>5</v>
@@ -7086,37 +7086,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="19" t="n">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="G6" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>2</v>
+      <c r="I6" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>7</v>
       </c>
       <c r="K6" s="22">
         <f>AVERAGE(B6:J6)</f>
@@ -7126,35 +7126,35 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Top-Hat clásico</t>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="19" t="n">
+      <c r="H7" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" s="19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K7" s="22">
         <f>AVERAGE(B7:J7)</f>
@@ -7164,35 +7164,35 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Ratio of low-pass Pyramid (RP)</t>
+          <t>Top-Hat clásico</t>
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="19" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="19" t="n">
         <v>6</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>4</v>
       </c>
       <c r="K8" s="22">
         <f>AVERAGE(B8:J8)</f>
@@ -7202,26 +7202,26 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Ratio of low-pass Pyramid (RP)</t>
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>4</v>
@@ -7230,7 +7230,7 @@
         <v>3</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9" s="22">
         <f>AVERAGE(B9:J9)</f>
@@ -7240,35 +7240,35 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Wavelet discreta (DWT)</t>
+          <t>Curvelet (CVT)</t>
         </is>
       </c>
       <c r="B10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="F10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="19" t="n">
+      <c r="I10" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>6</v>
-      </c>
       <c r="J10" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" s="22">
         <f>AVERAGE(B10:J10)</f>
@@ -7276,37 +7276,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>PROPUESTA NOVEDOSA (r=25, m=0,070)</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="23" t="n">
+      <c r="C11" s="19" t="n">
         <v>6</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="K11" s="22">
         <f>AVERAGE(B11:J11)</f>
@@ -7530,26 +7530,26 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Propuesta Novedosa (r=25, m=0,070)</t>
+          <t>Propuesta Novedosa (r=25, m=0,30)</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9129</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>0.6085</v>
+        <v>0.6165</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>0.9364</v>
+        <v>0.9101</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>0.8585</v>
+        <v>0.8058</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Lectura: toda fusión supera al visible solo (+0,12 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones, en banda estrecha (0,926–0,949), la propuesta es competitiva (0,936) sin ser líder. La superioridad en calidad de imagen no se traslada automáticamente a la detección (H3 parcial).</t>
+          <t>Lectura: toda fusión supera al visible solo (+0,11 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones (banda 0,913–0,949) la propuesta queda en el extremo inferior (0,913). El realce que premian las métricas de actividad no mejora la detección: ambos criterios deben reportarse por separado (H3 no sostenida).</t>
         </is>
       </c>
     </row>

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -11,25 +11,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSO_Configuracion" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSO_Barrido" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propuesta_por_Imagen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Friedman" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wilcoxon" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Global" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_LLVIP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_M3FD" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark_por_Escena" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propuesta_por_Imagen" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Friedman" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wilcoxon" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Global" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_LLVIP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_M3FD" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Benchmark_por_Escena'!$A$4:$K$144</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0E+00"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0E+00"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,13 +150,19 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,7 +171,7 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -529,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -656,70 +666,82 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Propuesta_por_Imagen</t>
+          <t>Benchmark_por_Escena</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Métricas de la propuesta en cada escena, con promedio y desvío por fórmula</t>
+          <t>Los 7 métodos en cada una de las 20 escenas (140 filas, con filtro y mejor por escena)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Friedman</t>
+          <t>Propuesta_por_Imagen</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Test global por métrica (7 métodos × 20 imágenes)</t>
+          <t>Métricas de la propuesta en cada escena, con promedio y desvío por fórmula</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Wilcoxon</t>
+          <t>Friedman</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>90 contrastes pareados (propuesta y Top-Hat clásico vs. los 5 del estado del arte)</t>
+          <t>Test global por métrica (7 métodos × 20 imágenes)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Ranking_Global</t>
+          <t>Wilcoxon</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Ranking promedio de los 7 métodos (nueve métricas)</t>
+          <t>90 contrastes pareados (propuesta y Top-Hat clásico vs. los 5 del estado del arte)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Deteccion_LLVIP</t>
+          <t>Ranking_Global</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>mAP de YOLOv8n reentrenado por método sobre LLVIP (evaluación orientada a tarea)</t>
+          <t>Ranking promedio de los 7 métodos (nueve métricas)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Deteccion_LLVIP</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>mAP de YOLOv8n reentrenado por método sobre LLVIP (evaluación orientada a tarea)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Deteccion_M3FD</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Clases complementarias en M3FD: AP por clase con un detector único VIS+IR (People/IR, Lamp/VIS)</t>
         </is>
@@ -731,6 +753,246 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evaluación orientada a tarea — detección de peatones en LLVIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOv8n reentrenado 40 épocas por método (subconjunto 2.000 train / 500 val, misma config y semilla). Etiquetas idénticas para todos: la diferencia de mAP aísla el efecto del método de fusión. En negrita el mejor por columna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Entrada del detector</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>mAP@0,5 ↑</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>mAP@0,5:0,95 ↑</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Precisión ↑</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Recall ↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>VIS (solo)</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>0.8033</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.7506</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>IR (solo)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.6627</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.8935999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>0.9487</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>0.6509</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.8788</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.9261</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.9404</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.9457</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.8532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>0.9479</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>0.9492</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.8577</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0.6388</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.8683</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0.9571</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.8662</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Propuesta Novedosa (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0.8058</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Lectura: toda fusión supera al visible solo (+0,11 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones (banda 0,913–0,949) la propuesta queda en el extremo inferior (0,913). El realce que premian las métricas de actividad no mejora la detección: ambos criterios deben reportarse por separado (H3 no sostenida).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2282,6 +2544,5092 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Benchmark escena por escena — los 7 métodos en cada uno de los 20 pares del TNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>En negrita el mejor valor de cada métrica dentro de cada escena. Todas las métricas son de tipo «mayor es mejor». Equivale a las Tablas 2a-2e del informe de avances, ampliado a las nueve métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Escena</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Método</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>MI_vis</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>MI_ir</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>SSIM</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>PSNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>APC_1_view_1_fk_06_005</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>6.59626</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>0.10543</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>1.22565</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>1.37062</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>1.10413</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>13.8419</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.72157</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>17.56691</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>6.70787</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0.1081</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>1.24639</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.02428</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.67064</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>1.00893</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>14.84247</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.74546</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>19.84633</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>6.55114</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>0.09805999999999999</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>1.21727</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.02617</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.84788</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.83345</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>15.28485</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.71926</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>20.06718</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>6.55078</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0.09895</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1.2172</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.02431</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.78471</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.90194</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>14.4637</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.7418400000000001</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>20.07229</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>6.52192</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0.09655</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1.21184</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.02503</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>0.83724</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>14.82389</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0.73227</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>20.11699</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>6.82114</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0.11995</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1.26743</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.04392</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0.64523</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>22.94585</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.58547</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>19.008</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>6.86487</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0.12581</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1.27556</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.59674</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>0.90354</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>19.00929</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>18.97018</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>APC_1_view_2_fk_ref_01_005</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>7.01095</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0.13824</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1.15038</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>2.31993</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0.99316</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>13.73683</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>0.7792</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>18.63797</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>6.82976</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>1.12065</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>1.26457</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0.91343</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>12.52108</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.80108</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>21.16004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>6.74217</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0.11312</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>1.10628</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.02465</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1.4218</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>14.25939</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0.77195</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>21.22357</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>6.74577</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0.11364</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1.10687</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>1.42365</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>0.8287600000000001</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>13.75424</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0.79389</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>21.23519</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>6.71961</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0.11169</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1.10258</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0.02365</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1.47255</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>0.80554</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>13.85716</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0.78609</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>21.28882</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>6.94596</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1.13972</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>0.04427</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>1.02886</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>0.69416</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>23.16733</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>0.61722</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>19.97434</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>7.04566</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0.14113</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>1.15608</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.03342</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>1.07965</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>0.78986</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>18.7637</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>0.70999</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>19.92037</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>APC_1_view_3_fk_ref_02_005</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>7.27903</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1.13346</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>0.02808</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>2.40099</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>1.25369</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>16.01441</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>0.73543</v>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>17.50153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>7.07216</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>0.14605</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1.10125</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>1.42345</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>0.95009</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>14.82921</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>0.75941</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>20.07295</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>7.03835</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1.09598</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>1.59952</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>0.9140200000000001</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>16.61699</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>0.73138</v>
+      </c>
+      <c r="K21" s="18" t="n">
+        <v>20.10736</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>7.02866</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>1.09447</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0.02802</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>1.59723</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>0.9438800000000001</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>16.05787</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>0.75263</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>20.1217</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>7.02044</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>0.14016</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1.09319</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>0.02846</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>1.65709</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>0.91967</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>16.16145</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>20.16434</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>7.22029</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>0.16178</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1.12431</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.05453</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>1.11745</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0.78359</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>28.33557</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0.57646</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>18.7199</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>7.29509</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0.17055</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>1.13596</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>1.19779</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>22.17859</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>0.6657</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <v>18.79566</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>APC_3_view_1_fk_bar_06_005</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>6.66512</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>0.10586</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1.22157</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>1.39576</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>1.49268</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>13.47605</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>0.80171</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>21.61575</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>6.67722</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>0.10636</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1.22379</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1.32316</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>13.27877</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>0.81403</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>23.64721</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>6.56842</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>0.09956</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>1.20385</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <v>1.07212</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>1.19483</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>13.9265</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>0.78878</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>23.82886</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>6.5885</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>0.10111</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1.20753</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>1.04951</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>13.59053</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>0.81198</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>23.79344</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>6.55155</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>0.09838</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1.20075</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>1.10686</v>
+      </c>
+      <c r="H30" s="18" t="n">
+        <v>1.19972</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>13.75293</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>0.80233</v>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>23.90218</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>6.85219</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>0.12038</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>1.25585</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>0.04149</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>0.85583</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>0.9539800000000001</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>22.1486</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>0.63737</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>21.82426</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>6.94135</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>0.13289</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>1.2722</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>0.88062</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>1.13016</v>
+      </c>
+      <c r="I32" s="18" t="n">
+        <v>18.32846</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>0.73169</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>21.22568</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>APC_3_view_2_fk_NL_01_005</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>6.97201</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0.13962</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>1.16701</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>0.02046</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>1.86818</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>1.13328</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>10.56835</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>0.78215</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>17.54086</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>6.85787</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>1.1479</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>0.94994</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <v>1.1245</v>
+      </c>
+      <c r="I34" s="18" t="n">
+        <v>11.02087</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>0.79539</v>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>20.10916</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>6.7508</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>1.12998</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>1.22415</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <v>1.01733</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>11.46282</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>0.77905</v>
+      </c>
+      <c r="K35" s="18" t="n">
+        <v>20.28329</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>6.74884</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1.12965</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>0.02059</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>1.20549</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>1.04213</v>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>10.68365</v>
+      </c>
+      <c r="J36" s="19" t="n">
+        <v>0.8039500000000001</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>20.29606</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>6.72958</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>0.12082</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>1.12643</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>1.2704</v>
+      </c>
+      <c r="H37" s="18" t="n">
+        <v>1.02305</v>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>10.99068</v>
+      </c>
+      <c r="J37" s="18" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>20.32782</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr"/>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>6.94621</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>0.13545</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>1.16269</v>
+      </c>
+      <c r="F38" s="19" t="n">
+        <v>0.03917</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>0.91278</v>
+      </c>
+      <c r="H38" s="18" t="n">
+        <v>0.76545</v>
+      </c>
+      <c r="I38" s="19" t="n">
+        <v>18.48379</v>
+      </c>
+      <c r="J38" s="18" t="n">
+        <v>0.63209</v>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>19.54804</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>6.93056</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>0.13882</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1.16007</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>0.92591</v>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>0.88712</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>14.19098</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>0.73046</v>
+      </c>
+      <c r="K39" s="18" t="n">
+        <v>19.49656</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>APC_3_view_3_fk_NL_05_005</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>7.15201</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>0.16908</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>1.24327</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>2.14235</v>
+      </c>
+      <c r="H40" s="18" t="n">
+        <v>0.93895</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>9.45031</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>0.74598</v>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>15.69475</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>7.03295</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>0.13421</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1.22257</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>1.02548</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>1.03259</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>10.21071</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>0.75911</v>
+      </c>
+      <c r="K41" s="18" t="n">
+        <v>18.36213</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr"/>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>6.91258</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>0.12629</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>1.20164</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>1.34597</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>0.90465</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>10.81506</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>0.74317</v>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>18.5076</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr"/>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>6.92429</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>0.12643</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1.20368</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>1.3121</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>0.97314</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>9.725989999999999</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>0.7708700000000001</v>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>18.5285</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>6.89118</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>0.12503</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>1.19792</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>1.40122</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>0.91369</v>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>10.20499</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>0.75769</v>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>18.54075</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr"/>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>7.06944</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>0.14056</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>1.22891</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>0.92539</v>
+      </c>
+      <c r="H45" s="18" t="n">
+        <v>0.66939</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>17.16422</v>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>0.6188900000000001</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>17.97383</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>7.08189</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>0.14442</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>1.23108</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>0.03029</v>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>0.97851</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>0.7826</v>
+      </c>
+      <c r="I46" s="18" t="n">
+        <v>12.80877</v>
+      </c>
+      <c r="J46" s="18" t="n">
+        <v>0.70773</v>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>17.98693</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Athena_2_men_in_front_of_house_meting003</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>6.89303</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0.18155</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>0.99552</v>
+      </c>
+      <c r="F47" s="18" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>1.56809</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>1.12427</v>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>12.51811</v>
+      </c>
+      <c r="J47" s="18" t="n">
+        <v>0.69325</v>
+      </c>
+      <c r="K47" s="18" t="n">
+        <v>13.04707</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr"/>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>6.74675</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>0.11726</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <v>0.97439</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>0.65319</v>
+      </c>
+      <c r="H48" s="18" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="I48" s="18" t="n">
+        <v>12.88288</v>
+      </c>
+      <c r="J48" s="18" t="n">
+        <v>0.68789</v>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>15.44294</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>6.66613</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>0.10716</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>0.96275</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <v>0.02835</v>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>0.75053</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <v>0.55609</v>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>13.67014</v>
+      </c>
+      <c r="J49" s="18" t="n">
+        <v>0.67872</v>
+      </c>
+      <c r="K49" s="18" t="n">
+        <v>15.67766</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr"/>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>6.67564</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>0.10806</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>0.96412</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="G50" s="18" t="n">
+        <v>0.77034</v>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="I50" s="18" t="n">
+        <v>12.35633</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>15.68368</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr"/>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>6.59901</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>0.10119</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>0.95305</v>
+      </c>
+      <c r="F51" s="18" t="n">
+        <v>0.02602</v>
+      </c>
+      <c r="G51" s="18" t="n">
+        <v>0.76396</v>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>0.57363</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>12.24783</v>
+      </c>
+      <c r="J51" s="18" t="n">
+        <v>0.6979</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>15.75355</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr"/>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>6.92687</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>1.0004</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>0.04465</v>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>0.6212800000000001</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="I52" s="19" t="n">
+        <v>20.54914</v>
+      </c>
+      <c r="J52" s="18" t="n">
+        <v>0.58124</v>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>15.1583</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>7.06718</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>1.02067</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>0.03381</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>0.68004</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="I53" s="18" t="n">
+        <v>15.65434</v>
+      </c>
+      <c r="J53" s="18" t="n">
+        <v>0.66638</v>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>15.16937</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Athena_APC_4_fennek01_005</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>6.17799</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>0.07003</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>0.98434</v>
+      </c>
+      <c r="F54" s="18" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>1.40143</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="I54" s="18" t="n">
+        <v>9.772360000000001</v>
+      </c>
+      <c r="J54" s="18" t="n">
+        <v>0.73407</v>
+      </c>
+      <c r="K54" s="18" t="n">
+        <v>20.16412</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr"/>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>5.97004</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>0.06146</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>0.95121</v>
+      </c>
+      <c r="F55" s="18" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="G55" s="18" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="H55" s="18" t="n">
+        <v>0.18526</v>
+      </c>
+      <c r="I55" s="18" t="n">
+        <v>9.88344</v>
+      </c>
+      <c r="J55" s="18" t="n">
+        <v>0.74917</v>
+      </c>
+      <c r="K55" s="18" t="n">
+        <v>22.46399</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr"/>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>5.78884</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>0.92234</v>
+      </c>
+      <c r="F56" s="18" t="n">
+        <v>0.02513</v>
+      </c>
+      <c r="G56" s="18" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>0.14044</v>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>10.97125</v>
+      </c>
+      <c r="J56" s="18" t="n">
+        <v>0.72071</v>
+      </c>
+      <c r="K56" s="18" t="n">
+        <v>22.63467</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr"/>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>5.78812</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>0.05402</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>0.92222</v>
+      </c>
+      <c r="F57" s="18" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="G57" s="18" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="H57" s="18" t="n">
+        <v>0.14137</v>
+      </c>
+      <c r="I57" s="18" t="n">
+        <v>9.69835</v>
+      </c>
+      <c r="J57" s="19" t="n">
+        <v>0.75635</v>
+      </c>
+      <c r="K57" s="18" t="n">
+        <v>22.70385</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr"/>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>5.70675</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>0.90926</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>0.02362</v>
+      </c>
+      <c r="G58" s="18" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>0.14442</v>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>10.11212</v>
+      </c>
+      <c r="J58" s="18" t="n">
+        <v>0.7400099999999999</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>22.74749</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>6.33741</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>1.00974</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="G59" s="18" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="H59" s="18" t="n">
+        <v>0.13634</v>
+      </c>
+      <c r="I59" s="19" t="n">
+        <v>18.66549</v>
+      </c>
+      <c r="J59" s="18" t="n">
+        <v>0.6067399999999999</v>
+      </c>
+      <c r="K59" s="18" t="n">
+        <v>21.33732</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr"/>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>6.35595</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>1.01269</v>
+      </c>
+      <c r="F60" s="18" t="n">
+        <v>0.03142</v>
+      </c>
+      <c r="G60" s="18" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="H60" s="18" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="I60" s="18" t="n">
+        <v>13.34313</v>
+      </c>
+      <c r="J60" s="18" t="n">
+        <v>0.6945</v>
+      </c>
+      <c r="K60" s="18" t="n">
+        <v>21.65353</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Athena_heather_IR_hei_vis_g</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>7.08916</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="18" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>5.6735</v>
+      </c>
+      <c r="J61" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr"/>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>7.08916</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="18" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G62" s="18" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>5.67353</v>
+      </c>
+      <c r="J62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="18" t="n">
+        <v>107.88111</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>7.08916</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>5.0107</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>5.0107</v>
+      </c>
+      <c r="I63" s="18" t="n">
+        <v>5.6735</v>
+      </c>
+      <c r="J63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr"/>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>7.08916</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="18" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>5.06421</v>
+      </c>
+      <c r="I64" s="18" t="n">
+        <v>5.6735</v>
+      </c>
+      <c r="J64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr"/>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>7.08916</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="18" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G65" s="18" t="n">
+        <v>5.01264</v>
+      </c>
+      <c r="H65" s="18" t="n">
+        <v>5.01264</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>5.6735</v>
+      </c>
+      <c r="J65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr"/>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>7.15608</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>0.20826</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>1.00944</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>0.02793</v>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>2.40825</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>2.40825</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>11.06336</v>
+      </c>
+      <c r="J66" s="18" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="K66" s="18" t="n">
+        <v>28.42239</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>7.04619</v>
+      </c>
+      <c r="D67" s="19" t="n">
+        <v>0.23082</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>0.99394</v>
+      </c>
+      <c r="F67" s="18" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="G67" s="18" t="n">
+        <v>2.08045</v>
+      </c>
+      <c r="H67" s="18" t="n">
+        <v>2.08045</v>
+      </c>
+      <c r="I67" s="18" t="n">
+        <v>10.40211</v>
+      </c>
+      <c r="J67" s="18" t="n">
+        <v>0.85653</v>
+      </c>
+      <c r="K67" s="18" t="n">
+        <v>24.05388</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Athena_heather_hei_vis</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>6.78031</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>0.11115</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>0.94497</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <v>0.02633</v>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="H68" s="19" t="n">
+        <v>0.99355</v>
+      </c>
+      <c r="I68" s="18" t="n">
+        <v>12.80947</v>
+      </c>
+      <c r="J68" s="18" t="n">
+        <v>0.64496</v>
+      </c>
+      <c r="K68" s="18" t="n">
+        <v>13.39049</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr"/>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n">
+        <v>7.17891</v>
+      </c>
+      <c r="D69" s="19" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>1.00052</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="G69" s="19" t="n">
+        <v>0.91232</v>
+      </c>
+      <c r="H69" s="18" t="n">
+        <v>0.66654</v>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>15.74497</v>
+      </c>
+      <c r="J69" s="18" t="n">
+        <v>0.61528</v>
+      </c>
+      <c r="K69" s="18" t="n">
+        <v>15.20664</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr"/>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>6.8429</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>0.95369</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="G70" s="18" t="n">
+        <v>0.81913</v>
+      </c>
+      <c r="H70" s="18" t="n">
+        <v>0.62241</v>
+      </c>
+      <c r="I70" s="18" t="n">
+        <v>14.25477</v>
+      </c>
+      <c r="J70" s="18" t="n">
+        <v>0.63997</v>
+      </c>
+      <c r="K70" s="18" t="n">
+        <v>15.94798</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr"/>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>6.85389</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>0.11716</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>0.95522</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>0.02695</v>
+      </c>
+      <c r="G71" s="18" t="n">
+        <v>0.84463</v>
+      </c>
+      <c r="H71" s="18" t="n">
+        <v>0.63883</v>
+      </c>
+      <c r="I71" s="18" t="n">
+        <v>12.96626</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>0.67106</v>
+      </c>
+      <c r="K71" s="18" t="n">
+        <v>15.94995</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr"/>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>6.77987</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>0.11074</v>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>0.94491</v>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="G72" s="18" t="n">
+        <v>0.80447</v>
+      </c>
+      <c r="H72" s="18" t="n">
+        <v>0.63798</v>
+      </c>
+      <c r="I72" s="18" t="n">
+        <v>12.84176</v>
+      </c>
+      <c r="J72" s="18" t="n">
+        <v>0.66816</v>
+      </c>
+      <c r="K72" s="19" t="n">
+        <v>16.0358</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>7.015</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>0.97768</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="G73" s="18" t="n">
+        <v>0.57984</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>0.47524</v>
+      </c>
+      <c r="I73" s="19" t="n">
+        <v>22.87326</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>0.51791</v>
+      </c>
+      <c r="K73" s="18" t="n">
+        <v>15.57986</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr"/>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>7.13527</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>0.14402</v>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>0.99444</v>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>0.03623</v>
+      </c>
+      <c r="G74" s="18" t="n">
+        <v>0.71353</v>
+      </c>
+      <c r="H74" s="18" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="I74" s="18" t="n">
+        <v>16.45011</v>
+      </c>
+      <c r="J74" s="18" t="n">
+        <v>0.61482</v>
+      </c>
+      <c r="K74" s="18" t="n">
+        <v>15.48112</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Athena_helicopter_helib_011</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>5.21331</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>1.12728</v>
+      </c>
+      <c r="F75" s="18" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="G75" s="19" t="n">
+        <v>2.45287</v>
+      </c>
+      <c r="H75" s="18" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="I75" s="18" t="n">
+        <v>5.77158</v>
+      </c>
+      <c r="J75" s="18" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="K75" s="18" t="n">
+        <v>15.60525</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr"/>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>5.39822</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>1.16727</v>
+      </c>
+      <c r="F76" s="18" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="G76" s="18" t="n">
+        <v>0.79199</v>
+      </c>
+      <c r="H76" s="19" t="n">
+        <v>0.53452</v>
+      </c>
+      <c r="I76" s="18" t="n">
+        <v>6.03553</v>
+      </c>
+      <c r="J76" s="19" t="n">
+        <v>0.82202</v>
+      </c>
+      <c r="K76" s="18" t="n">
+        <v>18.36653</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr"/>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>5.21282</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>1.12718</v>
+      </c>
+      <c r="F77" s="18" t="n">
+        <v>0.01435</v>
+      </c>
+      <c r="G77" s="18" t="n">
+        <v>0.97925</v>
+      </c>
+      <c r="H77" s="18" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="I77" s="18" t="n">
+        <v>6.87237</v>
+      </c>
+      <c r="J77" s="18" t="n">
+        <v>0.8085599999999999</v>
+      </c>
+      <c r="K77" s="18" t="n">
+        <v>18.45971</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr"/>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>5.22957</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>1.1308</v>
+      </c>
+      <c r="F78" s="18" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="G78" s="18" t="n">
+        <v>0.99954</v>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>0.51293</v>
+      </c>
+      <c r="I78" s="18" t="n">
+        <v>5.69648</v>
+      </c>
+      <c r="J78" s="18" t="n">
+        <v>0.82092</v>
+      </c>
+      <c r="K78" s="18" t="n">
+        <v>18.46457</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr"/>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>5.14043</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>1.11152</v>
+      </c>
+      <c r="F79" s="18" t="n">
+        <v>0.01352</v>
+      </c>
+      <c r="G79" s="18" t="n">
+        <v>0.94282</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="I79" s="18" t="n">
+        <v>5.90699</v>
+      </c>
+      <c r="J79" s="18" t="n">
+        <v>0.81453</v>
+      </c>
+      <c r="K79" s="19" t="n">
+        <v>18.49703</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr"/>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="n">
+        <v>5.54167</v>
+      </c>
+      <c r="D80" s="18" t="n">
+        <v>0.05228</v>
+      </c>
+      <c r="E80" s="19" t="n">
+        <v>1.19828</v>
+      </c>
+      <c r="F80" s="19" t="n">
+        <v>0.02408</v>
+      </c>
+      <c r="G80" s="18" t="n">
+        <v>0.6873899999999999</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="I80" s="19" t="n">
+        <v>10.44723</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>0.6865599999999999</v>
+      </c>
+      <c r="K80" s="18" t="n">
+        <v>18.32726</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr"/>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>5.51013</v>
+      </c>
+      <c r="D81" s="19" t="n">
+        <v>0.05816</v>
+      </c>
+      <c r="E81" s="18" t="n">
+        <v>1.19146</v>
+      </c>
+      <c r="F81" s="18" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="G81" s="18" t="n">
+        <v>0.91818</v>
+      </c>
+      <c r="H81" s="18" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="I81" s="18" t="n">
+        <v>7.91304</v>
+      </c>
+      <c r="J81" s="18" t="n">
+        <v>0.76457</v>
+      </c>
+      <c r="K81" s="18" t="n">
+        <v>18.3341</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Athena_lake_lake</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>7.09199</v>
+      </c>
+      <c r="D82" s="19" t="n">
+        <v>0.16713</v>
+      </c>
+      <c r="E82" s="19" t="n">
+        <v>1.02629</v>
+      </c>
+      <c r="F82" s="18" t="n">
+        <v>0.02296</v>
+      </c>
+      <c r="G82" s="19" t="n">
+        <v>2.30568</v>
+      </c>
+      <c r="H82" s="19" t="n">
+        <v>0.60784</v>
+      </c>
+      <c r="I82" s="18" t="n">
+        <v>12.01755</v>
+      </c>
+      <c r="J82" s="18" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="K82" s="18" t="n">
+        <v>14.22738</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr"/>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>6.88445</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>0.99626</v>
+      </c>
+      <c r="F83" s="18" t="n">
+        <v>0.02446</v>
+      </c>
+      <c r="G83" s="18" t="n">
+        <v>1.03794</v>
+      </c>
+      <c r="H83" s="18" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="I83" s="18" t="n">
+        <v>11.95323</v>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>0.71279</v>
+      </c>
+      <c r="K83" s="18" t="n">
+        <v>16.23441</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr"/>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>6.67377</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>0.10688</v>
+      </c>
+      <c r="E84" s="18" t="n">
+        <v>0.96577</v>
+      </c>
+      <c r="F84" s="18" t="n">
+        <v>0.02522</v>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>1.08825</v>
+      </c>
+      <c r="H84" s="18" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="I84" s="18" t="n">
+        <v>12.9084</v>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>0.69107</v>
+      </c>
+      <c r="K84" s="18" t="n">
+        <v>16.80251</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr"/>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>6.66897</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>0.10687</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0.96508</v>
+      </c>
+      <c r="F85" s="18" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="G85" s="18" t="n">
+        <v>1.11329</v>
+      </c>
+      <c r="H85" s="18" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="I85" s="18" t="n">
+        <v>11.78781</v>
+      </c>
+      <c r="J85" s="19" t="n">
+        <v>0.71983</v>
+      </c>
+      <c r="K85" s="18" t="n">
+        <v>16.82319</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr"/>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>6.64541</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>0.10203</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>0.96167</v>
+      </c>
+      <c r="F86" s="18" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="G86" s="18" t="n">
+        <v>1.12112</v>
+      </c>
+      <c r="H86" s="18" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="I86" s="18" t="n">
+        <v>11.84776</v>
+      </c>
+      <c r="J86" s="18" t="n">
+        <v>0.71457</v>
+      </c>
+      <c r="K86" s="19" t="n">
+        <v>16.88078</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr"/>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>6.82374</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>0.12212</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>0.98747</v>
+      </c>
+      <c r="F87" s="19" t="n">
+        <v>0.04018</v>
+      </c>
+      <c r="G87" s="18" t="n">
+        <v>0.74622</v>
+      </c>
+      <c r="H87" s="18" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="I87" s="19" t="n">
+        <v>18.88932</v>
+      </c>
+      <c r="J87" s="18" t="n">
+        <v>0.5773200000000001</v>
+      </c>
+      <c r="K87" s="18" t="n">
+        <v>16.41734</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr"/>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>6.92892</v>
+      </c>
+      <c r="D88" s="18" t="n">
+        <v>0.12943</v>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>1.00269</v>
+      </c>
+      <c r="F88" s="18" t="n">
+        <v>0.03131</v>
+      </c>
+      <c r="G88" s="18" t="n">
+        <v>0.78332</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="I88" s="18" t="n">
+        <v>14.59501</v>
+      </c>
+      <c r="J88" s="18" t="n">
+        <v>0.65321</v>
+      </c>
+      <c r="K88" s="18" t="n">
+        <v>16.3503</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Athena_man_in_doorway_maninhuis</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>7.21331</v>
+      </c>
+      <c r="D89" s="19" t="n">
+        <v>0.17953</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>1.00589</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="G89" s="19" t="n">
+        <v>1.92017</v>
+      </c>
+      <c r="H89" s="19" t="n">
+        <v>0.6521</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>15.18843</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>0.64418</v>
+      </c>
+      <c r="K89" s="18" t="n">
+        <v>12.78198</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr"/>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>7.16948</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>0.99978</v>
+      </c>
+      <c r="F90" s="18" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="G90" s="18" t="n">
+        <v>0.7700900000000001</v>
+      </c>
+      <c r="H90" s="18" t="n">
+        <v>0.2168</v>
+      </c>
+      <c r="I90" s="18" t="n">
+        <v>15.58958</v>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>0.64583</v>
+      </c>
+      <c r="K90" s="18" t="n">
+        <v>14.82591</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr"/>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>6.99956</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>0.12618</v>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>0.97609</v>
+      </c>
+      <c r="F91" s="18" t="n">
+        <v>0.03658</v>
+      </c>
+      <c r="G91" s="18" t="n">
+        <v>0.7831900000000001</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="I91" s="18" t="n">
+        <v>16.92897</v>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>0.62929</v>
+      </c>
+      <c r="K91" s="18" t="n">
+        <v>15.25231</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr"/>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>7.0078</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>0.12688</v>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>0.97724</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>0.03299</v>
+      </c>
+      <c r="G92" s="18" t="n">
+        <v>0.80298</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>14.99515</v>
+      </c>
+      <c r="J92" s="19" t="n">
+        <v>0.65864</v>
+      </c>
+      <c r="K92" s="18" t="n">
+        <v>15.27454</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr"/>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>6.92723</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>0.11844</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>0.03311</v>
+      </c>
+      <c r="G93" s="18" t="n">
+        <v>0.80436</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>14.85462</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>0.64883</v>
+      </c>
+      <c r="K93" s="19" t="n">
+        <v>15.36467</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr"/>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>7.24318</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>0.15752</v>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>1.01006</v>
+      </c>
+      <c r="F94" s="19" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="G94" s="18" t="n">
+        <v>0.60453</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="I94" s="19" t="n">
+        <v>24.56038</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>0.54091</v>
+      </c>
+      <c r="K94" s="18" t="n">
+        <v>14.55284</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>7.40091</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>0.17166</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>1.03206</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="G95" s="18" t="n">
+        <v>0.72285</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>18.92324</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>0.61499</v>
+      </c>
+      <c r="K95" s="18" t="n">
+        <v>14.56546</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>Athena_soldier_behind_smoke_1_meting012-1200</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>7.17898</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <v>0.23123</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>1.05596</v>
+      </c>
+      <c r="F96" s="18" t="n">
+        <v>0.02848</v>
+      </c>
+      <c r="G96" s="19" t="n">
+        <v>3.54367</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>0.16305</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>14.02508</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>0.63295</v>
+      </c>
+      <c r="K96" s="18" t="n">
+        <v>10.7292</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr"/>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="n">
+        <v>7.16835</v>
+      </c>
+      <c r="D97" s="18" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>1.0544</v>
+      </c>
+      <c r="F97" s="18" t="n">
+        <v>0.03024</v>
+      </c>
+      <c r="G97" s="18" t="n">
+        <v>0.86652</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>13.12209</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>0.61167</v>
+      </c>
+      <c r="K97" s="18" t="n">
+        <v>13.3969</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr"/>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="n">
+        <v>7.08179</v>
+      </c>
+      <c r="D98" s="18" t="n">
+        <v>0.14567</v>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>1.04167</v>
+      </c>
+      <c r="F98" s="18" t="n">
+        <v>0.03138</v>
+      </c>
+      <c r="G98" s="18" t="n">
+        <v>1.15817</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>14.78912</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>0.61592</v>
+      </c>
+      <c r="K98" s="18" t="n">
+        <v>13.53558</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr"/>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="n">
+        <v>7.08409</v>
+      </c>
+      <c r="D99" s="18" t="n">
+        <v>0.14671</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>1.04201</v>
+      </c>
+      <c r="F99" s="18" t="n">
+        <v>0.02869</v>
+      </c>
+      <c r="G99" s="18" t="n">
+        <v>1.20121</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>13.5888</v>
+      </c>
+      <c r="J99" s="19" t="n">
+        <v>0.64472</v>
+      </c>
+      <c r="K99" s="18" t="n">
+        <v>13.53407</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>7.05119</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>0.14202</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>1.03716</v>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>0.02911</v>
+      </c>
+      <c r="G100" s="18" t="n">
+        <v>1.18721</v>
+      </c>
+      <c r="H100" s="19" t="n">
+        <v>0.46914</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>13.74852</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>0.63498</v>
+      </c>
+      <c r="K100" s="19" t="n">
+        <v>13.57298</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr"/>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="n">
+        <v>7.30639</v>
+      </c>
+      <c r="D101" s="18" t="n">
+        <v>0.16287</v>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>1.0747</v>
+      </c>
+      <c r="F101" s="19" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="G101" s="18" t="n">
+        <v>0.96915</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="I101" s="19" t="n">
+        <v>22.3488</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>0.51624</v>
+      </c>
+      <c r="K101" s="18" t="n">
+        <v>13.24124</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr"/>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="n">
+        <v>7.40754</v>
+      </c>
+      <c r="D102" s="18" t="n">
+        <v>0.17539</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <v>1.08958</v>
+      </c>
+      <c r="F102" s="18" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="G102" s="18" t="n">
+        <v>1.01982</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>17.18517</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>0.58352</v>
+      </c>
+      <c r="K102" s="18" t="n">
+        <v>13.18021</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Athena_soldier_behind_smoke_2_meting012-1500</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="n">
+        <v>6.54622</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>0.23468</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>1.0539</v>
+      </c>
+      <c r="F103" s="18" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="G103" s="19" t="n">
+        <v>2.54002</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>0.19195</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>13.161</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>0.6379899999999999</v>
+      </c>
+      <c r="K103" s="18" t="n">
+        <v>8.361840000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr"/>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="n">
+        <v>7.23045</v>
+      </c>
+      <c r="D104" s="18" t="n">
+        <v>0.15536</v>
+      </c>
+      <c r="E104" s="19" t="n">
+        <v>1.16405</v>
+      </c>
+      <c r="F104" s="18" t="n">
+        <v>0.03009</v>
+      </c>
+      <c r="G104" s="18" t="n">
+        <v>0.77905</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="I104" s="18" t="n">
+        <v>13.14571</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>0.56352</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>11.0215</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr"/>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="n">
+        <v>6.99178</v>
+      </c>
+      <c r="D105" s="18" t="n">
+        <v>0.13789</v>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>1.12563</v>
+      </c>
+      <c r="F105" s="18" t="n">
+        <v>0.02656</v>
+      </c>
+      <c r="G105" s="18" t="n">
+        <v>1.17823</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>0.59076</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>13.83465</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>0.63226</v>
+      </c>
+      <c r="K105" s="18" t="n">
+        <v>11.20686</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr"/>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n">
+        <v>6.99567</v>
+      </c>
+      <c r="D106" s="18" t="n">
+        <v>0.13793</v>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>1.12626</v>
+      </c>
+      <c r="F106" s="18" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="G106" s="18" t="n">
+        <v>1.1741</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>0.56615</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>13.03147</v>
+      </c>
+      <c r="J106" s="19" t="n">
+        <v>0.65846</v>
+      </c>
+      <c r="K106" s="18" t="n">
+        <v>11.21098</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr"/>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="n">
+        <v>6.97636</v>
+      </c>
+      <c r="D107" s="18" t="n">
+        <v>0.13504</v>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>1.12315</v>
+      </c>
+      <c r="F107" s="18" t="n">
+        <v>0.02527</v>
+      </c>
+      <c r="G107" s="18" t="n">
+        <v>1.23395</v>
+      </c>
+      <c r="H107" s="19" t="n">
+        <v>0.62229</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>13.23925</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>0.6505300000000001</v>
+      </c>
+      <c r="K107" s="19" t="n">
+        <v>11.2204</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr"/>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="n">
+        <v>7.16513</v>
+      </c>
+      <c r="D108" s="18" t="n">
+        <v>0.15199</v>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>1.15354</v>
+      </c>
+      <c r="F108" s="19" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="G108" s="18" t="n">
+        <v>0.96589</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="I108" s="19" t="n">
+        <v>22.3723</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>0.50989</v>
+      </c>
+      <c r="K108" s="18" t="n">
+        <v>11.09177</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr"/>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n">
+        <v>7.22417</v>
+      </c>
+      <c r="D109" s="18" t="n">
+        <v>0.15721</v>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>1.16304</v>
+      </c>
+      <c r="F109" s="18" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="G109" s="18" t="n">
+        <v>1.03259</v>
+      </c>
+      <c r="H109" s="18" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="I109" s="18" t="n">
+        <v>15.28394</v>
+      </c>
+      <c r="J109" s="18" t="n">
+        <v>0.6042999999999999</v>
+      </c>
+      <c r="K109" s="18" t="n">
+        <v>11.12007</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Athena_soldier_behind_smoke_3_meting012-1700</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="n">
+        <v>7.36929</v>
+      </c>
+      <c r="D110" s="19" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="E110" s="19" t="n">
+        <v>1.05332</v>
+      </c>
+      <c r="F110" s="18" t="n">
+        <v>0.03344</v>
+      </c>
+      <c r="G110" s="19" t="n">
+        <v>3.04556</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>0.15028</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>16.54316</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>0.63718</v>
+      </c>
+      <c r="K110" s="18" t="n">
+        <v>10.99661</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr"/>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="n">
+        <v>7.119</v>
+      </c>
+      <c r="D111" s="18" t="n">
+        <v>0.13968</v>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>1.01754</v>
+      </c>
+      <c r="F111" s="18" t="n">
+        <v>0.03208</v>
+      </c>
+      <c r="G111" s="18" t="n">
+        <v>0.86066</v>
+      </c>
+      <c r="H111" s="19" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="I111" s="18" t="n">
+        <v>14.83563</v>
+      </c>
+      <c r="J111" s="18" t="n">
+        <v>0.64057</v>
+      </c>
+      <c r="K111" s="18" t="n">
+        <v>13.67704</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr"/>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n">
+        <v>6.98599</v>
+      </c>
+      <c r="D112" s="18" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>0.99853</v>
+      </c>
+      <c r="F112" s="18" t="n">
+        <v>0.03577</v>
+      </c>
+      <c r="G112" s="18" t="n">
+        <v>1.1015</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>17.19472</v>
+      </c>
+      <c r="J112" s="18" t="n">
+        <v>0.62488</v>
+      </c>
+      <c r="K112" s="18" t="n">
+        <v>13.81986</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr"/>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n">
+        <v>6.99019</v>
+      </c>
+      <c r="D113" s="18" t="n">
+        <v>0.12725</v>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>0.99913</v>
+      </c>
+      <c r="F113" s="18" t="n">
+        <v>0.03395</v>
+      </c>
+      <c r="G113" s="18" t="n">
+        <v>1.11374</v>
+      </c>
+      <c r="H113" s="18" t="n">
+        <v>0.21943</v>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>16.39519</v>
+      </c>
+      <c r="J113" s="19" t="n">
+        <v>0.65011</v>
+      </c>
+      <c r="K113" s="18" t="n">
+        <v>13.82819</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr"/>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n">
+        <v>6.96759</v>
+      </c>
+      <c r="D114" s="18" t="n">
+        <v>0.12283</v>
+      </c>
+      <c r="E114" s="18" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="F114" s="18" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="G114" s="18" t="n">
+        <v>1.14072</v>
+      </c>
+      <c r="H114" s="18" t="n">
+        <v>0.21818</v>
+      </c>
+      <c r="I114" s="18" t="n">
+        <v>16.52297</v>
+      </c>
+      <c r="J114" s="18" t="n">
+        <v>0.6403799999999999</v>
+      </c>
+      <c r="K114" s="19" t="n">
+        <v>13.85431</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr"/>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n">
+        <v>7.24181</v>
+      </c>
+      <c r="D115" s="18" t="n">
+        <v>0.15055</v>
+      </c>
+      <c r="E115" s="18" t="n">
+        <v>1.0351</v>
+      </c>
+      <c r="F115" s="19" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="G115" s="18" t="n">
+        <v>0.80605</v>
+      </c>
+      <c r="H115" s="18" t="n">
+        <v>0.13159</v>
+      </c>
+      <c r="I115" s="19" t="n">
+        <v>31.50251</v>
+      </c>
+      <c r="J115" s="18" t="n">
+        <v>0.46877</v>
+      </c>
+      <c r="K115" s="18" t="n">
+        <v>13.42753</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr"/>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n">
+        <v>7.3131</v>
+      </c>
+      <c r="D116" s="18" t="n">
+        <v>0.15689</v>
+      </c>
+      <c r="E116" s="18" t="n">
+        <v>1.04529</v>
+      </c>
+      <c r="F116" s="18" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="G116" s="18" t="n">
+        <v>1.01998</v>
+      </c>
+      <c r="H116" s="18" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="I116" s="18" t="n">
+        <v>21.52529</v>
+      </c>
+      <c r="J116" s="18" t="n">
+        <v>0.58462</v>
+      </c>
+      <c r="K116" s="18" t="n">
+        <v>13.55303</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Athena_soldier_in_trench_1_meting016</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="n">
+        <v>7.14848</v>
+      </c>
+      <c r="D117" s="19" t="n">
+        <v>0.17319</v>
+      </c>
+      <c r="E117" s="19" t="n">
+        <v>1.04241</v>
+      </c>
+      <c r="F117" s="18" t="n">
+        <v>0.02635</v>
+      </c>
+      <c r="G117" s="19" t="n">
+        <v>2.88781</v>
+      </c>
+      <c r="H117" s="19" t="n">
+        <v>0.73847</v>
+      </c>
+      <c r="I117" s="18" t="n">
+        <v>14.31045</v>
+      </c>
+      <c r="J117" s="18" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="K117" s="18" t="n">
+        <v>13.88338</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr"/>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="n">
+        <v>6.77201</v>
+      </c>
+      <c r="D118" s="18" t="n">
+        <v>0.11813</v>
+      </c>
+      <c r="E118" s="18" t="n">
+        <v>0.98751</v>
+      </c>
+      <c r="F118" s="18" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="G118" s="18" t="n">
+        <v>1.29178</v>
+      </c>
+      <c r="H118" s="18" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="I118" s="18" t="n">
+        <v>13.2212</v>
+      </c>
+      <c r="J118" s="19" t="n">
+        <v>0.73645</v>
+      </c>
+      <c r="K118" s="18" t="n">
+        <v>16.48982</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr"/>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="n">
+        <v>6.70023</v>
+      </c>
+      <c r="D119" s="18" t="n">
+        <v>0.11031</v>
+      </c>
+      <c r="E119" s="18" t="n">
+        <v>0.97704</v>
+      </c>
+      <c r="F119" s="18" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="G119" s="18" t="n">
+        <v>1.24388</v>
+      </c>
+      <c r="H119" s="18" t="n">
+        <v>0.46291</v>
+      </c>
+      <c r="I119" s="18" t="n">
+        <v>14.88437</v>
+      </c>
+      <c r="J119" s="18" t="n">
+        <v>0.70481</v>
+      </c>
+      <c r="K119" s="18" t="n">
+        <v>16.58783</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr"/>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="n">
+        <v>6.7096</v>
+      </c>
+      <c r="D120" s="18" t="n">
+        <v>0.11112</v>
+      </c>
+      <c r="E120" s="18" t="n">
+        <v>0.97841</v>
+      </c>
+      <c r="F120" s="18" t="n">
+        <v>0.02622</v>
+      </c>
+      <c r="G120" s="18" t="n">
+        <v>1.21747</v>
+      </c>
+      <c r="H120" s="18" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="I120" s="18" t="n">
+        <v>14.18233</v>
+      </c>
+      <c r="J120" s="18" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="K120" s="18" t="n">
+        <v>16.58643</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr"/>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="n">
+        <v>6.67725</v>
+      </c>
+      <c r="D121" s="18" t="n">
+        <v>0.10459</v>
+      </c>
+      <c r="E121" s="18" t="n">
+        <v>0.9736900000000001</v>
+      </c>
+      <c r="F121" s="18" t="n">
+        <v>0.02626</v>
+      </c>
+      <c r="G121" s="18" t="n">
+        <v>1.26121</v>
+      </c>
+      <c r="H121" s="18" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="I121" s="18" t="n">
+        <v>13.97959</v>
+      </c>
+      <c r="J121" s="18" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="K121" s="19" t="n">
+        <v>16.6703</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr"/>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n">
+        <v>6.93055</v>
+      </c>
+      <c r="D122" s="18" t="n">
+        <v>0.12858</v>
+      </c>
+      <c r="E122" s="18" t="n">
+        <v>1.01063</v>
+      </c>
+      <c r="F122" s="19" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="G122" s="18" t="n">
+        <v>0.84544</v>
+      </c>
+      <c r="H122" s="18" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="I122" s="19" t="n">
+        <v>24.30066</v>
+      </c>
+      <c r="J122" s="18" t="n">
+        <v>0.52439</v>
+      </c>
+      <c r="K122" s="18" t="n">
+        <v>16.16213</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr"/>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="n">
+        <v>6.99043</v>
+      </c>
+      <c r="D123" s="18" t="n">
+        <v>0.13208</v>
+      </c>
+      <c r="E123" s="18" t="n">
+        <v>1.01936</v>
+      </c>
+      <c r="F123" s="18" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="G123" s="18" t="n">
+        <v>1.02335</v>
+      </c>
+      <c r="H123" s="18" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="I123" s="18" t="n">
+        <v>18.10696</v>
+      </c>
+      <c r="J123" s="18" t="n">
+        <v>0.64312</v>
+      </c>
+      <c r="K123" s="18" t="n">
+        <v>16.19171</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Athena_soldier_in_trench_2_meting055</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="n">
+        <v>6.73158</v>
+      </c>
+      <c r="D124" s="19" t="n">
+        <v>0.12279</v>
+      </c>
+      <c r="E124" s="18" t="n">
+        <v>1.0193</v>
+      </c>
+      <c r="F124" s="18" t="n">
+        <v>0.02951</v>
+      </c>
+      <c r="G124" s="19" t="n">
+        <v>2.15668</v>
+      </c>
+      <c r="H124" s="19" t="n">
+        <v>0.54261</v>
+      </c>
+      <c r="I124" s="18" t="n">
+        <v>15.11527</v>
+      </c>
+      <c r="J124" s="18" t="n">
+        <v>0.69969</v>
+      </c>
+      <c r="K124" s="18" t="n">
+        <v>16.70199</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr"/>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="n">
+        <v>6.63621</v>
+      </c>
+      <c r="D125" s="18" t="n">
+        <v>0.10289</v>
+      </c>
+      <c r="E125" s="18" t="n">
+        <v>1.00486</v>
+      </c>
+      <c r="F125" s="18" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="G125" s="18" t="n">
+        <v>1.37868</v>
+      </c>
+      <c r="H125" s="18" t="n">
+        <v>0.21375</v>
+      </c>
+      <c r="I125" s="18" t="n">
+        <v>14.94544</v>
+      </c>
+      <c r="J125" s="18" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="K125" s="18" t="n">
+        <v>19.11213</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr"/>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="n">
+        <v>6.48079</v>
+      </c>
+      <c r="D126" s="18" t="n">
+        <v>0.09335</v>
+      </c>
+      <c r="E126" s="18" t="n">
+        <v>0.98133</v>
+      </c>
+      <c r="F126" s="18" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="G126" s="18" t="n">
+        <v>1.3427</v>
+      </c>
+      <c r="H126" s="18" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="I126" s="18" t="n">
+        <v>15.22199</v>
+      </c>
+      <c r="J126" s="18" t="n">
+        <v>0.69501</v>
+      </c>
+      <c r="K126" s="18" t="n">
+        <v>19.29144</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr"/>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="n">
+        <v>6.48436</v>
+      </c>
+      <c r="D127" s="18" t="n">
+        <v>0.09447999999999999</v>
+      </c>
+      <c r="E127" s="18" t="n">
+        <v>0.98187</v>
+      </c>
+      <c r="F127" s="18" t="n">
+        <v>0.02939</v>
+      </c>
+      <c r="G127" s="18" t="n">
+        <v>1.32576</v>
+      </c>
+      <c r="H127" s="18" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="I127" s="18" t="n">
+        <v>14.84191</v>
+      </c>
+      <c r="J127" s="19" t="n">
+        <v>0.70927</v>
+      </c>
+      <c r="K127" s="18" t="n">
+        <v>19.27657</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr"/>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="n">
+        <v>6.44778</v>
+      </c>
+      <c r="D128" s="18" t="n">
+        <v>0.08896</v>
+      </c>
+      <c r="E128" s="18" t="n">
+        <v>0.97633</v>
+      </c>
+      <c r="F128" s="18" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="G128" s="18" t="n">
+        <v>1.34281</v>
+      </c>
+      <c r="H128" s="18" t="n">
+        <v>0.19762</v>
+      </c>
+      <c r="I128" s="18" t="n">
+        <v>14.83737</v>
+      </c>
+      <c r="J128" s="18" t="n">
+        <v>0.70504</v>
+      </c>
+      <c r="K128" s="19" t="n">
+        <v>19.37928</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr"/>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="n">
+        <v>6.79983</v>
+      </c>
+      <c r="D129" s="18" t="n">
+        <v>0.11783</v>
+      </c>
+      <c r="E129" s="18" t="n">
+        <v>1.02964</v>
+      </c>
+      <c r="F129" s="19" t="n">
+        <v>0.06115</v>
+      </c>
+      <c r="G129" s="18" t="n">
+        <v>0.73865</v>
+      </c>
+      <c r="H129" s="18" t="n">
+        <v>0.13575</v>
+      </c>
+      <c r="I129" s="19" t="n">
+        <v>28.38415</v>
+      </c>
+      <c r="J129" s="18" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="K129" s="18" t="n">
+        <v>18.25096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr"/>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="n">
+        <v>6.86852</v>
+      </c>
+      <c r="D130" s="18" t="n">
+        <v>0.12106</v>
+      </c>
+      <c r="E130" s="19" t="n">
+        <v>1.04004</v>
+      </c>
+      <c r="F130" s="18" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="G130" s="18" t="n">
+        <v>1.0178</v>
+      </c>
+      <c r="H130" s="18" t="n">
+        <v>0.19241</v>
+      </c>
+      <c r="I130" s="18" t="n">
+        <v>20.84752</v>
+      </c>
+      <c r="J130" s="18" t="n">
+        <v>0.60032</v>
+      </c>
+      <c r="K130" s="18" t="n">
+        <v>18.43041</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Triclobs_Bosnia_R</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="n">
+        <v>6.6608</v>
+      </c>
+      <c r="D131" s="18" t="n">
+        <v>0.20848</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="F131" s="18" t="n">
+        <v>0.02039</v>
+      </c>
+      <c r="G131" s="18" t="n">
+        <v>0.5946900000000001</v>
+      </c>
+      <c r="H131" s="19" t="n">
+        <v>2.23326</v>
+      </c>
+      <c r="I131" s="18" t="n">
+        <v>14.33327</v>
+      </c>
+      <c r="J131" s="18" t="n">
+        <v>0.7113699999999999</v>
+      </c>
+      <c r="K131" s="18" t="n">
+        <v>12.8646</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr"/>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="n">
+        <v>6.84209</v>
+      </c>
+      <c r="D132" s="18" t="n">
+        <v>0.1981</v>
+      </c>
+      <c r="E132" s="18" t="n">
+        <v>1.14843</v>
+      </c>
+      <c r="F132" s="18" t="n">
+        <v>0.02799</v>
+      </c>
+      <c r="G132" s="18" t="n">
+        <v>1.01516</v>
+      </c>
+      <c r="H132" s="18" t="n">
+        <v>1.18966</v>
+      </c>
+      <c r="I132" s="18" t="n">
+        <v>16.30418</v>
+      </c>
+      <c r="J132" s="18" t="n">
+        <v>0.66851</v>
+      </c>
+      <c r="K132" s="18" t="n">
+        <v>15.65191</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr"/>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="n">
+        <v>6.82623</v>
+      </c>
+      <c r="D133" s="18" t="n">
+        <v>0.19539</v>
+      </c>
+      <c r="E133" s="18" t="n">
+        <v>1.14577</v>
+      </c>
+      <c r="F133" s="18" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="G133" s="19" t="n">
+        <v>1.02081</v>
+      </c>
+      <c r="H133" s="18" t="n">
+        <v>1.47385</v>
+      </c>
+      <c r="I133" s="18" t="n">
+        <v>15.47238</v>
+      </c>
+      <c r="J133" s="18" t="n">
+        <v>0.72483</v>
+      </c>
+      <c r="K133" s="18" t="n">
+        <v>15.67583</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr"/>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n">
+        <v>6.85274</v>
+      </c>
+      <c r="D134" s="18" t="n">
+        <v>0.19517</v>
+      </c>
+      <c r="E134" s="18" t="n">
+        <v>1.15022</v>
+      </c>
+      <c r="F134" s="18" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="G134" s="18" t="n">
+        <v>0.98306</v>
+      </c>
+      <c r="H134" s="18" t="n">
+        <v>1.38871</v>
+      </c>
+      <c r="I134" s="18" t="n">
+        <v>14.45144</v>
+      </c>
+      <c r="J134" s="19" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="K134" s="18" t="n">
+        <v>15.69059</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr"/>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="n">
+        <v>6.7869</v>
+      </c>
+      <c r="D135" s="18" t="n">
+        <v>0.19204</v>
+      </c>
+      <c r="E135" s="18" t="n">
+        <v>1.13917</v>
+      </c>
+      <c r="F135" s="18" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="G135" s="18" t="n">
+        <v>1.00349</v>
+      </c>
+      <c r="H135" s="18" t="n">
+        <v>1.40862</v>
+      </c>
+      <c r="I135" s="18" t="n">
+        <v>14.49227</v>
+      </c>
+      <c r="J135" s="18" t="n">
+        <v>0.7296899999999999</v>
+      </c>
+      <c r="K135" s="19" t="n">
+        <v>15.74157</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr"/>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="n">
+        <v>6.95871</v>
+      </c>
+      <c r="D136" s="18" t="n">
+        <v>0.20357</v>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="F136" s="19" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="G136" s="18" t="n">
+        <v>0.89691</v>
+      </c>
+      <c r="H136" s="18" t="n">
+        <v>1.10565</v>
+      </c>
+      <c r="I136" s="19" t="n">
+        <v>24.003</v>
+      </c>
+      <c r="J136" s="18" t="n">
+        <v>0.57218</v>
+      </c>
+      <c r="K136" s="18" t="n">
+        <v>15.33263</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr"/>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="n">
+        <v>6.97538</v>
+      </c>
+      <c r="D137" s="19" t="n">
+        <v>0.22364</v>
+      </c>
+      <c r="E137" s="19" t="n">
+        <v>1.1708</v>
+      </c>
+      <c r="F137" s="18" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="G137" s="18" t="n">
+        <v>0.88741</v>
+      </c>
+      <c r="H137" s="18" t="n">
+        <v>1.31187</v>
+      </c>
+      <c r="I137" s="18" t="n">
+        <v>18.8666</v>
+      </c>
+      <c r="J137" s="18" t="n">
+        <v>0.68531</v>
+      </c>
+      <c r="K137" s="18" t="n">
+        <v>15.00983</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>Triclobs_jeep_in_smoke_R</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>Pirámide de Laplace (LP)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="n">
+        <v>6.93067</v>
+      </c>
+      <c r="D138" s="18" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>1.01463</v>
+      </c>
+      <c r="F138" s="18" t="n">
+        <v>0.03888</v>
+      </c>
+      <c r="G138" s="18" t="n">
+        <v>0.8821</v>
+      </c>
+      <c r="H138" s="19" t="n">
+        <v>1.38236</v>
+      </c>
+      <c r="I138" s="18" t="n">
+        <v>22.47202</v>
+      </c>
+      <c r="J138" s="18" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="K138" s="18" t="n">
+        <v>14.06184</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr"/>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of low-pass Pyramid (RP)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="n">
+        <v>7.1874</v>
+      </c>
+      <c r="D139" s="18" t="n">
+        <v>0.14957</v>
+      </c>
+      <c r="E139" s="18" t="n">
+        <v>1.05222</v>
+      </c>
+      <c r="F139" s="18" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="G139" s="18" t="n">
+        <v>1.32143</v>
+      </c>
+      <c r="H139" s="18" t="n">
+        <v>0.93947</v>
+      </c>
+      <c r="I139" s="18" t="n">
+        <v>26.71208</v>
+      </c>
+      <c r="J139" s="18" t="n">
+        <v>0.59653</v>
+      </c>
+      <c r="K139" s="18" t="n">
+        <v>16.34186</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr"/>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>Wavelet discreta (DWT)</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="n">
+        <v>7.10092</v>
+      </c>
+      <c r="D140" s="18" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="E140" s="18" t="n">
+        <v>1.03956</v>
+      </c>
+      <c r="F140" s="18" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="G140" s="18" t="n">
+        <v>1.34031</v>
+      </c>
+      <c r="H140" s="18" t="n">
+        <v>1.00889</v>
+      </c>
+      <c r="I140" s="18" t="n">
+        <v>23.63965</v>
+      </c>
+      <c r="J140" s="18" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="K140" s="18" t="n">
+        <v>16.62357</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr"/>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="n">
+        <v>7.10352</v>
+      </c>
+      <c r="D141" s="18" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="E141" s="18" t="n">
+        <v>1.03994</v>
+      </c>
+      <c r="F141" s="18" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="G141" s="19" t="n">
+        <v>1.38081</v>
+      </c>
+      <c r="H141" s="18" t="n">
+        <v>0.99291</v>
+      </c>
+      <c r="I141" s="18" t="n">
+        <v>22.59167</v>
+      </c>
+      <c r="J141" s="19" t="n">
+        <v>0.6383799999999999</v>
+      </c>
+      <c r="K141" s="18" t="n">
+        <v>16.6409</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr"/>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Curvelet (CVT)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="n">
+        <v>7.06123</v>
+      </c>
+      <c r="D142" s="18" t="n">
+        <v>0.13242</v>
+      </c>
+      <c r="E142" s="18" t="n">
+        <v>1.03375</v>
+      </c>
+      <c r="F142" s="18" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="G142" s="18" t="n">
+        <v>1.30723</v>
+      </c>
+      <c r="H142" s="18" t="n">
+        <v>0.98019</v>
+      </c>
+      <c r="I142" s="18" t="n">
+        <v>22.92362</v>
+      </c>
+      <c r="J142" s="18" t="n">
+        <v>0.63071</v>
+      </c>
+      <c r="K142" s="19" t="n">
+        <v>16.69141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr"/>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>Top-Hat clásico</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="n">
+        <v>7.3674</v>
+      </c>
+      <c r="D143" s="18" t="n">
+        <v>0.16592</v>
+      </c>
+      <c r="E143" s="18" t="n">
+        <v>1.07857</v>
+      </c>
+      <c r="F143" s="19" t="n">
+        <v>0.08152</v>
+      </c>
+      <c r="G143" s="18" t="n">
+        <v>0.8535199999999999</v>
+      </c>
+      <c r="H143" s="18" t="n">
+        <v>0.53748</v>
+      </c>
+      <c r="I143" s="19" t="n">
+        <v>44.90313</v>
+      </c>
+      <c r="J143" s="18" t="n">
+        <v>0.45636</v>
+      </c>
+      <c r="K143" s="18" t="n">
+        <v>15.54351</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr"/>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="n">
+        <v>7.39259</v>
+      </c>
+      <c r="D144" s="19" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="E144" s="19" t="n">
+        <v>1.08226</v>
+      </c>
+      <c r="F144" s="18" t="n">
+        <v>0.05851</v>
+      </c>
+      <c r="G144" s="18" t="n">
+        <v>1.25104</v>
+      </c>
+      <c r="H144" s="18" t="n">
+        <v>0.93977</v>
+      </c>
+      <c r="I144" s="18" t="n">
+        <v>32.4941</v>
+      </c>
+      <c r="J144" s="18" t="n">
+        <v>0.56818</v>
+      </c>
+      <c r="K144" s="18" t="n">
+        <v>15.60396</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>Recuento sobre las 20 escenas — la propuesta obtiene el mejor valor en: EN 11/20 · SD 8/20 · FE 11/20 · MG 0/20 · MI_vis 0/20 · MI_ir 0/20 · SF 0/20 · SSIM 0/20 · PSNR 0/20. Confirma el patrón de los promedios: lidera las métricas de información y contraste, y cede las de fidelidad a las fuentes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K144"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3134,7 +8482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3186,15 +8534,15 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>81.38</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="22" t="n">
         <v>1.851250734915931e-15</v>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -3204,15 +8552,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>101.74</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="22" t="n">
         <v>1.088386607957448e-19</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -3222,15 +8570,15 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="21" t="n">
         <v>81.38</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="22" t="n">
         <v>1.851250734915931e-15</v>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -3240,15 +8588,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="21" t="n">
         <v>101.19</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="22" t="n">
         <v>1.414652483800934e-19</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -3258,15 +8606,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>71.84999999999999</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="22" t="n">
         <v>1.706123971832938e-13</v>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -3276,15 +8624,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="21" t="n">
         <v>59.98</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="22" t="n">
         <v>4.546523434404776e-11</v>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -3294,15 +8642,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="21" t="n">
         <v>96.31999999999999</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="22" t="n">
         <v>1.465042903035624e-18</v>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -3312,15 +8660,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="21" t="n">
         <v>99.58</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="22" t="n">
         <v>3.072490463062902e-19</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
@@ -3330,15 +8678,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="21" t="n">
         <v>107.32</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="22" t="n">
         <v>7.42059728052933e-21</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -3352,7 +8700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3450,7 +8798,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -3464,13 +8812,13 @@
       <c r="F5" s="12" t="n">
         <v>6.6645</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J5" s="15">
@@ -3489,7 +8837,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -3503,13 +8851,13 @@
       <c r="F6" s="12" t="n">
         <v>1.0529</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J6" s="15">
@@ -3528,7 +8876,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -3542,13 +8890,13 @@
       <c r="F7" s="12" t="n">
         <v>0.0256</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="15">
@@ -3567,7 +8915,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -3581,13 +8929,13 @@
       <c r="F8" s="12" t="n">
         <v>0.8843</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="22" t="n">
         <v>2.6702880859375e-05</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="22" t="n">
         <v>0.0002</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="23" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="J8" s="15">
@@ -3606,7 +8954,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -3620,13 +8968,13 @@
       <c r="F9" s="12" t="n">
         <v>1.3038</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="22" t="n">
         <v>5.7220458984375e-06</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="23" t="n">
         <v>-0.98</v>
       </c>
       <c r="J9" s="15">
@@ -3645,7 +8993,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -3659,13 +9007,13 @@
       <c r="F10" s="12" t="n">
         <v>22.8375</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J10" s="15">
@@ -3684,7 +9032,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -3698,13 +9046,13 @@
       <c r="F11" s="12" t="n">
         <v>0.1167</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="15">
@@ -3723,7 +9071,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -3737,13 +9085,13 @@
       <c r="F12" s="12" t="n">
         <v>13.151</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="15">
@@ -3762,7 +9110,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -3776,13 +9124,13 @@
       <c r="F13" s="12" t="n">
         <v>0.7305</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J13" s="15">
@@ -3801,7 +9149,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -3815,13 +9163,13 @@
       <c r="F14" s="12" t="n">
         <v>6.706</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J14" s="15">
@@ -3840,7 +9188,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -3854,13 +9202,13 @@
       <c r="F15" s="12" t="n">
         <v>1.0596</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J15" s="15">
@@ -3879,7 +9227,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -3893,13 +9241,13 @@
       <c r="F16" s="12" t="n">
         <v>0.0251</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="15">
@@ -3918,7 +9266,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -3932,13 +9280,13 @@
       <c r="F17" s="12" t="n">
         <v>0.8908</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="22" t="n">
         <v>1.33514404296875e-05</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="23" t="n">
         <v>-0.96</v>
       </c>
       <c r="J17" s="15">
@@ -3957,7 +9305,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -3971,13 +9319,13 @@
       <c r="F18" s="12" t="n">
         <v>1.2887</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="23" t="n">
         <v>-0.99</v>
       </c>
       <c r="J18" s="15">
@@ -3996,7 +9344,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -4010,13 +9358,13 @@
       <c r="F19" s="12" t="n">
         <v>22.7857</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J19" s="15">
@@ -4035,7 +9383,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -4049,13 +9397,13 @@
       <c r="F20" s="12" t="n">
         <v>0.1205</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="15">
@@ -4074,7 +9422,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -4088,13 +9436,13 @@
       <c r="F21" s="12" t="n">
         <v>13.0266</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="15">
@@ -4113,7 +9461,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -4127,13 +9475,13 @@
       <c r="F22" s="12" t="n">
         <v>0.7386</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J22" s="15">
@@ -4152,7 +9500,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -4166,13 +9514,13 @@
       <c r="F23" s="12" t="n">
         <v>6.7002</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J23" s="15">
@@ -4191,7 +9539,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -4205,13 +9553,13 @@
       <c r="F24" s="12" t="n">
         <v>1.0586</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="22" t="n">
         <v>3.814697265625e-06</v>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="23" t="n">
         <v>0.99</v>
       </c>
       <c r="J24" s="15">
@@ -4230,7 +9578,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -4244,13 +9592,13 @@
       <c r="F25" s="12" t="n">
         <v>0.027</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="21" t="n">
+      <c r="I25" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="15">
@@ -4269,7 +9617,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -4283,13 +9631,13 @@
       <c r="F26" s="12" t="n">
         <v>0.8809</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="22" t="n">
         <v>0.0001678466796875</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="22" t="n">
         <v>0.0005</v>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="23" t="n">
         <v>-0.88</v>
       </c>
       <c r="J26" s="15">
@@ -4308,7 +9656,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -4322,13 +9670,13 @@
       <c r="F27" s="12" t="n">
         <v>1.2846</v>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="22" t="n">
         <v>5.7220458984375e-06</v>
       </c>
-      <c r="H27" s="20" t="n">
+      <c r="H27" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="21" t="n">
+      <c r="I27" s="23" t="n">
         <v>-0.98</v>
       </c>
       <c r="J27" s="15">
@@ -4347,7 +9695,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -4361,13 +9709,13 @@
       <c r="F28" s="12" t="n">
         <v>22.7767</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J28" s="15">
@@ -4386,7 +9734,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -4400,13 +9748,13 @@
       <c r="F29" s="12" t="n">
         <v>0.1199</v>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H29" s="20" t="n">
+      <c r="H29" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="I29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="15">
@@ -4425,7 +9773,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -4439,13 +9787,13 @@
       <c r="F30" s="12" t="n">
         <v>13.9341</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H30" s="20" t="n">
+      <c r="H30" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="I30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="15">
@@ -4464,7 +9812,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -4478,13 +9826,13 @@
       <c r="F31" s="12" t="n">
         <v>0.7163</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H31" s="20" t="n">
+      <c r="H31" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="I31" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J31" s="15">
@@ -4503,7 +9851,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -4517,13 +9865,13 @@
       <c r="F32" s="12" t="n">
         <v>6.835</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="22" t="n">
         <v>0.0072956085205078</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="22" t="n">
         <v>0.0146</v>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="I32" s="23" t="n">
         <v>0.67</v>
       </c>
       <c r="J32" s="15">
@@ -4542,7 +9890,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -4556,13 +9904,13 @@
       <c r="F33" s="12" t="n">
         <v>1.0792</v>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="22" t="n">
         <v>0.0072956085205078</v>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H33" s="22" t="n">
         <v>0.0146</v>
       </c>
-      <c r="I33" s="21" t="n">
+      <c r="I33" s="23" t="n">
         <v>0.67</v>
       </c>
       <c r="J33" s="15">
@@ -4581,7 +9929,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -4595,13 +9943,13 @@
       <c r="F34" s="12" t="n">
         <v>0.0248</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H34" s="20" t="n">
+      <c r="H34" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="I34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="15">
@@ -4620,7 +9968,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -4634,13 +9982,13 @@
       <c r="F35" s="12" t="n">
         <v>1.0717</v>
       </c>
-      <c r="G35" s="20" t="n">
+      <c r="G35" s="22" t="n">
         <v>0.0003223419189453</v>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="22" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="I35" s="21" t="n">
+      <c r="I35" s="23" t="n">
         <v>-0.85</v>
       </c>
       <c r="J35" s="15">
@@ -4659,7 +10007,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -4673,13 +10021,13 @@
       <c r="F36" s="12" t="n">
         <v>2.1183</v>
       </c>
-      <c r="G36" s="20" t="n">
+      <c r="G36" s="22" t="n">
         <v>2.6702880859375e-05</v>
       </c>
-      <c r="H36" s="20" t="n">
+      <c r="H36" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I36" s="21" t="n">
+      <c r="I36" s="23" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="J36" s="15">
@@ -4698,7 +10046,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -4712,13 +10060,13 @@
       <c r="F37" s="12" t="n">
         <v>20.2687</v>
       </c>
-      <c r="G37" s="20" t="n">
+      <c r="G37" s="22" t="n">
         <v>0.0008506774902343</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="22" t="n">
         <v>0.0014</v>
       </c>
-      <c r="I37" s="21" t="n">
+      <c r="I37" s="23" t="n">
         <v>0.8</v>
       </c>
       <c r="J37" s="15">
@@ -4737,7 +10085,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -4751,13 +10099,13 @@
       <c r="F38" s="12" t="n">
         <v>0.1548</v>
       </c>
-      <c r="G38" s="20" t="n">
+      <c r="G38" s="22" t="n">
         <v>0.4980087280273437</v>
       </c>
-      <c r="H38" s="20" t="n">
+      <c r="H38" s="22" t="n">
         <v>0.498</v>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="I38" s="23" t="n">
         <v>-0.18</v>
       </c>
       <c r="J38" s="15">
@@ -4776,7 +10124,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -4790,13 +10138,13 @@
       <c r="F39" s="12" t="n">
         <v>13.04</v>
       </c>
-      <c r="G39" s="20" t="n">
+      <c r="G39" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="21" t="n">
+      <c r="I39" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="15">
@@ -4815,7 +10163,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -4829,13 +10177,13 @@
       <c r="F40" s="12" t="n">
         <v>0.7208</v>
       </c>
-      <c r="G40" s="20" t="n">
+      <c r="G40" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H40" s="20" t="n">
+      <c r="H40" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="21" t="n">
+      <c r="I40" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J40" s="15">
@@ -4854,7 +10202,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -4868,13 +10216,13 @@
       <c r="F41" s="12" t="n">
         <v>6.8285</v>
       </c>
-      <c r="G41" s="20" t="n">
+      <c r="G41" s="22" t="n">
         <v>2.6702880859375e-05</v>
       </c>
-      <c r="H41" s="20" t="n">
+      <c r="H41" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I41" s="21" t="n">
+      <c r="I41" s="23" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="J41" s="15">
@@ -4893,7 +10241,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -4907,13 +10255,13 @@
       <c r="F42" s="12" t="n">
         <v>1.079</v>
       </c>
-      <c r="G42" s="20" t="n">
+      <c r="G42" s="22" t="n">
         <v>2.6702880859375e-05</v>
       </c>
-      <c r="H42" s="20" t="n">
+      <c r="H42" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I42" s="21" t="n">
+      <c r="I42" s="23" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="J42" s="15">
@@ -4932,7 +10280,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -4946,13 +10294,13 @@
       <c r="F43" s="12" t="n">
         <v>0.0269</v>
       </c>
-      <c r="G43" s="20" t="n">
+      <c r="G43" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H43" s="20" t="n">
+      <c r="H43" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="21" t="n">
+      <c r="I43" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="15">
@@ -4971,7 +10319,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -4985,13 +10333,13 @@
       <c r="F44" s="12" t="n">
         <v>0.8807</v>
       </c>
-      <c r="G44" s="20" t="n">
+      <c r="G44" s="22" t="n">
         <v>0.0239505767822265</v>
       </c>
-      <c r="H44" s="20" t="n">
+      <c r="H44" s="22" t="n">
         <v>0.024</v>
       </c>
-      <c r="I44" s="21" t="n">
+      <c r="I44" s="23" t="n">
         <v>-0.57</v>
       </c>
       <c r="J44" s="15">
@@ -5010,7 +10358,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -5024,13 +10372,13 @@
       <c r="F45" s="12" t="n">
         <v>1.1698</v>
       </c>
-      <c r="G45" s="20" t="n">
+      <c r="G45" s="22" t="n">
         <v>0.0758514404296875</v>
       </c>
-      <c r="H45" s="20" t="n">
+      <c r="H45" s="22" t="n">
         <v>0.0759</v>
       </c>
-      <c r="I45" s="21" t="n">
+      <c r="I45" s="23" t="n">
         <v>-0.46</v>
       </c>
       <c r="J45" s="15">
@@ -5049,7 +10397,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -5063,13 +10411,13 @@
       <c r="F46" s="12" t="n">
         <v>21.9655</v>
       </c>
-      <c r="G46" s="20" t="n">
+      <c r="G46" s="22" t="n">
         <v>0.0001678466796875</v>
       </c>
-      <c r="H46" s="20" t="n">
+      <c r="H46" s="22" t="n">
         <v>0.0007</v>
       </c>
-      <c r="I46" s="21" t="n">
+      <c r="I46" s="23" t="n">
         <v>-0.88</v>
       </c>
       <c r="J46" s="15">
@@ -5088,7 +10436,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -5102,13 +10450,13 @@
       <c r="F47" s="12" t="n">
         <v>0.1304</v>
       </c>
-      <c r="G47" s="20" t="n">
+      <c r="G47" s="22" t="n">
         <v>1.9073486328125e-05</v>
       </c>
-      <c r="H47" s="20" t="n">
+      <c r="H47" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I47" s="21" t="n">
+      <c r="I47" s="23" t="n">
         <v>0.95</v>
       </c>
       <c r="J47" s="15">
@@ -5127,7 +10475,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -5141,13 +10489,13 @@
       <c r="F48" s="12" t="n">
         <v>13.3376</v>
       </c>
-      <c r="G48" s="20" t="n">
+      <c r="G48" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H48" s="20" t="n">
+      <c r="H48" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="21" t="n">
+      <c r="I48" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="15">
@@ -5166,7 +10514,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -5180,13 +10528,13 @@
       <c r="F49" s="12" t="n">
         <v>0.7212</v>
       </c>
-      <c r="G49" s="20" t="n">
+      <c r="G49" s="22" t="n">
         <v>6.29425048828125e-05</v>
       </c>
-      <c r="H49" s="20" t="n">
+      <c r="H49" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I49" s="21" t="n">
+      <c r="I49" s="23" t="n">
         <v>-0.91</v>
       </c>
       <c r="J49" s="15">
@@ -5205,7 +10553,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -5219,13 +10567,13 @@
       <c r="F50" s="12" t="n">
         <v>6.6645</v>
       </c>
-      <c r="G50" s="20" t="n">
+      <c r="G50" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H50" s="20" t="n">
+      <c r="H50" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I50" s="21" t="n">
+      <c r="I50" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="15">
@@ -5244,7 +10592,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -5258,13 +10606,13 @@
       <c r="F51" s="12" t="n">
         <v>1.0529</v>
       </c>
-      <c r="G51" s="20" t="n">
+      <c r="G51" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H51" s="20" t="n">
+      <c r="H51" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="21" t="n">
+      <c r="I51" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="15">
@@ -5283,7 +10631,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -5297,13 +10645,13 @@
       <c r="F52" s="12" t="n">
         <v>0.0256</v>
       </c>
-      <c r="G52" s="20" t="n">
+      <c r="G52" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H52" s="20" t="n">
+      <c r="H52" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="21" t="n">
+      <c r="I52" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="15">
@@ -5322,7 +10670,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -5336,13 +10684,13 @@
       <c r="F53" s="12" t="n">
         <v>0.8843</v>
       </c>
-      <c r="G53" s="20" t="n">
+      <c r="G53" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H53" s="20" t="n">
+      <c r="H53" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I53" s="21" t="n">
+      <c r="I53" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J53" s="15">
@@ -5361,7 +10709,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -5375,13 +10723,13 @@
       <c r="F54" s="12" t="n">
         <v>1.3038</v>
       </c>
-      <c r="G54" s="20" t="n">
+      <c r="G54" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H54" s="20" t="n">
+      <c r="H54" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I54" s="21" t="n">
+      <c r="I54" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J54" s="15">
@@ -5400,7 +10748,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -5414,13 +10762,13 @@
       <c r="F55" s="12" t="n">
         <v>22.8375</v>
       </c>
-      <c r="G55" s="20" t="n">
+      <c r="G55" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H55" s="20" t="n">
+      <c r="H55" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I55" s="21" t="n">
+      <c r="I55" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J55" s="15">
@@ -5439,7 +10787,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -5453,13 +10801,13 @@
       <c r="F56" s="12" t="n">
         <v>0.1167</v>
       </c>
-      <c r="G56" s="20" t="n">
+      <c r="G56" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H56" s="20" t="n">
+      <c r="H56" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="21" t="n">
+      <c r="I56" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="15">
@@ -5478,7 +10826,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -5492,13 +10840,13 @@
       <c r="F57" s="12" t="n">
         <v>13.151</v>
       </c>
-      <c r="G57" s="20" t="n">
+      <c r="G57" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H57" s="20" t="n">
+      <c r="H57" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="21" t="n">
+      <c r="I57" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="15">
@@ -5517,7 +10865,7 @@
           <t>CVT</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -5531,13 +10879,13 @@
       <c r="F58" s="12" t="n">
         <v>0.7305</v>
       </c>
-      <c r="G58" s="20" t="n">
+      <c r="G58" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H58" s="20" t="n">
+      <c r="H58" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="21" t="n">
+      <c r="I58" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J58" s="15">
@@ -5556,7 +10904,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -5570,13 +10918,13 @@
       <c r="F59" s="12" t="n">
         <v>6.706</v>
       </c>
-      <c r="G59" s="20" t="n">
+      <c r="G59" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H59" s="20" t="n">
+      <c r="H59" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="21" t="n">
+      <c r="I59" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="15">
@@ -5595,7 +10943,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -5609,13 +10957,13 @@
       <c r="F60" s="12" t="n">
         <v>1.0596</v>
       </c>
-      <c r="G60" s="20" t="n">
+      <c r="G60" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H60" s="20" t="n">
+      <c r="H60" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="21" t="n">
+      <c r="I60" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="15">
@@ -5634,7 +10982,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -5648,13 +10996,13 @@
       <c r="F61" s="12" t="n">
         <v>0.0251</v>
       </c>
-      <c r="G61" s="20" t="n">
+      <c r="G61" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H61" s="20" t="n">
+      <c r="H61" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="21" t="n">
+      <c r="I61" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="15">
@@ -5673,7 +11021,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -5687,13 +11035,13 @@
       <c r="F62" s="12" t="n">
         <v>0.8908</v>
       </c>
-      <c r="G62" s="20" t="n">
+      <c r="G62" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H62" s="20" t="n">
+      <c r="H62" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="21" t="n">
+      <c r="I62" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J62" s="15">
@@ -5712,7 +11060,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -5726,13 +11074,13 @@
       <c r="F63" s="12" t="n">
         <v>1.2887</v>
       </c>
-      <c r="G63" s="20" t="n">
+      <c r="G63" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H63" s="20" t="n">
+      <c r="H63" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="21" t="n">
+      <c r="I63" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J63" s="15">
@@ -5751,7 +11099,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -5765,13 +11113,13 @@
       <c r="F64" s="12" t="n">
         <v>22.7857</v>
       </c>
-      <c r="G64" s="20" t="n">
+      <c r="G64" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H64" s="20" t="n">
+      <c r="H64" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="21" t="n">
+      <c r="I64" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J64" s="15">
@@ -5790,7 +11138,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -5804,13 +11152,13 @@
       <c r="F65" s="12" t="n">
         <v>0.1205</v>
       </c>
-      <c r="G65" s="20" t="n">
+      <c r="G65" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H65" s="20" t="n">
+      <c r="H65" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="21" t="n">
+      <c r="I65" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="15">
@@ -5829,7 +11177,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -5843,13 +11191,13 @@
       <c r="F66" s="12" t="n">
         <v>13.0266</v>
       </c>
-      <c r="G66" s="20" t="n">
+      <c r="G66" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H66" s="20" t="n">
+      <c r="H66" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I66" s="21" t="n">
+      <c r="I66" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="15">
@@ -5868,7 +11216,7 @@
           <t>DTCWT</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -5882,13 +11230,13 @@
       <c r="F67" s="12" t="n">
         <v>0.7386</v>
       </c>
-      <c r="G67" s="20" t="n">
+      <c r="G67" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H67" s="20" t="n">
+      <c r="H67" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="21" t="n">
+      <c r="I67" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J67" s="15">
@@ -5907,7 +11255,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -5921,13 +11269,13 @@
       <c r="F68" s="12" t="n">
         <v>6.7002</v>
       </c>
-      <c r="G68" s="20" t="n">
+      <c r="G68" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H68" s="20" t="n">
+      <c r="H68" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="21" t="n">
+      <c r="I68" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J68" s="15">
@@ -5946,7 +11294,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -5960,13 +11308,13 @@
       <c r="F69" s="12" t="n">
         <v>1.0586</v>
       </c>
-      <c r="G69" s="20" t="n">
+      <c r="G69" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H69" s="20" t="n">
+      <c r="H69" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="21" t="n">
+      <c r="I69" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J69" s="15">
@@ -5985,7 +11333,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C70" s="18" t="inlineStr">
+      <c r="C70" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -5999,13 +11347,13 @@
       <c r="F70" s="12" t="n">
         <v>0.027</v>
       </c>
-      <c r="G70" s="20" t="n">
+      <c r="G70" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H70" s="20" t="n">
+      <c r="H70" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I70" s="21" t="n">
+      <c r="I70" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="15">
@@ -6024,7 +11372,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -6038,13 +11386,13 @@
       <c r="F71" s="12" t="n">
         <v>0.8809</v>
       </c>
-      <c r="G71" s="20" t="n">
+      <c r="G71" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H71" s="20" t="n">
+      <c r="H71" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="21" t="n">
+      <c r="I71" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J71" s="15">
@@ -6063,7 +11411,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -6077,13 +11425,13 @@
       <c r="F72" s="12" t="n">
         <v>1.2846</v>
       </c>
-      <c r="G72" s="20" t="n">
+      <c r="G72" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H72" s="20" t="n">
+      <c r="H72" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="21" t="n">
+      <c r="I72" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J72" s="15">
@@ -6102,7 +11450,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
+      <c r="C73" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -6116,13 +11464,13 @@
       <c r="F73" s="12" t="n">
         <v>22.7767</v>
       </c>
-      <c r="G73" s="20" t="n">
+      <c r="G73" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H73" s="20" t="n">
+      <c r="H73" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="21" t="n">
+      <c r="I73" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J73" s="15">
@@ -6141,7 +11489,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -6155,13 +11503,13 @@
       <c r="F74" s="12" t="n">
         <v>0.1199</v>
       </c>
-      <c r="G74" s="20" t="n">
+      <c r="G74" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H74" s="20" t="n">
+      <c r="H74" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="21" t="n">
+      <c r="I74" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="15">
@@ -6180,7 +11528,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -6194,13 +11542,13 @@
       <c r="F75" s="12" t="n">
         <v>13.9341</v>
       </c>
-      <c r="G75" s="20" t="n">
+      <c r="G75" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H75" s="20" t="n">
+      <c r="H75" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="21" t="n">
+      <c r="I75" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="15">
@@ -6219,7 +11567,7 @@
           <t>DWT</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C76" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -6233,13 +11581,13 @@
       <c r="F76" s="12" t="n">
         <v>0.7163</v>
       </c>
-      <c r="G76" s="20" t="n">
+      <c r="G76" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H76" s="20" t="n">
+      <c r="H76" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I76" s="21" t="n">
+      <c r="I76" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J76" s="15">
@@ -6258,7 +11606,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C77" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -6272,13 +11620,13 @@
       <c r="F77" s="12" t="n">
         <v>6.835</v>
       </c>
-      <c r="G77" s="20" t="n">
+      <c r="G77" s="22" t="n">
         <v>0.0758514404296875</v>
       </c>
-      <c r="H77" s="20" t="n">
+      <c r="H77" s="22" t="n">
         <v>0.0759</v>
       </c>
-      <c r="I77" s="21" t="n">
+      <c r="I77" s="23" t="n">
         <v>0.46</v>
       </c>
       <c r="J77" s="15">
@@ -6297,7 +11645,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C78" s="18" t="inlineStr">
+      <c r="C78" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -6311,13 +11659,13 @@
       <c r="F78" s="12" t="n">
         <v>1.0792</v>
       </c>
-      <c r="G78" s="20" t="n">
+      <c r="G78" s="22" t="n">
         <v>0.0758514404296875</v>
       </c>
-      <c r="H78" s="20" t="n">
+      <c r="H78" s="22" t="n">
         <v>0.0759</v>
       </c>
-      <c r="I78" s="21" t="n">
+      <c r="I78" s="23" t="n">
         <v>0.46</v>
       </c>
       <c r="J78" s="15">
@@ -6336,7 +11684,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C79" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -6350,13 +11698,13 @@
       <c r="F79" s="12" t="n">
         <v>0.0248</v>
       </c>
-      <c r="G79" s="20" t="n">
+      <c r="G79" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H79" s="20" t="n">
+      <c r="H79" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="21" t="n">
+      <c r="I79" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="15">
@@ -6375,7 +11723,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C80" s="18" t="inlineStr">
+      <c r="C80" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -6389,13 +11737,13 @@
       <c r="F80" s="12" t="n">
         <v>1.0717</v>
       </c>
-      <c r="G80" s="20" t="n">
+      <c r="G80" s="22" t="n">
         <v>3.62396240234375e-05</v>
       </c>
-      <c r="H80" s="20" t="n">
+      <c r="H80" s="22" t="n">
         <v>0.0002</v>
       </c>
-      <c r="I80" s="21" t="n">
+      <c r="I80" s="23" t="n">
         <v>-0.93</v>
       </c>
       <c r="J80" s="15">
@@ -6414,7 +11762,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C81" s="18" t="inlineStr">
+      <c r="C81" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -6428,13 +11776,13 @@
       <c r="F81" s="12" t="n">
         <v>2.1183</v>
       </c>
-      <c r="G81" s="20" t="n">
+      <c r="G81" s="22" t="n">
         <v>1.9073486328125e-05</v>
       </c>
-      <c r="H81" s="20" t="n">
+      <c r="H81" s="22" t="n">
         <v>0.0001</v>
       </c>
-      <c r="I81" s="21" t="n">
+      <c r="I81" s="23" t="n">
         <v>-0.95</v>
       </c>
       <c r="J81" s="15">
@@ -6453,7 +11801,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C82" s="18" t="inlineStr">
+      <c r="C82" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -6467,13 +11815,13 @@
       <c r="F82" s="12" t="n">
         <v>20.2687</v>
       </c>
-      <c r="G82" s="20" t="n">
+      <c r="G82" s="22" t="n">
         <v>0.0007076263427734</v>
       </c>
-      <c r="H82" s="20" t="n">
+      <c r="H82" s="22" t="n">
         <v>0.0014</v>
       </c>
-      <c r="I82" s="21" t="n">
+      <c r="I82" s="23" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="J82" s="15">
@@ -6492,7 +11840,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C83" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -6506,13 +11854,13 @@
       <c r="F83" s="12" t="n">
         <v>0.1548</v>
       </c>
-      <c r="G83" s="20" t="n">
+      <c r="G83" s="22" t="n">
         <v>0.082550048828125</v>
       </c>
-      <c r="H83" s="20" t="n">
+      <c r="H83" s="22" t="n">
         <v>0.1651</v>
       </c>
-      <c r="I83" s="21" t="n">
+      <c r="I83" s="23" t="n">
         <v>-0.45</v>
       </c>
       <c r="J83" s="15">
@@ -6531,7 +11879,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C84" s="18" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -6545,13 +11893,13 @@
       <c r="F84" s="12" t="n">
         <v>13.04</v>
       </c>
-      <c r="G84" s="20" t="n">
+      <c r="G84" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H84" s="20" t="n">
+      <c r="H84" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="21" t="n">
+      <c r="I84" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J84" s="15">
@@ -6570,7 +11918,7 @@
           <t>LP</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr">
+      <c r="C85" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -6584,13 +11932,13 @@
       <c r="F85" s="12" t="n">
         <v>0.7208</v>
       </c>
-      <c r="G85" s="20" t="n">
+      <c r="G85" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H85" s="20" t="n">
+      <c r="H85" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I85" s="21" t="n">
+      <c r="I85" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J85" s="15">
@@ -6609,7 +11957,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C86" s="18" t="inlineStr">
+      <c r="C86" s="20" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
@@ -6623,13 +11971,13 @@
       <c r="F86" s="12" t="n">
         <v>6.8285</v>
       </c>
-      <c r="G86" s="20" t="n">
+      <c r="G86" s="22" t="n">
         <v>0.0008506774902343</v>
       </c>
-      <c r="H86" s="20" t="n">
+      <c r="H86" s="22" t="n">
         <v>0.0026</v>
       </c>
-      <c r="I86" s="21" t="n">
+      <c r="I86" s="23" t="n">
         <v>0.8</v>
       </c>
       <c r="J86" s="15">
@@ -6648,7 +11996,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C87" s="18" t="inlineStr">
+      <c r="C87" s="20" t="inlineStr">
         <is>
           <t>FE</t>
         </is>
@@ -6662,13 +12010,13 @@
       <c r="F87" s="12" t="n">
         <v>1.079</v>
       </c>
-      <c r="G87" s="20" t="n">
+      <c r="G87" s="22" t="n">
         <v>0.0005855560302734</v>
       </c>
-      <c r="H87" s="20" t="n">
+      <c r="H87" s="22" t="n">
         <v>0.0018</v>
       </c>
-      <c r="I87" s="21" t="n">
+      <c r="I87" s="23" t="n">
         <v>0.82</v>
       </c>
       <c r="J87" s="15">
@@ -6687,7 +12035,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C88" s="18" t="inlineStr">
+      <c r="C88" s="20" t="inlineStr">
         <is>
           <t>MG</t>
         </is>
@@ -6701,13 +12049,13 @@
       <c r="F88" s="12" t="n">
         <v>0.0269</v>
       </c>
-      <c r="G88" s="20" t="n">
+      <c r="G88" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H88" s="20" t="n">
+      <c r="H88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I88" s="21" t="n">
+      <c r="I88" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J88" s="15">
@@ -6726,7 +12074,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
+      <c r="C89" s="20" t="inlineStr">
         <is>
           <t>MI_ir</t>
         </is>
@@ -6740,13 +12088,13 @@
       <c r="F89" s="12" t="n">
         <v>0.8807</v>
       </c>
-      <c r="G89" s="20" t="n">
+      <c r="G89" s="22" t="n">
         <v>4.76837158203125e-05</v>
       </c>
-      <c r="H89" s="20" t="n">
+      <c r="H89" s="22" t="n">
         <v>0.0002</v>
       </c>
-      <c r="I89" s="21" t="n">
+      <c r="I89" s="23" t="n">
         <v>-0.92</v>
       </c>
       <c r="J89" s="15">
@@ -6765,7 +12113,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C90" s="18" t="inlineStr">
+      <c r="C90" s="20" t="inlineStr">
         <is>
           <t>MI_vis</t>
         </is>
@@ -6779,13 +12127,13 @@
       <c r="F90" s="12" t="n">
         <v>1.1698</v>
       </c>
-      <c r="G90" s="20" t="n">
+      <c r="G90" s="22" t="n">
         <v>0.0004825592041015</v>
       </c>
-      <c r="H90" s="20" t="n">
+      <c r="H90" s="22" t="n">
         <v>0.001</v>
       </c>
-      <c r="I90" s="21" t="n">
+      <c r="I90" s="23" t="n">
         <v>-0.83</v>
       </c>
       <c r="J90" s="15">
@@ -6804,7 +12152,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C91" s="18" t="inlineStr">
+      <c r="C91" s="20" t="inlineStr">
         <is>
           <t>PSNR</t>
         </is>
@@ -6818,13 +12166,13 @@
       <c r="F91" s="12" t="n">
         <v>21.9655</v>
       </c>
-      <c r="G91" s="20" t="n">
+      <c r="G91" s="22" t="n">
         <v>0.0003223419189453</v>
       </c>
-      <c r="H91" s="20" t="n">
+      <c r="H91" s="22" t="n">
         <v>0.001</v>
       </c>
-      <c r="I91" s="21" t="n">
+      <c r="I91" s="23" t="n">
         <v>-0.85</v>
       </c>
       <c r="J91" s="15">
@@ -6843,7 +12191,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C92" s="18" t="inlineStr">
+      <c r="C92" s="20" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
@@ -6857,13 +12205,13 @@
       <c r="F92" s="12" t="n">
         <v>0.1304</v>
       </c>
-      <c r="G92" s="20" t="n">
+      <c r="G92" s="22" t="n">
         <v>0.0016899108886718</v>
       </c>
-      <c r="H92" s="20" t="n">
+      <c r="H92" s="22" t="n">
         <v>0.0051</v>
       </c>
-      <c r="I92" s="21" t="n">
+      <c r="I92" s="23" t="n">
         <v>0.76</v>
       </c>
       <c r="J92" s="15">
@@ -6882,7 +12230,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C93" s="18" t="inlineStr">
+      <c r="C93" s="20" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
@@ -6896,13 +12244,13 @@
       <c r="F93" s="12" t="n">
         <v>13.3376</v>
       </c>
-      <c r="G93" s="20" t="n">
+      <c r="G93" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H93" s="20" t="n">
+      <c r="H93" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I93" s="21" t="n">
+      <c r="I93" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J93" s="15">
@@ -6921,7 +12269,7 @@
           <t>RP</t>
         </is>
       </c>
-      <c r="C94" s="18" t="inlineStr">
+      <c r="C94" s="20" t="inlineStr">
         <is>
           <t>SSIM</t>
         </is>
@@ -6935,13 +12283,13 @@
       <c r="F94" s="12" t="n">
         <v>0.7212</v>
       </c>
-      <c r="G94" s="20" t="n">
+      <c r="G94" s="22" t="n">
         <v>1.9073486328125e-06</v>
       </c>
-      <c r="H94" s="20" t="n">
+      <c r="H94" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I94" s="21" t="n">
+      <c r="I94" s="23" t="n">
         <v>-1</v>
       </c>
       <c r="J94" s="15">
@@ -6954,7 +12302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7053,34 +12401,34 @@
           <t>Pirámide de Laplace (LP)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="19" t="n">
+      <c r="C5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="19" t="n">
+      <c r="F5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="24">
         <f>AVERAGE(B5:J5)</f>
         <v/>
       </c>
@@ -7091,34 +12439,34 @@
           <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="23" t="n">
+      <c r="B6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="23" t="n">
+      <c r="D6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="24">
         <f>AVERAGE(B6:J6)</f>
         <v/>
       </c>
@@ -7129,34 +12477,34 @@
           <t>Dual-Tree Complex Wavelet (DTCWT)</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="19" t="n">
+      <c r="I7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="24">
         <f>AVERAGE(B7:J7)</f>
         <v/>
       </c>
@@ -7167,34 +12515,34 @@
           <t>Top-Hat clásico</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="19" t="n">
+      <c r="E8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="19" t="n">
+      <c r="H8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="24">
         <f>AVERAGE(B8:J8)</f>
         <v/>
       </c>
@@ -7205,34 +12553,34 @@
           <t>Ratio of low-pass Pyramid (RP)</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="24">
         <f>AVERAGE(B9:J9)</f>
         <v/>
       </c>
@@ -7243,34 +12591,34 @@
           <t>Curvelet (CVT)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="22">
+      <c r="J10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="24">
         <f>AVERAGE(B10:J10)</f>
         <v/>
       </c>
@@ -7281,276 +12629,36 @@
           <t>Wavelet discreta (DWT)</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="24">
         <f>AVERAGE(B11:J11)</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Evaluación orientada a tarea — detección de peatones en LLVIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>YOLOv8n reentrenado 40 épocas por método (subconjunto 2.000 train / 500 val, misma config y semilla). Etiquetas idénticas para todos: la diferencia de mAP aísla el efecto del método de fusión. En negrita el mejor por columna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Entrada del detector</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>mAP@0,5 ↑</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>mAP@0,5:0,95 ↑</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Precisión ↑</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Recall ↑</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>VIS (solo)</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0.4512</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0.8033</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.7506</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>IR (solo)</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>0.6627</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.8935999999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Pirámide de Laplace (LP)</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>0.9487</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>0.6509</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>0.9426</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.8788</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Ratio of low-pass Pyramid (RP)</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>0.9261</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>0.5381</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>0.9404</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.8663999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Wavelet discreta (DWT)</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>0.9457</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0.6141</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>0.9735</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.8532</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Dual-Tree Complex Wavelet (DTCWT)</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n">
-        <v>0.9479</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0.6329</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>0.9492</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.8577</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Curvelet (CVT)</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>0.9414</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>0.6388</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.8683</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Top-Hat clásico</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>0.9383</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>0.6093</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>0.9571</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.8662</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Propuesta Novedosa (r=25, m=0,30)</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>0.9129</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <v>0.6165</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>0.9101</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0.8058</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Lectura: toda fusión supera al visible solo (+0,11 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones (banda 0,913–0,949) la propuesta queda en el extremo inferior (0,913). El realce que premian las métricas de actividad no mejora la detección: ambos criterios deben reportarse por separado (H3 no sostenida).</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -8117,7 +8117,7 @@
       <c r="D5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F5" s="20" t="n">
@@ -8150,7 +8150,7 @@
       <c r="D6" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F6" s="20" t="n">
@@ -8183,7 +8183,7 @@
       <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9104</v>
       </c>
       <c r="F7" s="20" t="n">
@@ -8216,7 +8216,7 @@
       <c r="D8" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F8" s="20" t="n">
@@ -8249,7 +8249,7 @@
       <c r="D9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F9" s="21" t="n">
@@ -8282,7 +8282,7 @@
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F10" s="20" t="n">
@@ -8315,7 +8315,7 @@
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F11" s="20" t="n">
@@ -8348,7 +8348,7 @@
       <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F12" s="20" t="n">
@@ -8381,7 +8381,7 @@
       <c r="D13" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F13" s="20" t="n">
@@ -8414,7 +8414,7 @@
       <c r="D14" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" s="20" t="n">
@@ -8447,7 +8447,7 @@
       <c r="D15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F15" s="20" t="n">
@@ -8480,7 +8480,7 @@
       <c r="D16" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F16" s="20" t="n">
@@ -8513,7 +8513,7 @@
       <c r="D17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F17" s="20" t="n">
@@ -8546,7 +8546,7 @@
       <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="20" t="n">
@@ -8579,7 +8579,7 @@
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F19" s="20" t="n">
@@ -8612,7 +8612,7 @@
       <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="20" t="n">
@@ -8645,7 +8645,7 @@
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F21" s="20" t="n">
@@ -8678,7 +8678,7 @@
       <c r="D22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F22" s="20" t="n">
@@ -8711,7 +8711,7 @@
       <c r="D23" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F23" s="20" t="n">
@@ -8744,7 +8744,7 @@
       <c r="D24" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F24" s="20" t="n">
@@ -8777,7 +8777,7 @@
       <c r="D25" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F25" s="20" t="n">
@@ -8810,7 +8810,7 @@
       <c r="D26" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F26" s="20" t="n">
@@ -8843,7 +8843,7 @@
       <c r="D27" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F27" s="20" t="n">
@@ -8876,7 +8876,7 @@
       <c r="D28" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F28" s="20" t="n">
@@ -8909,7 +8909,7 @@
       <c r="D29" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F29" s="20" t="n">
@@ -8946,7 +8946,7 @@
       <c r="D30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F30" s="21" t="n">
@@ -8979,7 +8979,7 @@
       <c r="D31" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F31" s="20" t="n">
@@ -9012,7 +9012,7 @@
       <c r="D32" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F32" s="20" t="n">
@@ -9045,7 +9045,7 @@
       <c r="D33" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F33" s="20" t="n">
@@ -9078,7 +9078,7 @@
       <c r="D34" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F34" s="20" t="n">
@@ -9111,7 +9111,7 @@
       <c r="D35" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F35" s="20" t="n">
@@ -9144,7 +9144,7 @@
       <c r="D36" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F36" s="20" t="n">
@@ -9177,7 +9177,7 @@
       <c r="D37" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F37" s="20" t="n">
@@ -9210,7 +9210,7 @@
       <c r="D38" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F38" s="20" t="n">
@@ -9243,7 +9243,7 @@
       <c r="D39" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F39" s="20" t="n">
@@ -9276,7 +9276,7 @@
       <c r="D40" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F40" s="20" t="n">
@@ -9309,7 +9309,7 @@
       <c r="D41" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F41" s="20" t="n">
@@ -9342,7 +9342,7 @@
       <c r="D42" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F42" s="20" t="n">
@@ -9375,7 +9375,7 @@
       <c r="D43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F43" s="20" t="n">
@@ -9408,7 +9408,7 @@
       <c r="D44" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F44" s="20" t="n">
@@ -9441,7 +9441,7 @@
       <c r="D45" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F45" s="20" t="n">
@@ -9474,7 +9474,7 @@
       <c r="D46" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F46" s="20" t="n">
@@ -9507,7 +9507,7 @@
       <c r="D47" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F47" s="20" t="n">
@@ -9540,7 +9540,7 @@
       <c r="D48" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F48" s="20" t="n">
@@ -9573,7 +9573,7 @@
       <c r="D49" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F49" s="20" t="n">
@@ -9606,7 +9606,7 @@
       <c r="D50" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F50" s="20" t="n">
@@ -9639,7 +9639,7 @@
       <c r="D51" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F51" s="20" t="n">
@@ -9672,7 +9672,7 @@
       <c r="D52" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F52" s="20" t="n">
@@ -9705,7 +9705,7 @@
       <c r="D53" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F53" s="20" t="n">
@@ -9738,7 +9738,7 @@
       <c r="D54" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F54" s="20" t="n">
@@ -9775,7 +9775,7 @@
       <c r="D55" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F55" s="20" t="n">
@@ -9808,7 +9808,7 @@
       <c r="D56" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="17" t="n">
+      <c r="E56" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F56" s="21" t="n">
@@ -9841,7 +9841,7 @@
       <c r="D57" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F57" s="20" t="n">
@@ -9874,7 +9874,7 @@
       <c r="D58" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F58" s="20" t="n">
@@ -9907,7 +9907,7 @@
       <c r="D59" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F59" s="20" t="n">
@@ -9940,7 +9940,7 @@
       <c r="D60" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E60" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F60" s="20" t="n">
@@ -9973,7 +9973,7 @@
       <c r="D61" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E61" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F61" s="20" t="n">
@@ -10006,7 +10006,7 @@
       <c r="D62" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E62" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F62" s="20" t="n">
@@ -10039,7 +10039,7 @@
       <c r="D63" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="16" t="n">
+      <c r="E63" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F63" s="20" t="n">
@@ -10072,7 +10072,7 @@
       <c r="D64" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="16" t="n">
+      <c r="E64" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F64" s="20" t="n">
@@ -10105,7 +10105,7 @@
       <c r="D65" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E65" s="16" t="n">
+      <c r="E65" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F65" s="20" t="n">
@@ -10138,7 +10138,7 @@
       <c r="D66" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="16" t="n">
+      <c r="E66" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F66" s="20" t="n">
@@ -10171,7 +10171,7 @@
       <c r="D67" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="16" t="n">
+      <c r="E67" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F67" s="20" t="n">
@@ -10204,7 +10204,7 @@
       <c r="D68" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="16" t="n">
+      <c r="E68" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F68" s="20" t="n">
@@ -10237,7 +10237,7 @@
       <c r="D69" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E69" s="16" t="n">
+      <c r="E69" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F69" s="20" t="n">
@@ -10270,7 +10270,7 @@
       <c r="D70" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F70" s="20" t="n">
@@ -10303,7 +10303,7 @@
       <c r="D71" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E71" s="16" t="n">
+      <c r="E71" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F71" s="20" t="n">
@@ -10336,7 +10336,7 @@
       <c r="D72" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F72" s="20" t="n">
@@ -10369,7 +10369,7 @@
       <c r="D73" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="16" t="n">
+      <c r="E73" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F73" s="20" t="n">
@@ -10402,7 +10402,7 @@
       <c r="D74" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E74" s="16" t="n">
+      <c r="E74" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F74" s="20" t="n">
@@ -10435,7 +10435,7 @@
       <c r="D75" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F75" s="20" t="n">
@@ -10468,7 +10468,7 @@
       <c r="D76" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="16" t="n">
+      <c r="E76" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F76" s="20" t="n">
@@ -10501,7 +10501,7 @@
       <c r="D77" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="16" t="n">
+      <c r="E77" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F77" s="20" t="n">
@@ -10534,7 +10534,7 @@
       <c r="D78" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="16" t="n">
+      <c r="E78" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F78" s="20" t="n">
@@ -10567,7 +10567,7 @@
       <c r="D79" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="16" t="n">
+      <c r="E79" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F79" s="20" t="n">
@@ -10604,7 +10604,7 @@
       <c r="D80" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E80" s="16" t="n">
+      <c r="E80" s="12" t="n">
         <v>1.5353</v>
       </c>
       <c r="F80" s="20" t="n">
@@ -10637,7 +10637,7 @@
       <c r="D81" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="17" t="n">
+      <c r="E81" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F81" s="21" t="n">
@@ -10670,7 +10670,7 @@
       <c r="D82" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="16" t="n">
+      <c r="E82" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F82" s="20" t="n">
@@ -10703,7 +10703,7 @@
       <c r="D83" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="16" t="n">
+      <c r="E83" s="12" t="n">
         <v>1.3634</v>
       </c>
       <c r="F83" s="20" t="n">
@@ -10736,7 +10736,7 @@
       <c r="D84" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="16" t="n">
+      <c r="E84" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F84" s="20" t="n">
@@ -10769,7 +10769,7 @@
       <c r="D85" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E85" s="16" t="n">
+      <c r="E85" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F85" s="20" t="n">
@@ -10802,7 +10802,7 @@
       <c r="D86" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="16" t="n">
+      <c r="E86" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F86" s="20" t="n">
@@ -10835,7 +10835,7 @@
       <c r="D87" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E87" s="16" t="n">
+      <c r="E87" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F87" s="20" t="n">
@@ -10868,7 +10868,7 @@
       <c r="D88" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="16" t="n">
+      <c r="E88" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F88" s="20" t="n">
@@ -10901,7 +10901,7 @@
       <c r="D89" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E89" s="16" t="n">
+      <c r="E89" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F89" s="20" t="n">
@@ -10934,7 +10934,7 @@
       <c r="D90" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E90" s="16" t="n">
+      <c r="E90" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F90" s="20" t="n">
@@ -10967,7 +10967,7 @@
       <c r="D91" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="16" t="n">
+      <c r="E91" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F91" s="20" t="n">
@@ -11000,7 +11000,7 @@
       <c r="D92" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="16" t="n">
+      <c r="E92" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F92" s="20" t="n">
@@ -11033,7 +11033,7 @@
       <c r="D93" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="16" t="n">
+      <c r="E93" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F93" s="20" t="n">
@@ -11066,7 +11066,7 @@
       <c r="D94" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E94" s="16" t="n">
+      <c r="E94" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F94" s="20" t="n">
@@ -11099,7 +11099,7 @@
       <c r="D95" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="16" t="n">
+      <c r="E95" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F95" s="20" t="n">
@@ -11132,7 +11132,7 @@
       <c r="D96" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="16" t="n">
+      <c r="E96" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F96" s="20" t="n">
@@ -11165,7 +11165,7 @@
       <c r="D97" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E97" s="16" t="n">
+      <c r="E97" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F97" s="20" t="n">
@@ -11198,7 +11198,7 @@
       <c r="D98" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="16" t="n">
+      <c r="E98" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F98" s="20" t="n">
@@ -11231,7 +11231,7 @@
       <c r="D99" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E99" s="16" t="n">
+      <c r="E99" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F99" s="20" t="n">
@@ -11264,7 +11264,7 @@
       <c r="D100" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E100" s="16" t="n">
+      <c r="E100" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F100" s="20" t="n">
@@ -11297,7 +11297,7 @@
       <c r="D101" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E101" s="16" t="n">
+      <c r="E101" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F101" s="20" t="n">
@@ -11330,7 +11330,7 @@
       <c r="D102" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="16" t="n">
+      <c r="E102" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F102" s="20" t="n">
@@ -11363,7 +11363,7 @@
       <c r="D103" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="16" t="n">
+      <c r="E103" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F103" s="20" t="n">
@@ -11396,7 +11396,7 @@
       <c r="D104" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="16" t="n">
+      <c r="E104" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F104" s="20" t="n">
@@ -11433,7 +11433,7 @@
       <c r="D105" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E105" s="12" t="n">
         <v>0.9476</v>
       </c>
       <c r="F105" s="20" t="n">
@@ -11466,7 +11466,7 @@
       <c r="D106" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E106" s="17" t="n">
+      <c r="E106" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F106" s="21" t="n">
@@ -11499,7 +11499,7 @@
       <c r="D107" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="16" t="n">
+      <c r="E107" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F107" s="20" t="n">
@@ -11532,7 +11532,7 @@
       <c r="D108" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="16" t="n">
+      <c r="E108" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F108" s="20" t="n">
@@ -11565,7 +11565,7 @@
       <c r="D109" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E109" s="16" t="n">
+      <c r="E109" s="12" t="n">
         <v>0.4554</v>
       </c>
       <c r="F109" s="20" t="n">
@@ -11598,7 +11598,7 @@
       <c r="D110" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E110" s="16" t="n">
+      <c r="E110" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F110" s="20" t="n">
@@ -11631,7 +11631,7 @@
       <c r="D111" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="16" t="n">
+      <c r="E111" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F111" s="20" t="n">
@@ -11664,7 +11664,7 @@
       <c r="D112" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="16" t="n">
+      <c r="E112" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F112" s="20" t="n">
@@ -11697,7 +11697,7 @@
       <c r="D113" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="16" t="n">
+      <c r="E113" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F113" s="20" t="n">
@@ -11730,7 +11730,7 @@
       <c r="D114" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E114" s="16" t="n">
+      <c r="E114" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F114" s="20" t="n">
@@ -11763,7 +11763,7 @@
       <c r="D115" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E115" s="16" t="n">
+      <c r="E115" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F115" s="20" t="n">
@@ -11796,7 +11796,7 @@
       <c r="D116" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="16" t="n">
+      <c r="E116" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F116" s="20" t="n">
@@ -11829,7 +11829,7 @@
       <c r="D117" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="16" t="n">
+      <c r="E117" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F117" s="20" t="n">
@@ -11862,7 +11862,7 @@
       <c r="D118" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="16" t="n">
+      <c r="E118" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F118" s="20" t="n">
@@ -11895,7 +11895,7 @@
       <c r="D119" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E119" s="16" t="n">
+      <c r="E119" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F119" s="20" t="n">
@@ -11928,7 +11928,7 @@
       <c r="D120" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="E120" s="16" t="n">
+      <c r="E120" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F120" s="20" t="n">
@@ -11961,7 +11961,7 @@
       <c r="D121" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E121" s="16" t="n">
+      <c r="E121" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F121" s="20" t="n">
@@ -11994,7 +11994,7 @@
       <c r="D122" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E122" s="16" t="n">
+      <c r="E122" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F122" s="20" t="n">
@@ -12027,7 +12027,7 @@
       <c r="D123" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E123" s="16" t="n">
+      <c r="E123" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F123" s="20" t="n">
@@ -12060,7 +12060,7 @@
       <c r="D124" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E124" s="16" t="n">
+      <c r="E124" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F124" s="20" t="n">
@@ -12093,7 +12093,7 @@
       <c r="D125" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E125" s="16" t="n">
+      <c r="E125" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F125" s="20" t="n">
@@ -12126,7 +12126,7 @@
       <c r="D126" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E126" s="16" t="n">
+      <c r="E126" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F126" s="20" t="n">
@@ -12159,7 +12159,7 @@
       <c r="D127" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E127" s="16" t="n">
+      <c r="E127" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F127" s="20" t="n">
@@ -12192,7 +12192,7 @@
       <c r="D128" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="16" t="n">
+      <c r="E128" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F128" s="20" t="n">
@@ -12225,7 +12225,7 @@
       <c r="D129" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E129" s="16" t="n">
+      <c r="E129" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F129" s="20" t="n">
@@ -12262,7 +12262,7 @@
       <c r="D130" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E130" s="17" t="n">
+      <c r="E130" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F130" s="21" t="n">
@@ -12295,7 +12295,7 @@
       <c r="D131" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="16" t="n">
+      <c r="E131" s="12" t="n">
         <v>0.3775</v>
       </c>
       <c r="F131" s="20" t="n">
@@ -12328,7 +12328,7 @@
       <c r="D132" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E132" s="16" t="n">
+      <c r="E132" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F132" s="20" t="n">
@@ -12361,7 +12361,7 @@
       <c r="D133" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E133" s="16" t="n">
+      <c r="E133" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F133" s="20" t="n">
@@ -12394,7 +12394,7 @@
       <c r="D134" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E134" s="16" t="n">
+      <c r="E134" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F134" s="20" t="n">
@@ -12427,7 +12427,7 @@
       <c r="D135" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E135" s="16" t="n">
+      <c r="E135" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F135" s="20" t="n">
@@ -12460,7 +12460,7 @@
       <c r="D136" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="16" t="n">
+      <c r="E136" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F136" s="20" t="n">
@@ -12493,7 +12493,7 @@
       <c r="D137" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E137" s="16" t="n">
+      <c r="E137" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F137" s="20" t="n">
@@ -12526,7 +12526,7 @@
       <c r="D138" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E138" s="16" t="n">
+      <c r="E138" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F138" s="20" t="n">
@@ -12559,7 +12559,7 @@
       <c r="D139" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="16" t="n">
+      <c r="E139" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F139" s="20" t="n">
@@ -12592,7 +12592,7 @@
       <c r="D140" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="16" t="n">
+      <c r="E140" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F140" s="20" t="n">
@@ -12625,7 +12625,7 @@
       <c r="D141" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E141" s="16" t="n">
+      <c r="E141" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F141" s="20" t="n">
@@ -12658,7 +12658,7 @@
       <c r="D142" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E142" s="16" t="n">
+      <c r="E142" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F142" s="20" t="n">
@@ -12691,7 +12691,7 @@
       <c r="D143" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E143" s="16" t="n">
+      <c r="E143" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F143" s="20" t="n">
@@ -12724,7 +12724,7 @@
       <c r="D144" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E144" s="16" t="n">
+      <c r="E144" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F144" s="20" t="n">
@@ -12757,7 +12757,7 @@
       <c r="D145" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E145" s="16" t="n">
+      <c r="E145" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F145" s="20" t="n">
@@ -12790,7 +12790,7 @@
       <c r="D146" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E146" s="16" t="n">
+      <c r="E146" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F146" s="20" t="n">
@@ -12823,7 +12823,7 @@
       <c r="D147" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="16" t="n">
+      <c r="E147" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F147" s="20" t="n">
@@ -12856,7 +12856,7 @@
       <c r="D148" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="16" t="n">
+      <c r="E148" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F148" s="20" t="n">
@@ -12889,7 +12889,7 @@
       <c r="D149" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="16" t="n">
+      <c r="E149" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F149" s="20" t="n">
@@ -12922,7 +12922,7 @@
       <c r="D150" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E150" s="16" t="n">
+      <c r="E150" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F150" s="20" t="n">
@@ -12955,7 +12955,7 @@
       <c r="D151" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E151" s="16" t="n">
+      <c r="E151" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F151" s="20" t="n">
@@ -12988,7 +12988,7 @@
       <c r="D152" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E152" s="16" t="n">
+      <c r="E152" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F152" s="20" t="n">
@@ -13021,7 +13021,7 @@
       <c r="D153" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="16" t="n">
+      <c r="E153" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F153" s="20" t="n">
@@ -13054,7 +13054,7 @@
       <c r="D154" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E154" s="16" t="n">
+      <c r="E154" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F154" s="20" t="n">
@@ -13091,7 +13091,7 @@
       <c r="D155" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E155" s="16" t="n">
+      <c r="E155" s="12" t="n">
         <v>1.0443</v>
       </c>
       <c r="F155" s="20" t="n">
@@ -13124,7 +13124,7 @@
       <c r="D156" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E156" s="17" t="n">
+      <c r="E156" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F156" s="21" t="n">
@@ -13157,7 +13157,7 @@
       <c r="D157" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E157" s="16" t="n">
+      <c r="E157" s="12" t="n">
         <v>1.008</v>
       </c>
       <c r="F157" s="20" t="n">
@@ -13190,7 +13190,7 @@
       <c r="D158" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E158" s="16" t="n">
+      <c r="E158" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F158" s="20" t="n">
@@ -13223,7 +13223,7 @@
       <c r="D159" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E159" s="16" t="n">
+      <c r="E159" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F159" s="20" t="n">
@@ -13256,7 +13256,7 @@
       <c r="D160" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E160" s="16" t="n">
+      <c r="E160" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F160" s="20" t="n">
@@ -13289,7 +13289,7 @@
       <c r="D161" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E161" s="16" t="n">
+      <c r="E161" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F161" s="20" t="n">
@@ -13322,7 +13322,7 @@
       <c r="D162" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E162" s="16" t="n">
+      <c r="E162" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F162" s="20" t="n">
@@ -13355,7 +13355,7 @@
       <c r="D163" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="16" t="n">
+      <c r="E163" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F163" s="20" t="n">
@@ -13388,7 +13388,7 @@
       <c r="D164" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E164" s="16" t="n">
+      <c r="E164" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F164" s="20" t="n">
@@ -13421,7 +13421,7 @@
       <c r="D165" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E165" s="16" t="n">
+      <c r="E165" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F165" s="20" t="n">
@@ -13454,7 +13454,7 @@
       <c r="D166" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E166" s="16" t="n">
+      <c r="E166" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F166" s="20" t="n">
@@ -13487,7 +13487,7 @@
       <c r="D167" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E167" s="16" t="n">
+      <c r="E167" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F167" s="20" t="n">
@@ -13520,7 +13520,7 @@
       <c r="D168" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E168" s="16" t="n">
+      <c r="E168" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F168" s="20" t="n">
@@ -13553,7 +13553,7 @@
       <c r="D169" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E169" s="16" t="n">
+      <c r="E169" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F169" s="20" t="n">
@@ -13586,7 +13586,7 @@
       <c r="D170" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E170" s="16" t="n">
+      <c r="E170" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F170" s="20" t="n">
@@ -13619,7 +13619,7 @@
       <c r="D171" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E171" s="16" t="n">
+      <c r="E171" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F171" s="20" t="n">
@@ -13652,7 +13652,7 @@
       <c r="D172" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E172" s="16" t="n">
+      <c r="E172" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F172" s="20" t="n">
@@ -13685,7 +13685,7 @@
       <c r="D173" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E173" s="16" t="n">
+      <c r="E173" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F173" s="20" t="n">
@@ -13718,7 +13718,7 @@
       <c r="D174" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E174" s="16" t="n">
+      <c r="E174" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F174" s="20" t="n">
@@ -13751,7 +13751,7 @@
       <c r="D175" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E175" s="16" t="n">
+      <c r="E175" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F175" s="20" t="n">
@@ -13784,7 +13784,7 @@
       <c r="D176" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E176" s="16" t="n">
+      <c r="E176" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F176" s="20" t="n">
@@ -13817,7 +13817,7 @@
       <c r="D177" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E177" s="16" t="n">
+      <c r="E177" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F177" s="20" t="n">
@@ -13850,7 +13850,7 @@
       <c r="D178" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E178" s="16" t="n">
+      <c r="E178" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F178" s="20" t="n">
@@ -13883,7 +13883,7 @@
       <c r="D179" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E179" s="16" t="n">
+      <c r="E179" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F179" s="20" t="n">
@@ -13920,7 +13920,7 @@
       <c r="D180" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E180" s="16" t="n">
+      <c r="E180" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F180" s="20" t="n">
@@ -13953,7 +13953,7 @@
       <c r="D181" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="E181" s="16" t="n">
+      <c r="E181" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F181" s="20" t="n">
@@ -13986,7 +13986,7 @@
       <c r="D182" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E182" s="16" t="n">
+      <c r="E182" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F182" s="20" t="n">
@@ -14019,7 +14019,7 @@
       <c r="D183" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E183" s="16" t="n">
+      <c r="E183" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F183" s="20" t="n">
@@ -14052,7 +14052,7 @@
       <c r="D184" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E184" s="17" t="n">
+      <c r="E184" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F184" s="21" t="n">
@@ -14085,7 +14085,7 @@
       <c r="D185" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E185" s="16" t="n">
+      <c r="E185" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F185" s="20" t="n">
@@ -14118,7 +14118,7 @@
       <c r="D186" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E186" s="16" t="n">
+      <c r="E186" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F186" s="20" t="n">
@@ -14151,7 +14151,7 @@
       <c r="D187" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E187" s="16" t="n">
+      <c r="E187" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F187" s="20" t="n">
@@ -14184,7 +14184,7 @@
       <c r="D188" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E188" s="16" t="n">
+      <c r="E188" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F188" s="20" t="n">
@@ -14217,7 +14217,7 @@
       <c r="D189" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E189" s="16" t="n">
+      <c r="E189" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F189" s="20" t="n">
@@ -14250,7 +14250,7 @@
       <c r="D190" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E190" s="16" t="n">
+      <c r="E190" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F190" s="20" t="n">
@@ -14283,7 +14283,7 @@
       <c r="D191" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E191" s="16" t="n">
+      <c r="E191" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F191" s="20" t="n">
@@ -14316,7 +14316,7 @@
       <c r="D192" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E192" s="16" t="n">
+      <c r="E192" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F192" s="20" t="n">
@@ -14349,7 +14349,7 @@
       <c r="D193" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E193" s="16" t="n">
+      <c r="E193" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F193" s="20" t="n">
@@ -14382,7 +14382,7 @@
       <c r="D194" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="16" t="n">
+      <c r="E194" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F194" s="20" t="n">
@@ -14415,7 +14415,7 @@
       <c r="D195" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E195" s="16" t="n">
+      <c r="E195" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F195" s="20" t="n">
@@ -14448,7 +14448,7 @@
       <c r="D196" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E196" s="16" t="n">
+      <c r="E196" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F196" s="20" t="n">
@@ -14481,7 +14481,7 @@
       <c r="D197" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E197" s="16" t="n">
+      <c r="E197" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F197" s="20" t="n">
@@ -14514,7 +14514,7 @@
       <c r="D198" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E198" s="16" t="n">
+      <c r="E198" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F198" s="20" t="n">
@@ -14547,7 +14547,7 @@
       <c r="D199" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E199" s="16" t="n">
+      <c r="E199" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F199" s="20" t="n">
@@ -14580,7 +14580,7 @@
       <c r="D200" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E200" s="16" t="n">
+      <c r="E200" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F200" s="20" t="n">
@@ -14613,7 +14613,7 @@
       <c r="D201" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E201" s="16" t="n">
+      <c r="E201" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F201" s="20" t="n">
@@ -14646,7 +14646,7 @@
       <c r="D202" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E202" s="16" t="n">
+      <c r="E202" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F202" s="20" t="n">
@@ -14679,7 +14679,7 @@
       <c r="D203" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E203" s="16" t="n">
+      <c r="E203" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F203" s="20" t="n">
@@ -14712,7 +14712,7 @@
       <c r="D204" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E204" s="16" t="n">
+      <c r="E204" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F204" s="20" t="n">
@@ -14749,7 +14749,7 @@
       <c r="D205" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E205" s="17" t="n">
+      <c r="E205" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F205" s="21" t="n">
@@ -14782,7 +14782,7 @@
       <c r="D206" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E206" s="16" t="n">
+      <c r="E206" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F206" s="20" t="n">
@@ -14815,7 +14815,7 @@
       <c r="D207" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E207" s="16" t="n">
+      <c r="E207" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F207" s="20" t="n">
@@ -14848,7 +14848,7 @@
       <c r="D208" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E208" s="16" t="n">
+      <c r="E208" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F208" s="20" t="n">
@@ -14881,7 +14881,7 @@
       <c r="D209" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E209" s="16" t="n">
+      <c r="E209" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F209" s="20" t="n">
@@ -14914,7 +14914,7 @@
       <c r="D210" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E210" s="16" t="n">
+      <c r="E210" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F210" s="20" t="n">
@@ -14947,7 +14947,7 @@
       <c r="D211" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E211" s="16" t="n">
+      <c r="E211" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F211" s="20" t="n">
@@ -14980,7 +14980,7 @@
       <c r="D212" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E212" s="16" t="n">
+      <c r="E212" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F212" s="20" t="n">
@@ -15013,7 +15013,7 @@
       <c r="D213" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E213" s="16" t="n">
+      <c r="E213" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F213" s="20" t="n">
@@ -15046,7 +15046,7 @@
       <c r="D214" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E214" s="16" t="n">
+      <c r="E214" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F214" s="20" t="n">
@@ -15079,7 +15079,7 @@
       <c r="D215" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E215" s="16" t="n">
+      <c r="E215" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F215" s="20" t="n">
@@ -15112,7 +15112,7 @@
       <c r="D216" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E216" s="16" t="n">
+      <c r="E216" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F216" s="20" t="n">
@@ -15145,7 +15145,7 @@
       <c r="D217" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E217" s="16" t="n">
+      <c r="E217" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F217" s="20" t="n">
@@ -15178,7 +15178,7 @@
       <c r="D218" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E218" s="16" t="n">
+      <c r="E218" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F218" s="20" t="n">
@@ -15211,7 +15211,7 @@
       <c r="D219" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E219" s="16" t="n">
+      <c r="E219" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F219" s="20" t="n">
@@ -15244,7 +15244,7 @@
       <c r="D220" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E220" s="16" t="n">
+      <c r="E220" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F220" s="20" t="n">
@@ -15277,7 +15277,7 @@
       <c r="D221" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E221" s="16" t="n">
+      <c r="E221" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F221" s="20" t="n">
@@ -15310,7 +15310,7 @@
       <c r="D222" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E222" s="16" t="n">
+      <c r="E222" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F222" s="20" t="n">
@@ -15343,7 +15343,7 @@
       <c r="D223" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E223" s="16" t="n">
+      <c r="E223" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F223" s="20" t="n">
@@ -15376,7 +15376,7 @@
       <c r="D224" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E224" s="16" t="n">
+      <c r="E224" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F224" s="20" t="n">
@@ -15409,7 +15409,7 @@
       <c r="D225" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E225" s="16" t="n">
+      <c r="E225" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F225" s="20" t="n">
@@ -15442,7 +15442,7 @@
       <c r="D226" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E226" s="16" t="n">
+      <c r="E226" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F226" s="20" t="n">
@@ -15475,7 +15475,7 @@
       <c r="D227" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E227" s="16" t="n">
+      <c r="E227" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F227" s="20" t="n">
@@ -15508,7 +15508,7 @@
       <c r="D228" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E228" s="16" t="n">
+      <c r="E228" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F228" s="20" t="n">
@@ -15541,7 +15541,7 @@
       <c r="D229" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E229" s="16" t="n">
+      <c r="E229" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F229" s="20" t="n">
@@ -15578,7 +15578,7 @@
       <c r="D230" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E230" s="17" t="n">
+      <c r="E230" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F230" s="21" t="n">
@@ -15611,7 +15611,7 @@
       <c r="D231" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E231" s="16" t="n">
+      <c r="E231" s="12" t="n">
         <v>0.388</v>
       </c>
       <c r="F231" s="20" t="n">
@@ -15644,7 +15644,7 @@
       <c r="D232" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E232" s="16" t="n">
+      <c r="E232" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F232" s="20" t="n">
@@ -15677,7 +15677,7 @@
       <c r="D233" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E233" s="16" t="n">
+      <c r="E233" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F233" s="20" t="n">
@@ -15710,7 +15710,7 @@
       <c r="D234" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="16" t="n">
+      <c r="E234" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F234" s="20" t="n">
@@ -15743,7 +15743,7 @@
       <c r="D235" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E235" s="16" t="n">
+      <c r="E235" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F235" s="20" t="n">
@@ -15776,7 +15776,7 @@
       <c r="D236" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E236" s="16" t="n">
+      <c r="E236" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F236" s="20" t="n">
@@ -15809,7 +15809,7 @@
       <c r="D237" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="16" t="n">
+      <c r="E237" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F237" s="20" t="n">
@@ -15842,7 +15842,7 @@
       <c r="D238" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E238" s="16" t="n">
+      <c r="E238" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F238" s="20" t="n">
@@ -15875,7 +15875,7 @@
       <c r="D239" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E239" s="16" t="n">
+      <c r="E239" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F239" s="20" t="n">
@@ -15908,7 +15908,7 @@
       <c r="D240" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E240" s="16" t="n">
+      <c r="E240" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F240" s="20" t="n">
@@ -15941,7 +15941,7 @@
       <c r="D241" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E241" s="16" t="n">
+      <c r="E241" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F241" s="20" t="n">
@@ -15974,7 +15974,7 @@
       <c r="D242" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E242" s="16" t="n">
+      <c r="E242" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F242" s="20" t="n">
@@ -16007,7 +16007,7 @@
       <c r="D243" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E243" s="16" t="n">
+      <c r="E243" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F243" s="20" t="n">
@@ -16040,7 +16040,7 @@
       <c r="D244" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E244" s="16" t="n">
+      <c r="E244" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F244" s="20" t="n">
@@ -16073,7 +16073,7 @@
       <c r="D245" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="16" t="n">
+      <c r="E245" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F245" s="20" t="n">
@@ -16106,7 +16106,7 @@
       <c r="D246" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E246" s="16" t="n">
+      <c r="E246" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F246" s="20" t="n">
@@ -16139,7 +16139,7 @@
       <c r="D247" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E247" s="16" t="n">
+      <c r="E247" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F247" s="20" t="n">
@@ -16172,7 +16172,7 @@
       <c r="D248" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E248" s="16" t="n">
+      <c r="E248" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F248" s="20" t="n">
@@ -16205,7 +16205,7 @@
       <c r="D249" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E249" s="16" t="n">
+      <c r="E249" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F249" s="20" t="n">
@@ -16238,7 +16238,7 @@
       <c r="D250" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E250" s="16" t="n">
+      <c r="E250" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F250" s="20" t="n">
@@ -16271,7 +16271,7 @@
       <c r="D251" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E251" s="16" t="n">
+      <c r="E251" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F251" s="20" t="n">
@@ -16304,7 +16304,7 @@
       <c r="D252" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E252" s="16" t="n">
+      <c r="E252" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F252" s="20" t="n">
@@ -16337,7 +16337,7 @@
       <c r="D253" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="16" t="n">
+      <c r="E253" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F253" s="20" t="n">
@@ -16370,7 +16370,7 @@
       <c r="D254" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E254" s="16" t="n">
+      <c r="E254" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F254" s="20" t="n">
@@ -16407,7 +16407,7 @@
       <c r="D255" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E255" s="17" t="n">
+      <c r="E255" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F255" s="21" t="n">
@@ -16440,7 +16440,7 @@
       <c r="D256" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E256" s="16" t="n">
+      <c r="E256" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F256" s="20" t="n">
@@ -16473,7 +16473,7 @@
       <c r="D257" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E257" s="16" t="n">
+      <c r="E257" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F257" s="20" t="n">
@@ -16506,7 +16506,7 @@
       <c r="D258" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E258" s="16" t="n">
+      <c r="E258" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F258" s="20" t="n">
@@ -16539,7 +16539,7 @@
       <c r="D259" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E259" s="16" t="n">
+      <c r="E259" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F259" s="20" t="n">
@@ -16572,7 +16572,7 @@
       <c r="D260" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="16" t="n">
+      <c r="E260" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F260" s="20" t="n">
@@ -16605,7 +16605,7 @@
       <c r="D261" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E261" s="16" t="n">
+      <c r="E261" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F261" s="20" t="n">
@@ -16638,7 +16638,7 @@
       <c r="D262" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E262" s="16" t="n">
+      <c r="E262" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F262" s="20" t="n">
@@ -16671,7 +16671,7 @@
       <c r="D263" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E263" s="16" t="n">
+      <c r="E263" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F263" s="20" t="n">
@@ -16704,7 +16704,7 @@
       <c r="D264" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E264" s="16" t="n">
+      <c r="E264" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F264" s="20" t="n">
@@ -16737,7 +16737,7 @@
       <c r="D265" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E265" s="16" t="n">
+      <c r="E265" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F265" s="20" t="n">
@@ -16770,7 +16770,7 @@
       <c r="D266" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E266" s="16" t="n">
+      <c r="E266" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F266" s="20" t="n">
@@ -16803,7 +16803,7 @@
       <c r="D267" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E267" s="16" t="n">
+      <c r="E267" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F267" s="20" t="n">
@@ -16836,7 +16836,7 @@
       <c r="D268" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E268" s="16" t="n">
+      <c r="E268" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F268" s="20" t="n">
@@ -16869,7 +16869,7 @@
       <c r="D269" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E269" s="16" t="n">
+      <c r="E269" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F269" s="20" t="n">
@@ -16902,7 +16902,7 @@
       <c r="D270" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E270" s="16" t="n">
+      <c r="E270" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F270" s="20" t="n">
@@ -16935,7 +16935,7 @@
       <c r="D271" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E271" s="16" t="n">
+      <c r="E271" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F271" s="20" t="n">
@@ -16968,7 +16968,7 @@
       <c r="D272" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E272" s="16" t="n">
+      <c r="E272" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F272" s="20" t="n">
@@ -17001,7 +17001,7 @@
       <c r="D273" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E273" s="16" t="n">
+      <c r="E273" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F273" s="20" t="n">
@@ -17034,7 +17034,7 @@
       <c r="D274" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E274" s="16" t="n">
+      <c r="E274" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F274" s="20" t="n">
@@ -17067,7 +17067,7 @@
       <c r="D275" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E275" s="16" t="n">
+      <c r="E275" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F275" s="20" t="n">
@@ -17100,7 +17100,7 @@
       <c r="D276" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E276" s="16" t="n">
+      <c r="E276" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F276" s="20" t="n">
@@ -17133,7 +17133,7 @@
       <c r="D277" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E277" s="16" t="n">
+      <c r="E277" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F277" s="20" t="n">
@@ -17166,7 +17166,7 @@
       <c r="D278" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E278" s="16" t="n">
+      <c r="E278" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F278" s="20" t="n">
@@ -17199,7 +17199,7 @@
       <c r="D279" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E279" s="16" t="n">
+      <c r="E279" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F279" s="20" t="n">
@@ -17236,7 +17236,7 @@
       <c r="D280" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E280" s="16" t="n">
+      <c r="E280" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F280" s="20" t="n">
@@ -17269,7 +17269,7 @@
       <c r="D281" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E281" s="16" t="n">
+      <c r="E281" s="12" t="n">
         <v>1.4125</v>
       </c>
       <c r="F281" s="20" t="n">
@@ -17302,7 +17302,7 @@
       <c r="D282" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E282" s="16" t="n">
+      <c r="E282" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F282" s="20" t="n">
@@ -17335,7 +17335,7 @@
       <c r="D283" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E283" s="16" t="n">
+      <c r="E283" s="12" t="n">
         <v>1.6934</v>
       </c>
       <c r="F283" s="20" t="n">
@@ -17368,7 +17368,7 @@
       <c r="D284" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E284" s="16" t="n">
+      <c r="E284" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F284" s="20" t="n">
@@ -17401,7 +17401,7 @@
       <c r="D285" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E285" s="17" t="n">
+      <c r="E285" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F285" s="21" t="n">
@@ -17434,7 +17434,7 @@
       <c r="D286" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E286" s="16" t="n">
+      <c r="E286" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F286" s="20" t="n">
@@ -17467,7 +17467,7 @@
       <c r="D287" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E287" s="16" t="n">
+      <c r="E287" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F287" s="20" t="n">
@@ -17500,7 +17500,7 @@
       <c r="D288" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E288" s="16" t="n">
+      <c r="E288" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F288" s="20" t="n">
@@ -17533,7 +17533,7 @@
       <c r="D289" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E289" s="16" t="n">
+      <c r="E289" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F289" s="20" t="n">
@@ -17566,7 +17566,7 @@
       <c r="D290" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E290" s="16" t="n">
+      <c r="E290" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F290" s="20" t="n">
@@ -17599,7 +17599,7 @@
       <c r="D291" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E291" s="16" t="n">
+      <c r="E291" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F291" s="20" t="n">
@@ -17632,7 +17632,7 @@
       <c r="D292" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E292" s="16" t="n">
+      <c r="E292" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F292" s="20" t="n">
@@ -17665,7 +17665,7 @@
       <c r="D293" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E293" s="16" t="n">
+      <c r="E293" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F293" s="20" t="n">
@@ -17698,7 +17698,7 @@
       <c r="D294" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E294" s="16" t="n">
+      <c r="E294" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F294" s="20" t="n">
@@ -17731,7 +17731,7 @@
       <c r="D295" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E295" s="16" t="n">
+      <c r="E295" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F295" s="20" t="n">
@@ -17764,7 +17764,7 @@
       <c r="D296" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E296" s="16" t="n">
+      <c r="E296" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F296" s="20" t="n">
@@ -17797,7 +17797,7 @@
       <c r="D297" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E297" s="16" t="n">
+      <c r="E297" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F297" s="20" t="n">
@@ -17830,7 +17830,7 @@
       <c r="D298" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E298" s="16" t="n">
+      <c r="E298" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F298" s="20" t="n">
@@ -17863,7 +17863,7 @@
       <c r="D299" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E299" s="16" t="n">
+      <c r="E299" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F299" s="20" t="n">
@@ -17896,7 +17896,7 @@
       <c r="D300" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E300" s="16" t="n">
+      <c r="E300" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F300" s="20" t="n">
@@ -17929,7 +17929,7 @@
       <c r="D301" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E301" s="16" t="n">
+      <c r="E301" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F301" s="20" t="n">
@@ -17962,7 +17962,7 @@
       <c r="D302" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E302" s="16" t="n">
+      <c r="E302" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F302" s="20" t="n">
@@ -17995,7 +17995,7 @@
       <c r="D303" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E303" s="16" t="n">
+      <c r="E303" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F303" s="20" t="n">
@@ -18028,7 +18028,7 @@
       <c r="D304" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E304" s="16" t="n">
+      <c r="E304" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F304" s="20" t="n">
@@ -18065,7 +18065,7 @@
       <c r="D305" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E305" s="17" t="n">
+      <c r="E305" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F305" s="21" t="n">
@@ -18098,7 +18098,7 @@
       <c r="D306" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E306" s="16" t="n">
+      <c r="E306" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F306" s="20" t="n">
@@ -18131,7 +18131,7 @@
       <c r="D307" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E307" s="16" t="n">
+      <c r="E307" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F307" s="20" t="n">
@@ -18164,7 +18164,7 @@
       <c r="D308" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E308" s="16" t="n">
+      <c r="E308" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F308" s="20" t="n">
@@ -18197,7 +18197,7 @@
       <c r="D309" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E309" s="16" t="n">
+      <c r="E309" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F309" s="20" t="n">
@@ -18230,7 +18230,7 @@
       <c r="D310" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E310" s="16" t="n">
+      <c r="E310" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F310" s="20" t="n">
@@ -18263,7 +18263,7 @@
       <c r="D311" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E311" s="16" t="n">
+      <c r="E311" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F311" s="20" t="n">
@@ -18296,7 +18296,7 @@
       <c r="D312" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E312" s="16" t="n">
+      <c r="E312" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F312" s="20" t="n">
@@ -18329,7 +18329,7 @@
       <c r="D313" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E313" s="16" t="n">
+      <c r="E313" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F313" s="20" t="n">
@@ -18362,7 +18362,7 @@
       <c r="D314" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E314" s="16" t="n">
+      <c r="E314" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F314" s="20" t="n">
@@ -18395,7 +18395,7 @@
       <c r="D315" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E315" s="16" t="n">
+      <c r="E315" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F315" s="20" t="n">
@@ -18428,7 +18428,7 @@
       <c r="D316" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E316" s="16" t="n">
+      <c r="E316" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F316" s="20" t="n">
@@ -18461,7 +18461,7 @@
       <c r="D317" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E317" s="16" t="n">
+      <c r="E317" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F317" s="20" t="n">
@@ -18494,7 +18494,7 @@
       <c r="D318" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E318" s="16" t="n">
+      <c r="E318" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F318" s="20" t="n">
@@ -18527,7 +18527,7 @@
       <c r="D319" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E319" s="16" t="n">
+      <c r="E319" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F319" s="20" t="n">
@@ -18560,7 +18560,7 @@
       <c r="D320" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E320" s="16" t="n">
+      <c r="E320" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F320" s="20" t="n">
@@ -18593,7 +18593,7 @@
       <c r="D321" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E321" s="16" t="n">
+      <c r="E321" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F321" s="20" t="n">
@@ -18626,7 +18626,7 @@
       <c r="D322" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E322" s="16" t="n">
+      <c r="E322" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F322" s="20" t="n">
@@ -18659,7 +18659,7 @@
       <c r="D323" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E323" s="16" t="n">
+      <c r="E323" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F323" s="20" t="n">
@@ -18692,7 +18692,7 @@
       <c r="D324" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E324" s="16" t="n">
+      <c r="E324" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F324" s="20" t="n">
@@ -18725,7 +18725,7 @@
       <c r="D325" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E325" s="16" t="n">
+      <c r="E325" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F325" s="20" t="n">
@@ -18758,7 +18758,7 @@
       <c r="D326" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E326" s="16" t="n">
+      <c r="E326" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F326" s="20" t="n">
@@ -18791,7 +18791,7 @@
       <c r="D327" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E327" s="16" t="n">
+      <c r="E327" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F327" s="20" t="n">
@@ -18824,7 +18824,7 @@
       <c r="D328" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E328" s="16" t="n">
+      <c r="E328" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F328" s="20" t="n">
@@ -18857,7 +18857,7 @@
       <c r="D329" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E329" s="16" t="n">
+      <c r="E329" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F329" s="20" t="n">
@@ -18894,7 +18894,7 @@
       <c r="D330" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E330" s="16" t="n">
+      <c r="E330" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F330" s="20" t="n">
@@ -18927,7 +18927,7 @@
       <c r="D331" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E331" s="16" t="n">
+      <c r="E331" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F331" s="20" t="n">
@@ -18960,7 +18960,7 @@
       <c r="D332" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E332" s="17" t="n">
+      <c r="E332" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F332" s="21" t="n">
@@ -18993,7 +18993,7 @@
       <c r="D333" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E333" s="16" t="n">
+      <c r="E333" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F333" s="20" t="n">
@@ -19026,7 +19026,7 @@
       <c r="D334" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E334" s="16" t="n">
+      <c r="E334" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F334" s="20" t="n">
@@ -19059,7 +19059,7 @@
       <c r="D335" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E335" s="16" t="n">
+      <c r="E335" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F335" s="20" t="n">
@@ -19092,7 +19092,7 @@
       <c r="D336" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E336" s="16" t="n">
+      <c r="E336" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F336" s="20" t="n">
@@ -19125,7 +19125,7 @@
       <c r="D337" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E337" s="16" t="n">
+      <c r="E337" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F337" s="20" t="n">
@@ -19158,7 +19158,7 @@
       <c r="D338" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E338" s="16" t="n">
+      <c r="E338" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F338" s="20" t="n">
@@ -19191,7 +19191,7 @@
       <c r="D339" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E339" s="16" t="n">
+      <c r="E339" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F339" s="20" t="n">
@@ -19224,7 +19224,7 @@
       <c r="D340" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E340" s="16" t="n">
+      <c r="E340" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F340" s="20" t="n">
@@ -19257,7 +19257,7 @@
       <c r="D341" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E341" s="16" t="n">
+      <c r="E341" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F341" s="20" t="n">
@@ -19290,7 +19290,7 @@
       <c r="D342" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E342" s="16" t="n">
+      <c r="E342" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F342" s="20" t="n">
@@ -19323,7 +19323,7 @@
       <c r="D343" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E343" s="16" t="n">
+      <c r="E343" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F343" s="20" t="n">
@@ -19356,7 +19356,7 @@
       <c r="D344" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E344" s="16" t="n">
+      <c r="E344" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F344" s="20" t="n">
@@ -19389,7 +19389,7 @@
       <c r="D345" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E345" s="16" t="n">
+      <c r="E345" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F345" s="20" t="n">
@@ -19422,7 +19422,7 @@
       <c r="D346" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E346" s="16" t="n">
+      <c r="E346" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F346" s="20" t="n">
@@ -19455,7 +19455,7 @@
       <c r="D347" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E347" s="16" t="n">
+      <c r="E347" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F347" s="20" t="n">
@@ -19488,7 +19488,7 @@
       <c r="D348" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E348" s="16" t="n">
+      <c r="E348" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F348" s="20" t="n">
@@ -19521,7 +19521,7 @@
       <c r="D349" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E349" s="16" t="n">
+      <c r="E349" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F349" s="20" t="n">
@@ -19554,7 +19554,7 @@
       <c r="D350" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E350" s="16" t="n">
+      <c r="E350" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F350" s="20" t="n">
@@ -19587,7 +19587,7 @@
       <c r="D351" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E351" s="16" t="n">
+      <c r="E351" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F351" s="20" t="n">
@@ -19620,7 +19620,7 @@
       <c r="D352" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E352" s="16" t="n">
+      <c r="E352" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F352" s="20" t="n">
@@ -19653,7 +19653,7 @@
       <c r="D353" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E353" s="16" t="n">
+      <c r="E353" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F353" s="20" t="n">
@@ -19686,7 +19686,7 @@
       <c r="D354" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E354" s="16" t="n">
+      <c r="E354" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F354" s="20" t="n">
@@ -19723,7 +19723,7 @@
       <c r="D355" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E355" s="16" t="n">
+      <c r="E355" s="12" t="n">
         <v>0.835</v>
       </c>
       <c r="F355" s="20" t="n">
@@ -19756,7 +19756,7 @@
       <c r="D356" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E356" s="16" t="n">
+      <c r="E356" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F356" s="20" t="n">
@@ -19789,7 +19789,7 @@
       <c r="D357" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E357" s="17" t="n">
+      <c r="E357" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F357" s="21" t="n">
@@ -19822,7 +19822,7 @@
       <c r="D358" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E358" s="16" t="n">
+      <c r="E358" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F358" s="20" t="n">
@@ -19855,7 +19855,7 @@
       <c r="D359" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E359" s="16" t="n">
+      <c r="E359" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F359" s="20" t="n">
@@ -19888,7 +19888,7 @@
       <c r="D360" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E360" s="16" t="n">
+      <c r="E360" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F360" s="20" t="n">
@@ -19921,7 +19921,7 @@
       <c r="D361" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E361" s="16" t="n">
+      <c r="E361" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F361" s="20" t="n">
@@ -19954,7 +19954,7 @@
       <c r="D362" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E362" s="16" t="n">
+      <c r="E362" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F362" s="20" t="n">
@@ -19987,7 +19987,7 @@
       <c r="D363" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E363" s="16" t="n">
+      <c r="E363" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F363" s="20" t="n">
@@ -20020,7 +20020,7 @@
       <c r="D364" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E364" s="16" t="n">
+      <c r="E364" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F364" s="20" t="n">
@@ -20053,7 +20053,7 @@
       <c r="D365" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E365" s="16" t="n">
+      <c r="E365" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F365" s="20" t="n">
@@ -20086,7 +20086,7 @@
       <c r="D366" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E366" s="16" t="n">
+      <c r="E366" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F366" s="20" t="n">
@@ -20119,7 +20119,7 @@
       <c r="D367" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E367" s="16" t="n">
+      <c r="E367" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F367" s="20" t="n">
@@ -20152,7 +20152,7 @@
       <c r="D368" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E368" s="16" t="n">
+      <c r="E368" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F368" s="20" t="n">
@@ -20185,7 +20185,7 @@
       <c r="D369" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E369" s="16" t="n">
+      <c r="E369" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F369" s="20" t="n">
@@ -20218,7 +20218,7 @@
       <c r="D370" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E370" s="16" t="n">
+      <c r="E370" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F370" s="20" t="n">
@@ -20251,7 +20251,7 @@
       <c r="D371" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E371" s="16" t="n">
+      <c r="E371" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F371" s="20" t="n">
@@ -20284,7 +20284,7 @@
       <c r="D372" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E372" s="16" t="n">
+      <c r="E372" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F372" s="20" t="n">
@@ -20317,7 +20317,7 @@
       <c r="D373" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E373" s="16" t="n">
+      <c r="E373" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F373" s="20" t="n">
@@ -20350,7 +20350,7 @@
       <c r="D374" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E374" s="16" t="n">
+      <c r="E374" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F374" s="20" t="n">
@@ -20383,7 +20383,7 @@
       <c r="D375" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E375" s="16" t="n">
+      <c r="E375" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F375" s="20" t="n">
@@ -20416,7 +20416,7 @@
       <c r="D376" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E376" s="16" t="n">
+      <c r="E376" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F376" s="20" t="n">
@@ -20449,7 +20449,7 @@
       <c r="D377" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E377" s="16" t="n">
+      <c r="E377" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F377" s="20" t="n">
@@ -20482,7 +20482,7 @@
       <c r="D378" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E378" s="16" t="n">
+      <c r="E378" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F378" s="20" t="n">
@@ -20515,7 +20515,7 @@
       <c r="D379" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E379" s="16" t="n">
+      <c r="E379" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F379" s="20" t="n">
@@ -20552,7 +20552,7 @@
       <c r="D380" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E380" s="16" t="n">
+      <c r="E380" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F380" s="20" t="n">
@@ -20585,7 +20585,7 @@
       <c r="D381" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E381" s="16" t="n">
+      <c r="E381" s="12" t="n">
         <v>0.6614</v>
       </c>
       <c r="F381" s="20" t="n">
@@ -20618,7 +20618,7 @@
       <c r="D382" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E382" s="16" t="n">
+      <c r="E382" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F382" s="20" t="n">
@@ -20651,7 +20651,7 @@
       <c r="D383" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E383" s="16" t="n">
+      <c r="E383" s="12" t="n">
         <v>1.2078</v>
       </c>
       <c r="F383" s="20" t="n">
@@ -20684,7 +20684,7 @@
       <c r="D384" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E384" s="16" t="n">
+      <c r="E384" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F384" s="20" t="n">
@@ -20717,7 +20717,7 @@
       <c r="D385" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E385" s="16" t="n">
+      <c r="E385" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F385" s="20" t="n">
@@ -20750,7 +20750,7 @@
       <c r="D386" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E386" s="17" t="n">
+      <c r="E386" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F386" s="21" t="n">
@@ -20783,7 +20783,7 @@
       <c r="D387" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E387" s="16" t="n">
+      <c r="E387" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F387" s="20" t="n">
@@ -20816,7 +20816,7 @@
       <c r="D388" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E388" s="16" t="n">
+      <c r="E388" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F388" s="20" t="n">
@@ -20849,7 +20849,7 @@
       <c r="D389" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E389" s="16" t="n">
+      <c r="E389" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F389" s="20" t="n">
@@ -20882,7 +20882,7 @@
       <c r="D390" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E390" s="16" t="n">
+      <c r="E390" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F390" s="20" t="n">
@@ -20915,7 +20915,7 @@
       <c r="D391" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E391" s="16" t="n">
+      <c r="E391" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F391" s="20" t="n">
@@ -20948,7 +20948,7 @@
       <c r="D392" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E392" s="16" t="n">
+      <c r="E392" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F392" s="20" t="n">
@@ -20981,7 +20981,7 @@
       <c r="D393" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E393" s="16" t="n">
+      <c r="E393" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F393" s="20" t="n">
@@ -21014,7 +21014,7 @@
       <c r="D394" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E394" s="16" t="n">
+      <c r="E394" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F394" s="20" t="n">
@@ -21047,7 +21047,7 @@
       <c r="D395" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E395" s="16" t="n">
+      <c r="E395" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F395" s="20" t="n">
@@ -21080,7 +21080,7 @@
       <c r="D396" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E396" s="16" t="n">
+      <c r="E396" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F396" s="20" t="n">
@@ -21113,7 +21113,7 @@
       <c r="D397" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E397" s="16" t="n">
+      <c r="E397" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F397" s="20" t="n">
@@ -21146,7 +21146,7 @@
       <c r="D398" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E398" s="16" t="n">
+      <c r="E398" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F398" s="20" t="n">
@@ -21179,7 +21179,7 @@
       <c r="D399" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E399" s="16" t="n">
+      <c r="E399" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F399" s="20" t="n">
@@ -21212,7 +21212,7 @@
       <c r="D400" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E400" s="16" t="n">
+      <c r="E400" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F400" s="20" t="n">
@@ -21245,7 +21245,7 @@
       <c r="D401" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E401" s="16" t="n">
+      <c r="E401" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F401" s="20" t="n">
@@ -21278,7 +21278,7 @@
       <c r="D402" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E402" s="16" t="n">
+      <c r="E402" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F402" s="20" t="n">
@@ -21311,7 +21311,7 @@
       <c r="D403" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E403" s="16" t="n">
+      <c r="E403" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F403" s="20" t="n">
@@ -21344,7 +21344,7 @@
       <c r="D404" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E404" s="16" t="n">
+      <c r="E404" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F404" s="20" t="n">
@@ -21381,7 +21381,7 @@
       <c r="D405" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E405" s="16" t="n">
+      <c r="E405" s="12" t="n">
         <v>1.1386</v>
       </c>
       <c r="F405" s="20" t="n">
@@ -21414,7 +21414,7 @@
       <c r="D406" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E406" s="16" t="n">
+      <c r="E406" s="12" t="n">
         <v>0.4092</v>
       </c>
       <c r="F406" s="20" t="n">
@@ -21447,7 +21447,7 @@
       <c r="D407" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E407" s="16" t="n">
+      <c r="E407" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F407" s="20" t="n">
@@ -21480,7 +21480,7 @@
       <c r="D408" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E408" s="17" t="n">
+      <c r="E408" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F408" s="21" t="n">
@@ -21513,7 +21513,7 @@
       <c r="D409" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E409" s="16" t="n">
+      <c r="E409" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F409" s="20" t="n">
@@ -21546,7 +21546,7 @@
       <c r="D410" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E410" s="16" t="n">
+      <c r="E410" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F410" s="20" t="n">
@@ -21579,7 +21579,7 @@
       <c r="D411" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E411" s="16" t="n">
+      <c r="E411" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F411" s="20" t="n">
@@ -21612,7 +21612,7 @@
       <c r="D412" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E412" s="16" t="n">
+      <c r="E412" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F412" s="20" t="n">
@@ -21645,7 +21645,7 @@
       <c r="D413" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E413" s="16" t="n">
+      <c r="E413" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F413" s="20" t="n">
@@ -21678,7 +21678,7 @@
       <c r="D414" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E414" s="16" t="n">
+      <c r="E414" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F414" s="20" t="n">
@@ -21711,7 +21711,7 @@
       <c r="D415" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E415" s="16" t="n">
+      <c r="E415" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F415" s="20" t="n">
@@ -21744,7 +21744,7 @@
       <c r="D416" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E416" s="16" t="n">
+      <c r="E416" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F416" s="20" t="n">
@@ -21777,7 +21777,7 @@
       <c r="D417" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E417" s="16" t="n">
+      <c r="E417" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F417" s="20" t="n">
@@ -21810,7 +21810,7 @@
       <c r="D418" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E418" s="16" t="n">
+      <c r="E418" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F418" s="20" t="n">
@@ -21843,7 +21843,7 @@
       <c r="D419" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E419" s="16" t="n">
+      <c r="E419" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F419" s="20" t="n">
@@ -21876,7 +21876,7 @@
       <c r="D420" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E420" s="16" t="n">
+      <c r="E420" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F420" s="20" t="n">
@@ -21909,7 +21909,7 @@
       <c r="D421" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E421" s="16" t="n">
+      <c r="E421" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F421" s="20" t="n">
@@ -21942,7 +21942,7 @@
       <c r="D422" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E422" s="16" t="n">
+      <c r="E422" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F422" s="20" t="n">
@@ -21975,7 +21975,7 @@
       <c r="D423" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E423" s="16" t="n">
+      <c r="E423" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F423" s="20" t="n">
@@ -22008,7 +22008,7 @@
       <c r="D424" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E424" s="16" t="n">
+      <c r="E424" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F424" s="20" t="n">
@@ -22041,7 +22041,7 @@
       <c r="D425" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E425" s="16" t="n">
+      <c r="E425" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F425" s="20" t="n">
@@ -22074,7 +22074,7 @@
       <c r="D426" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E426" s="16" t="n">
+      <c r="E426" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F426" s="20" t="n">
@@ -22107,7 +22107,7 @@
       <c r="D427" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E427" s="16" t="n">
+      <c r="E427" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F427" s="20" t="n">
@@ -22140,7 +22140,7 @@
       <c r="D428" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E428" s="16" t="n">
+      <c r="E428" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F428" s="20" t="n">
@@ -22173,7 +22173,7 @@
       <c r="D429" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E429" s="16" t="n">
+      <c r="E429" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F429" s="20" t="n">
@@ -22210,7 +22210,7 @@
       <c r="D430" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E430" s="17" t="n">
+      <c r="E430" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F430" s="21" t="n">
@@ -22243,7 +22243,7 @@
       <c r="D431" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E431" s="16" t="n">
+      <c r="E431" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F431" s="20" t="n">
@@ -22276,7 +22276,7 @@
       <c r="D432" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E432" s="16" t="n">
+      <c r="E432" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F432" s="20" t="n">
@@ -22309,7 +22309,7 @@
       <c r="D433" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E433" s="16" t="n">
+      <c r="E433" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F433" s="20" t="n">
@@ -22342,7 +22342,7 @@
       <c r="D434" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E434" s="16" t="n">
+      <c r="E434" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F434" s="20" t="n">
@@ -22375,7 +22375,7 @@
       <c r="D435" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E435" s="16" t="n">
+      <c r="E435" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F435" s="20" t="n">
@@ -22408,7 +22408,7 @@
       <c r="D436" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E436" s="16" t="n">
+      <c r="E436" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F436" s="20" t="n">
@@ -22441,7 +22441,7 @@
       <c r="D437" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E437" s="16" t="n">
+      <c r="E437" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F437" s="20" t="n">
@@ -22474,7 +22474,7 @@
       <c r="D438" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E438" s="16" t="n">
+      <c r="E438" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F438" s="20" t="n">
@@ -22507,7 +22507,7 @@
       <c r="D439" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E439" s="16" t="n">
+      <c r="E439" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F439" s="20" t="n">
@@ -22540,7 +22540,7 @@
       <c r="D440" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E440" s="16" t="n">
+      <c r="E440" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F440" s="20" t="n">
@@ -22573,7 +22573,7 @@
       <c r="D441" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E441" s="16" t="n">
+      <c r="E441" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F441" s="20" t="n">
@@ -22606,7 +22606,7 @@
       <c r="D442" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E442" s="16" t="n">
+      <c r="E442" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F442" s="20" t="n">
@@ -22639,7 +22639,7 @@
       <c r="D443" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E443" s="16" t="n">
+      <c r="E443" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F443" s="20" t="n">
@@ -22672,7 +22672,7 @@
       <c r="D444" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E444" s="16" t="n">
+      <c r="E444" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F444" s="20" t="n">
@@ -22705,7 +22705,7 @@
       <c r="D445" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E445" s="16" t="n">
+      <c r="E445" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F445" s="20" t="n">
@@ -22738,7 +22738,7 @@
       <c r="D446" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E446" s="16" t="n">
+      <c r="E446" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F446" s="20" t="n">
@@ -22771,7 +22771,7 @@
       <c r="D447" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E447" s="16" t="n">
+      <c r="E447" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F447" s="20" t="n">
@@ -22804,7 +22804,7 @@
       <c r="D448" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E448" s="16" t="n">
+      <c r="E448" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F448" s="20" t="n">
@@ -22837,7 +22837,7 @@
       <c r="D449" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E449" s="16" t="n">
+      <c r="E449" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F449" s="20" t="n">
@@ -22870,7 +22870,7 @@
       <c r="D450" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E450" s="16" t="n">
+      <c r="E450" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F450" s="20" t="n">
@@ -22903,7 +22903,7 @@
       <c r="D451" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E451" s="16" t="n">
+      <c r="E451" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F451" s="20" t="n">
@@ -22936,7 +22936,7 @@
       <c r="D452" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E452" s="16" t="n">
+      <c r="E452" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F452" s="20" t="n">
@@ -22969,7 +22969,7 @@
       <c r="D453" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E453" s="16" t="n">
+      <c r="E453" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F453" s="20" t="n">
@@ -23002,7 +23002,7 @@
       <c r="D454" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E454" s="16" t="n">
+      <c r="E454" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F454" s="20" t="n">
@@ -23039,7 +23039,7 @@
       <c r="D455" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E455" s="17" t="n">
+      <c r="E455" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F455" s="21" t="n">
@@ -23072,7 +23072,7 @@
       <c r="D456" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E456" s="16" t="n">
+      <c r="E456" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F456" s="20" t="n">
@@ -23105,7 +23105,7 @@
       <c r="D457" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E457" s="16" t="n">
+      <c r="E457" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F457" s="20" t="n">
@@ -23138,7 +23138,7 @@
       <c r="D458" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E458" s="16" t="n">
+      <c r="E458" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F458" s="20" t="n">
@@ -23171,7 +23171,7 @@
       <c r="D459" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E459" s="16" t="n">
+      <c r="E459" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F459" s="20" t="n">
@@ -23204,7 +23204,7 @@
       <c r="D460" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E460" s="16" t="n">
+      <c r="E460" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F460" s="20" t="n">
@@ -23237,7 +23237,7 @@
       <c r="D461" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E461" s="16" t="n">
+      <c r="E461" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F461" s="20" t="n">
@@ -23270,7 +23270,7 @@
       <c r="D462" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E462" s="16" t="n">
+      <c r="E462" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F462" s="20" t="n">
@@ -23303,7 +23303,7 @@
       <c r="D463" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E463" s="16" t="n">
+      <c r="E463" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F463" s="20" t="n">
@@ -23336,7 +23336,7 @@
       <c r="D464" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E464" s="16" t="n">
+      <c r="E464" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F464" s="20" t="n">
@@ -23369,7 +23369,7 @@
       <c r="D465" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E465" s="16" t="n">
+      <c r="E465" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F465" s="20" t="n">
@@ -23402,7 +23402,7 @@
       <c r="D466" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E466" s="16" t="n">
+      <c r="E466" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F466" s="20" t="n">
@@ -23435,7 +23435,7 @@
       <c r="D467" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E467" s="16" t="n">
+      <c r="E467" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F467" s="20" t="n">
@@ -23468,7 +23468,7 @@
       <c r="D468" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E468" s="16" t="n">
+      <c r="E468" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F468" s="20" t="n">
@@ -23501,7 +23501,7 @@
       <c r="D469" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E469" s="16" t="n">
+      <c r="E469" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F469" s="20" t="n">
@@ -23534,7 +23534,7 @@
       <c r="D470" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E470" s="16" t="n">
+      <c r="E470" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F470" s="20" t="n">
@@ -23567,7 +23567,7 @@
       <c r="D471" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E471" s="16" t="n">
+      <c r="E471" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F471" s="20" t="n">
@@ -23600,7 +23600,7 @@
       <c r="D472" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E472" s="16" t="n">
+      <c r="E472" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F472" s="20" t="n">
@@ -23633,7 +23633,7 @@
       <c r="D473" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E473" s="16" t="n">
+      <c r="E473" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F473" s="20" t="n">
@@ -23666,7 +23666,7 @@
       <c r="D474" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E474" s="16" t="n">
+      <c r="E474" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F474" s="20" t="n">
@@ -23699,7 +23699,7 @@
       <c r="D475" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E475" s="16" t="n">
+      <c r="E475" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F475" s="20" t="n">
@@ -23732,7 +23732,7 @@
       <c r="D476" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E476" s="16" t="n">
+      <c r="E476" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F476" s="20" t="n">
@@ -23765,7 +23765,7 @@
       <c r="D477" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E477" s="16" t="n">
+      <c r="E477" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F477" s="20" t="n">
@@ -23798,7 +23798,7 @@
       <c r="D478" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E478" s="16" t="n">
+      <c r="E478" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F478" s="20" t="n">
@@ -23831,7 +23831,7 @@
       <c r="D479" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E479" s="16" t="n">
+      <c r="E479" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F479" s="20" t="n">
@@ -23868,7 +23868,7 @@
       <c r="D480" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E480" s="17" t="n">
+      <c r="E480" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="F480" s="21" t="n">
@@ -23901,7 +23901,7 @@
       <c r="D481" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E481" s="16" t="n">
+      <c r="E481" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F481" s="20" t="n">
@@ -23934,7 +23934,7 @@
       <c r="D482" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E482" s="16" t="n">
+      <c r="E482" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F482" s="20" t="n">
@@ -23967,7 +23967,7 @@
       <c r="D483" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E483" s="16" t="n">
+      <c r="E483" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F483" s="20" t="n">
@@ -24000,7 +24000,7 @@
       <c r="D484" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E484" s="16" t="n">
+      <c r="E484" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F484" s="20" t="n">
@@ -24033,7 +24033,7 @@
       <c r="D485" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E485" s="16" t="n">
+      <c r="E485" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F485" s="20" t="n">
@@ -24066,7 +24066,7 @@
       <c r="D486" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E486" s="16" t="n">
+      <c r="E486" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F486" s="20" t="n">
@@ -24099,7 +24099,7 @@
       <c r="D487" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E487" s="16" t="n">
+      <c r="E487" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F487" s="20" t="n">
@@ -24132,7 +24132,7 @@
       <c r="D488" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E488" s="16" t="n">
+      <c r="E488" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F488" s="20" t="n">
@@ -24165,7 +24165,7 @@
       <c r="D489" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E489" s="16" t="n">
+      <c r="E489" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F489" s="20" t="n">
@@ -24198,7 +24198,7 @@
       <c r="D490" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E490" s="16" t="n">
+      <c r="E490" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F490" s="20" t="n">
@@ -24231,7 +24231,7 @@
       <c r="D491" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E491" s="16" t="n">
+      <c r="E491" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F491" s="20" t="n">
@@ -24264,7 +24264,7 @@
       <c r="D492" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E492" s="16" t="n">
+      <c r="E492" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F492" s="20" t="n">
@@ -24297,7 +24297,7 @@
       <c r="D493" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E493" s="16" t="n">
+      <c r="E493" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F493" s="20" t="n">
@@ -24330,7 +24330,7 @@
       <c r="D494" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E494" s="16" t="n">
+      <c r="E494" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F494" s="20" t="n">
@@ -24363,7 +24363,7 @@
       <c r="D495" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E495" s="16" t="n">
+      <c r="E495" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F495" s="20" t="n">
@@ -24396,7 +24396,7 @@
       <c r="D496" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E496" s="16" t="n">
+      <c r="E496" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F496" s="20" t="n">
@@ -24429,7 +24429,7 @@
       <c r="D497" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E497" s="16" t="n">
+      <c r="E497" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F497" s="20" t="n">
@@ -24462,7 +24462,7 @@
       <c r="D498" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E498" s="16" t="n">
+      <c r="E498" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F498" s="20" t="n">
@@ -24495,7 +24495,7 @@
       <c r="D499" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E499" s="16" t="n">
+      <c r="E499" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F499" s="20" t="n">
@@ -24528,7 +24528,7 @@
       <c r="D500" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E500" s="16" t="n">
+      <c r="E500" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F500" s="20" t="n">
@@ -24561,7 +24561,7 @@
       <c r="D501" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E501" s="16" t="n">
+      <c r="E501" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F501" s="20" t="n">
@@ -24594,7 +24594,7 @@
       <c r="D502" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E502" s="16" t="n">
+      <c r="E502" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F502" s="20" t="n">
@@ -24627,7 +24627,7 @@
       <c r="D503" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E503" s="16" t="n">
+      <c r="E503" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F503" s="20" t="n">
@@ -24660,7 +24660,7 @@
       <c r="D504" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="E504" s="16" t="n">
+      <c r="E504" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F504" s="20" t="n">

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Barrido de 25 configuraciones PSO (partículas 2-10 × iteraciones 10-50, Cuadro 1 de Ortega &amp; Espinoza 2025) sobre (r, m), r en [1,25]. El peso converge al piso del rango publicado (m* = 0,30) en las 25 configuraciones, porque Fo decrece de forma estrictamente monótona en m. El radio NO lo fija el PSO: dentro de ese rango Fo prefiere r = 1 (1,7354 frente a 1,7039 en r = 25), de modo que r = 25 es una decisión de diseño tomada sobre las métricas de evaluación, de las cuales cinco lo favorecen (EN, SD, FE, MG, SF) y cuatro prefieren r = 1 (SSIM, PSNR, MI_vis, MI_ir).</t>
+          <t>Barrido de 25 configuraciones PSO (partículas 2-10 × iteraciones 10-50, Cuadro 1 de Ortega &amp; Espinoza 2025) sobre (r, m), r en [1,25]. El peso converge al piso del rango publicado (m* = 0,30) en las 25 configuraciones, porque Fo decrece de forma estrictamente monótona en m. El radio NO lo fija el PSO: dentro de ese rango Fo prefiere r = 1 (1,7350 frente a 1,7057 en r = 25), de modo que r = 25 es una decisión de diseño tomada sobre las métricas de evaluación, de las cuales cinco lo favorecen (EN, SD, FE, MG, SF) y cuatro prefieren r = 1 (SSIM, PSNR, MI_vis, MI_ir).</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Fo = 1.7354</t>
+          <t>Fo = 1.7350</t>
         </is>
       </c>
     </row>
@@ -1865,16 +1865,16 @@
         <v>20</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>1.6988</v>
+        <v>1.699</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1894,10 +1894,10 @@
         <v>0.3</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1917,10 +1917,10 @@
         <v>0.3</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>166</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1940,10 +1940,10 @@
         <v>0.3</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1963,10 +1963,10 @@
         <v>0.3</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1986,10 +1986,10 @@
         <v>0.3</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2009,10 +2009,10 @@
         <v>0.3</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>401</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -2032,10 +2032,10 @@
         <v>0.3</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -2055,7 +2055,7 @@
         <v>0.3</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>29</v>
@@ -2078,10 +2078,10 @@
         <v>0.3</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -2101,10 +2101,10 @@
         <v>0.3</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -2124,10 +2124,10 @@
         <v>0.3</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -2147,10 +2147,10 @@
         <v>0.3</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
@@ -2170,10 +2170,10 @@
         <v>0.3</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -2193,10 +2193,10 @@
         <v>0.3</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -2216,10 +2216,10 @@
         <v>0.3</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -2239,7 +2239,7 @@
         <v>0.3</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>30</v>
@@ -2262,33 +2262,33 @@
         <v>0.3</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="11" t="n">
         <v>320</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>1.7354</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>136</v>
+      <c r="D23" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1.7057</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>261</v>
       </c>
     </row>
     <row r="24">
@@ -2308,10 +2308,10 @@
         <v>0.3</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>194</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -2331,10 +2331,10 @@
         <v>0.3</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -2354,7 +2354,7 @@
         <v>0.3</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>40</v>
@@ -2377,10 +2377,10 @@
         <v>0.3</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -2400,10 +2400,10 @@
         <v>0.3</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>658</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -2423,10 +2423,10 @@
         <v>0.3</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>1.6988</v>
+        <v>1.699</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="34">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B34" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="35">
@@ -2519,19 +2519,19 @@
         </is>
       </c>
       <c r="B35" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="C35" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="36">
@@ -2541,19 +2541,19 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="C36" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>1.7039</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.7057</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>1.7057</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="37">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="C37" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>1.7354</v>
+        <v>1.735</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1.7039</v>
+        <v>1.7057</v>
       </c>
     </row>
     <row r="39">
@@ -7501,7 +7501,7 @@
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t>Triclobs_jeep_in_smoke_R</t>
+          <t>Triclobs_Kaptein_1123</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -7509,32 +7509,32 @@
           <t>Pirámide de Laplace (LP)</t>
         </is>
       </c>
-      <c r="C131" s="18" t="n">
-        <v>6.93067</v>
-      </c>
-      <c r="D131" s="18" t="n">
-        <v>0.14345</v>
-      </c>
-      <c r="E131" s="18" t="n">
-        <v>1.01463</v>
+      <c r="C131" s="19" t="n">
+        <v>7.18866</v>
+      </c>
+      <c r="D131" s="19" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="E131" s="19" t="n">
+        <v>1.02787</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.03888</v>
-      </c>
-      <c r="G131" s="18" t="n">
-        <v>0.8821</v>
+        <v>0.02132</v>
+      </c>
+      <c r="G131" s="19" t="n">
+        <v>1.18122</v>
       </c>
       <c r="H131" s="19" t="n">
-        <v>1.38236</v>
+        <v>1.98686</v>
       </c>
       <c r="I131" s="18" t="n">
-        <v>22.47202</v>
+        <v>9.284409999999999</v>
       </c>
       <c r="J131" s="18" t="n">
-        <v>0.6109</v>
+        <v>0.7003200000000001</v>
       </c>
       <c r="K131" s="18" t="n">
-        <v>14.06184</v>
+        <v>13.42766</v>
       </c>
     </row>
     <row r="132">
@@ -7545,31 +7545,31 @@
         </is>
       </c>
       <c r="C132" s="18" t="n">
-        <v>7.1874</v>
+        <v>6.714</v>
       </c>
       <c r="D132" s="18" t="n">
-        <v>0.14957</v>
+        <v>0.13217</v>
       </c>
       <c r="E132" s="18" t="n">
-        <v>1.05222</v>
+        <v>0.96</v>
       </c>
       <c r="F132" s="18" t="n">
-        <v>0.04906</v>
+        <v>0.02494</v>
       </c>
       <c r="G132" s="18" t="n">
-        <v>1.32143</v>
+        <v>0.63908</v>
       </c>
       <c r="H132" s="18" t="n">
-        <v>0.93947</v>
+        <v>0.45759</v>
       </c>
       <c r="I132" s="18" t="n">
-        <v>26.71208</v>
+        <v>11.33854</v>
       </c>
       <c r="J132" s="18" t="n">
-        <v>0.59653</v>
+        <v>0.67879</v>
       </c>
       <c r="K132" s="18" t="n">
-        <v>16.34186</v>
+        <v>15.94768</v>
       </c>
     </row>
     <row r="133">
@@ -7580,31 +7580,31 @@
         </is>
       </c>
       <c r="C133" s="18" t="n">
-        <v>7.10092</v>
+        <v>6.71605</v>
       </c>
       <c r="D133" s="18" t="n">
-        <v>0.13585</v>
+        <v>0.1307</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>1.03956</v>
+        <v>0.9603</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.04219</v>
+        <v>0.0234</v>
       </c>
       <c r="G133" s="18" t="n">
-        <v>1.34031</v>
+        <v>0.84667</v>
       </c>
       <c r="H133" s="18" t="n">
-        <v>1.00889</v>
+        <v>0.70966</v>
       </c>
       <c r="I133" s="18" t="n">
-        <v>23.63965</v>
+        <v>10.76803</v>
       </c>
       <c r="J133" s="18" t="n">
-        <v>0.62621</v>
+        <v>0.70151</v>
       </c>
       <c r="K133" s="18" t="n">
-        <v>16.62357</v>
+        <v>16.2381</v>
       </c>
     </row>
     <row r="134">
@@ -7615,31 +7615,31 @@
         </is>
       </c>
       <c r="C134" s="18" t="n">
-        <v>7.10352</v>
+        <v>6.724</v>
       </c>
       <c r="D134" s="18" t="n">
-        <v>0.13673</v>
+        <v>0.13193</v>
       </c>
       <c r="E134" s="18" t="n">
-        <v>1.03994</v>
+        <v>0.96143</v>
       </c>
       <c r="F134" s="18" t="n">
-        <v>0.04012</v>
-      </c>
-      <c r="G134" s="19" t="n">
-        <v>1.38081</v>
+        <v>0.02094</v>
+      </c>
+      <c r="G134" s="18" t="n">
+        <v>0.8519600000000001</v>
       </c>
       <c r="H134" s="18" t="n">
-        <v>0.99291</v>
+        <v>0.70386</v>
       </c>
       <c r="I134" s="18" t="n">
-        <v>22.59167</v>
+        <v>9.12002</v>
       </c>
       <c r="J134" s="19" t="n">
-        <v>0.6383799999999999</v>
+        <v>0.72489</v>
       </c>
       <c r="K134" s="18" t="n">
-        <v>16.6409</v>
+        <v>16.23278</v>
       </c>
     </row>
     <row r="135">
@@ -7650,31 +7650,31 @@
         </is>
       </c>
       <c r="C135" s="18" t="n">
-        <v>7.06123</v>
+        <v>6.68842</v>
       </c>
       <c r="D135" s="18" t="n">
-        <v>0.13242</v>
+        <v>0.12784</v>
       </c>
       <c r="E135" s="18" t="n">
-        <v>1.03375</v>
+        <v>0.95634</v>
       </c>
       <c r="F135" s="18" t="n">
-        <v>0.0416</v>
+        <v>0.02183</v>
       </c>
       <c r="G135" s="18" t="n">
-        <v>1.30723</v>
+        <v>0.85902</v>
       </c>
       <c r="H135" s="18" t="n">
-        <v>0.98019</v>
+        <v>0.7168600000000001</v>
       </c>
       <c r="I135" s="18" t="n">
-        <v>22.92362</v>
+        <v>9.413040000000001</v>
       </c>
       <c r="J135" s="18" t="n">
-        <v>0.63071</v>
+        <v>0.7144</v>
       </c>
       <c r="K135" s="19" t="n">
-        <v>16.69141</v>
+        <v>16.29629</v>
       </c>
     </row>
     <row r="136">
@@ -7685,31 +7685,31 @@
         </is>
       </c>
       <c r="C136" s="18" t="n">
-        <v>7.3674</v>
+        <v>6.92661</v>
       </c>
       <c r="D136" s="18" t="n">
-        <v>0.16592</v>
+        <v>0.13896</v>
       </c>
       <c r="E136" s="18" t="n">
-        <v>1.07857</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="F136" s="19" t="n">
-        <v>0.08152</v>
+        <v>0.03862</v>
       </c>
       <c r="G136" s="18" t="n">
-        <v>0.8535199999999999</v>
+        <v>0.69873</v>
       </c>
       <c r="H136" s="18" t="n">
-        <v>0.53748</v>
+        <v>0.53608</v>
       </c>
       <c r="I136" s="19" t="n">
-        <v>44.90313</v>
+        <v>15.95473</v>
       </c>
       <c r="J136" s="18" t="n">
-        <v>0.45636</v>
+        <v>0.57725</v>
       </c>
       <c r="K136" s="18" t="n">
-        <v>15.54351</v>
+        <v>15.98544</v>
       </c>
     </row>
     <row r="137">
@@ -7719,38 +7719,38 @@
           <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
         </is>
       </c>
-      <c r="C137" s="19" t="n">
-        <v>7.39259</v>
-      </c>
-      <c r="D137" s="19" t="n">
-        <v>0.17707</v>
-      </c>
-      <c r="E137" s="19" t="n">
-        <v>1.08226</v>
+      <c r="C137" s="18" t="n">
+        <v>6.98109</v>
+      </c>
+      <c r="D137" s="18" t="n">
+        <v>0.15508</v>
+      </c>
+      <c r="E137" s="18" t="n">
+        <v>0.99819</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.05851</v>
+        <v>0.02884</v>
       </c>
       <c r="G137" s="18" t="n">
-        <v>1.25104</v>
+        <v>0.7872400000000001</v>
       </c>
       <c r="H137" s="18" t="n">
-        <v>0.93977</v>
+        <v>0.67077</v>
       </c>
       <c r="I137" s="18" t="n">
-        <v>32.4941</v>
+        <v>12.38207</v>
       </c>
       <c r="J137" s="18" t="n">
-        <v>0.56818</v>
+        <v>0.67193</v>
       </c>
       <c r="K137" s="18" t="n">
-        <v>15.60396</v>
+        <v>15.78024</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t>Triclobs_Kaptein_1123</t>
+          <t>Triclobs_jeep_in_smoke_R</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -7758,32 +7758,32 @@
           <t>Pirámide de Laplace (LP)</t>
         </is>
       </c>
-      <c r="C138" s="19" t="n">
-        <v>7.18866</v>
-      </c>
-      <c r="D138" s="19" t="n">
-        <v>0.20126</v>
-      </c>
-      <c r="E138" s="19" t="n">
-        <v>1.02787</v>
+      <c r="C138" s="18" t="n">
+        <v>6.93067</v>
+      </c>
+      <c r="D138" s="18" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>1.01463</v>
       </c>
       <c r="F138" s="18" t="n">
-        <v>0.02132</v>
-      </c>
-      <c r="G138" s="19" t="n">
-        <v>1.18122</v>
+        <v>0.03888</v>
+      </c>
+      <c r="G138" s="18" t="n">
+        <v>0.8821</v>
       </c>
       <c r="H138" s="19" t="n">
-        <v>1.98686</v>
+        <v>1.38236</v>
       </c>
       <c r="I138" s="18" t="n">
-        <v>9.284409999999999</v>
+        <v>22.47202</v>
       </c>
       <c r="J138" s="18" t="n">
-        <v>0.7003200000000001</v>
+        <v>0.6109</v>
       </c>
       <c r="K138" s="18" t="n">
-        <v>13.42766</v>
+        <v>14.06184</v>
       </c>
     </row>
     <row r="139">
@@ -7794,31 +7794,31 @@
         </is>
       </c>
       <c r="C139" s="18" t="n">
-        <v>6.714</v>
+        <v>7.1874</v>
       </c>
       <c r="D139" s="18" t="n">
-        <v>0.13217</v>
+        <v>0.14957</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.96</v>
+        <v>1.05222</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.02494</v>
+        <v>0.04906</v>
       </c>
       <c r="G139" s="18" t="n">
-        <v>0.63908</v>
+        <v>1.32143</v>
       </c>
       <c r="H139" s="18" t="n">
-        <v>0.45759</v>
+        <v>0.93947</v>
       </c>
       <c r="I139" s="18" t="n">
-        <v>11.33854</v>
+        <v>26.71208</v>
       </c>
       <c r="J139" s="18" t="n">
-        <v>0.67879</v>
+        <v>0.59653</v>
       </c>
       <c r="K139" s="18" t="n">
-        <v>15.94768</v>
+        <v>16.34186</v>
       </c>
     </row>
     <row r="140">
@@ -7829,31 +7829,31 @@
         </is>
       </c>
       <c r="C140" s="18" t="n">
-        <v>6.71605</v>
+        <v>7.10092</v>
       </c>
       <c r="D140" s="18" t="n">
-        <v>0.1307</v>
+        <v>0.13585</v>
       </c>
       <c r="E140" s="18" t="n">
-        <v>0.9603</v>
+        <v>1.03956</v>
       </c>
       <c r="F140" s="18" t="n">
-        <v>0.0234</v>
+        <v>0.04219</v>
       </c>
       <c r="G140" s="18" t="n">
-        <v>0.84667</v>
+        <v>1.34031</v>
       </c>
       <c r="H140" s="18" t="n">
-        <v>0.70966</v>
+        <v>1.00889</v>
       </c>
       <c r="I140" s="18" t="n">
-        <v>10.76803</v>
+        <v>23.63965</v>
       </c>
       <c r="J140" s="18" t="n">
-        <v>0.70151</v>
+        <v>0.62621</v>
       </c>
       <c r="K140" s="18" t="n">
-        <v>16.2381</v>
+        <v>16.62357</v>
       </c>
     </row>
     <row r="141">
@@ -7864,31 +7864,31 @@
         </is>
       </c>
       <c r="C141" s="18" t="n">
-        <v>6.724</v>
+        <v>7.10352</v>
       </c>
       <c r="D141" s="18" t="n">
-        <v>0.13193</v>
+        <v>0.13673</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>0.96143</v>
+        <v>1.03994</v>
       </c>
       <c r="F141" s="18" t="n">
-        <v>0.02094</v>
-      </c>
-      <c r="G141" s="18" t="n">
-        <v>0.8519600000000001</v>
+        <v>0.04012</v>
+      </c>
+      <c r="G141" s="19" t="n">
+        <v>1.38081</v>
       </c>
       <c r="H141" s="18" t="n">
-        <v>0.70386</v>
+        <v>0.99291</v>
       </c>
       <c r="I141" s="18" t="n">
-        <v>9.12002</v>
+        <v>22.59167</v>
       </c>
       <c r="J141" s="19" t="n">
-        <v>0.72489</v>
+        <v>0.6383799999999999</v>
       </c>
       <c r="K141" s="18" t="n">
-        <v>16.23278</v>
+        <v>16.6409</v>
       </c>
     </row>
     <row r="142">
@@ -7899,31 +7899,31 @@
         </is>
       </c>
       <c r="C142" s="18" t="n">
-        <v>6.68842</v>
+        <v>7.06123</v>
       </c>
       <c r="D142" s="18" t="n">
-        <v>0.12784</v>
+        <v>0.13242</v>
       </c>
       <c r="E142" s="18" t="n">
-        <v>0.95634</v>
+        <v>1.03375</v>
       </c>
       <c r="F142" s="18" t="n">
-        <v>0.02183</v>
+        <v>0.0416</v>
       </c>
       <c r="G142" s="18" t="n">
-        <v>0.85902</v>
+        <v>1.30723</v>
       </c>
       <c r="H142" s="18" t="n">
-        <v>0.7168600000000001</v>
+        <v>0.98019</v>
       </c>
       <c r="I142" s="18" t="n">
-        <v>9.413040000000001</v>
+        <v>22.92362</v>
       </c>
       <c r="J142" s="18" t="n">
-        <v>0.7144</v>
+        <v>0.63071</v>
       </c>
       <c r="K142" s="19" t="n">
-        <v>16.29629</v>
+        <v>16.69141</v>
       </c>
     </row>
     <row r="143">
@@ -7934,31 +7934,31 @@
         </is>
       </c>
       <c r="C143" s="18" t="n">
-        <v>6.92661</v>
+        <v>7.3674</v>
       </c>
       <c r="D143" s="18" t="n">
-        <v>0.13896</v>
+        <v>0.16592</v>
       </c>
       <c r="E143" s="18" t="n">
-        <v>0.9903999999999999</v>
+        <v>1.07857</v>
       </c>
       <c r="F143" s="19" t="n">
-        <v>0.03862</v>
+        <v>0.08152</v>
       </c>
       <c r="G143" s="18" t="n">
-        <v>0.69873</v>
+        <v>0.8535199999999999</v>
       </c>
       <c r="H143" s="18" t="n">
-        <v>0.53608</v>
+        <v>0.53748</v>
       </c>
       <c r="I143" s="19" t="n">
-        <v>15.95473</v>
+        <v>44.90313</v>
       </c>
       <c r="J143" s="18" t="n">
-        <v>0.57725</v>
+        <v>0.45636</v>
       </c>
       <c r="K143" s="18" t="n">
-        <v>15.98544</v>
+        <v>15.54351</v>
       </c>
     </row>
     <row r="144">
@@ -7968,32 +7968,32 @@
           <t>PROPUESTA NOVEDOSA (r=25, m=0,30)</t>
         </is>
       </c>
-      <c r="C144" s="18" t="n">
-        <v>6.98109</v>
-      </c>
-      <c r="D144" s="18" t="n">
-        <v>0.15508</v>
-      </c>
-      <c r="E144" s="18" t="n">
-        <v>0.99819</v>
+      <c r="C144" s="19" t="n">
+        <v>7.39259</v>
+      </c>
+      <c r="D144" s="19" t="n">
+        <v>0.17707</v>
+      </c>
+      <c r="E144" s="19" t="n">
+        <v>1.08226</v>
       </c>
       <c r="F144" s="18" t="n">
-        <v>0.02884</v>
+        <v>0.05851</v>
       </c>
       <c r="G144" s="18" t="n">
-        <v>0.7872400000000001</v>
+        <v>1.25104</v>
       </c>
       <c r="H144" s="18" t="n">
-        <v>0.67077</v>
+        <v>0.93977</v>
       </c>
       <c r="I144" s="18" t="n">
-        <v>12.38207</v>
+        <v>32.4941</v>
       </c>
       <c r="J144" s="18" t="n">
-        <v>0.67193</v>
+        <v>0.56818</v>
       </c>
       <c r="K144" s="18" t="n">
-        <v>15.78024</v>
+        <v>15.60396</v>
       </c>
     </row>
     <row r="146">
@@ -25397,69 +25397,69 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Triclobs_jeep_in_smoke_R</t>
+          <t>Triclobs_Kaptein_1123</t>
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>7.3926</v>
+        <v>6.9811</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.1771</v>
+        <v>0.1551</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>1.0823</v>
+        <v>0.9982</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0585</v>
+        <v>0.0288</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1.251</v>
+        <v>0.7872</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>0.9398</v>
+        <v>0.6708</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>32.4941</v>
+        <v>12.3821</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0.5682</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J23" s="16" t="n">
-        <v>15.604</v>
+        <v>15.7802</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Triclobs_Kaptein_1123</t>
+          <t>Triclobs_jeep_in_smoke_R</t>
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>6.9811</v>
+        <v>7.3926</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.1551</v>
+        <v>0.1771</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.9982</v>
+        <v>1.0823</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0288</v>
+        <v>0.0585</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.7872</v>
+        <v>1.251</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>0.6708</v>
+        <v>0.9398</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>12.3821</v>
+        <v>32.4941</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.5682</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>15.7802</v>
+        <v>15.604</v>
       </c>
     </row>
     <row r="25">

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -1097,7 +1097,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -1311,7 +1311,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="B11" s="16" t="n">
@@ -2819,7 +2819,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="B9" s="16" t="n">
@@ -2955,7 +2955,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>En negrita el mejor valor de cada métrica dentro de cada escena. Todas las métricas son de tipo «mayor es mejor». Equivale a las Tablas 2a-2e del informe de avances, ampliado a las nueve métricas.</t>
+          <t>En negrita el mejor valor de cada métrica dentro de cada escena. Todas las métricas son de tipo «mayor es mejor». Equivale a las Tablas 4a-4e del informe de avances, ampliado a las nueve métricas.</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       <c r="A9" s="9" t="inlineStr"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C9" s="18" t="n">
@@ -3413,7 +3413,7 @@
       <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
@@ -3662,7 +3662,7 @@
       <c r="A23" s="9" t="inlineStr"/>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
@@ -3911,7 +3911,7 @@
       <c r="A30" s="9" t="inlineStr"/>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
@@ -4160,7 +4160,7 @@
       <c r="A37" s="9" t="inlineStr"/>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
@@ -4409,7 +4409,7 @@
       <c r="A44" s="9" t="inlineStr"/>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
@@ -4658,7 +4658,7 @@
       <c r="A51" s="9" t="inlineStr"/>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C51" s="18" t="n">
@@ -4907,7 +4907,7 @@
       <c r="A58" s="9" t="inlineStr"/>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C58" s="18" t="n">
@@ -5156,7 +5156,7 @@
       <c r="A65" s="9" t="inlineStr"/>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C65" s="18" t="n">
@@ -5405,7 +5405,7 @@
       <c r="A72" s="9" t="inlineStr"/>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C72" s="18" t="n">
@@ -5654,7 +5654,7 @@
       <c r="A79" s="9" t="inlineStr"/>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C79" s="18" t="n">
@@ -5903,7 +5903,7 @@
       <c r="A86" s="9" t="inlineStr"/>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C86" s="18" t="n">
@@ -6152,7 +6152,7 @@
       <c r="A93" s="9" t="inlineStr"/>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C93" s="18" t="n">
@@ -6401,7 +6401,7 @@
       <c r="A100" s="9" t="inlineStr"/>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C100" s="18" t="n">
@@ -6650,7 +6650,7 @@
       <c r="A107" s="9" t="inlineStr"/>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C107" s="18" t="n">
@@ -6899,7 +6899,7 @@
       <c r="A114" s="9" t="inlineStr"/>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C114" s="18" t="n">
@@ -7148,7 +7148,7 @@
       <c r="A121" s="9" t="inlineStr"/>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C121" s="18" t="n">
@@ -7397,7 +7397,7 @@
       <c r="A128" s="9" t="inlineStr"/>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C128" s="18" t="n">
@@ -7646,7 +7646,7 @@
       <c r="A135" s="9" t="inlineStr"/>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C135" s="18" t="n">
@@ -7895,7 +7895,7 @@
       <c r="A142" s="9" t="inlineStr"/>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>Curvelet (CVT)</t>
+          <t>Wavelet db4 (CVT)</t>
         </is>
       </c>
       <c r="C142" s="18" t="n">

--- a/docs/Avances_Tesis_Tablas.xlsx
+++ b/docs/Avances_Tesis_Tablas.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_Global" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_LLVIP" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deteccion_M3FD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PSO_Estabilidad" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Benchmark_por_Escena'!$A$4:$K$144</definedName>
@@ -30,13 +31,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0E+00"/>
+    <numFmt numFmtId="170" formatCode="0.0 %"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -110,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +183,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,7 +633,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>YOLOv8n reentrenado por método, evaluado con el checkpoint final (last.pt) para no heredar el sesgo de elegirlo sobre el mismo conjunto que se reporta. El IR solo lidera (mAP@0,5 = 0.9708); toda fusión supera al VIS solo (0.8133); la propuesta alcanza 0.9057: el realce que premian las métricas de actividad no mejora la detección (H3 no sostenida).</t>
+          <t>YOLOv8n reentrenado por método, evaluado con el checkpoint final (last.pt) para no heredar el sesgo de elegirlo sobre el mismo conjunto que se reporta. El IR solo lidera (mAP@0,5 = 0.9708); toda fusión supera al VIS solo (0.8133); la propuesta alcanza 0.9057: el realce que premian las métricas de actividad no mejora la detección. Es la hipótesis H6, que SE SOSTIENE: lo que queda rechazado es la traslación de la calidad a la tarea.</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1376,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Lectura: toda fusión supera al visible solo (+0,11 a +0,14 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,957) y ninguna fusión lo supera (peatón nocturno = térmico); entre las fusiones (banda 0,913–0,949) la propuesta queda en el extremo inferior (0,913). El realce que premian las métricas de actividad no mejora la detección: ambos criterios deben reportarse por separado (H3 no sostenida).</t>
+          <t>Lectura: toda fusión supera al visible solo, que alcanza 0,813 (+0,092 a +0,138 en mAP@0,5); el infrarrojo solo es la modalidad más fuerte (0,971) y ninguna fusión lo supera (el peatón nocturno es esencialmente térmico); entre las fusiones (banda 0,906-0,952) la propuesta queda en el extremo inferior (0,906). El realce que premian las métricas de actividad no mejora la detección: ambos criterios deben reportarse por separado. Es la hipótesis H6, que SE SOSTIENE —lo que queda rechazado es la traslación de la calidad a la tarea, no la hipótesis—.</t>
         </is>
       </c>
     </row>
@@ -1617,13 +1625,916 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Estabilidad del barrido PSO — 500 corridas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>20 repeticiones independientes de cada una de las 25 configuraciones. La repeticion 0 usa las semillas del barrido publicado y lo reproduce celda por celda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Corridas</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Fo media</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Fo mínima</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Fo máxima</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>% con r* = 1</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>% con m* = 0,30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>n = 2 · T = 10</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>1.70781585</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>1.670449</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>n = 2 · T = 20</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>1.7197372</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>1.699016</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>n = 2 · T = 30</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>1.7154144</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>1.698023</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>n = 2 · T = 40</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>1.71598965</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>1.704391</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>n = 2 · T = 50</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>1.71860645</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>1.70025</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>n = 4 · T = 10</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>1.71887875</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>n = 4 · T = 20</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>1.71887875</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>n = 4 · T = 30</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>1.7203435</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>n = 4 · T = 40</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>1.71301975</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>n = 4 · T = 50</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>1.72180825</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>n = 6 · T = 10</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>1.71887875</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>n = 6 · T = 20</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>1.717414</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>n = 6 · T = 30</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>1.7144845</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>n = 6 · T = 40</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>1.71887875</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>n = 6 · T = 50</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>1.723273</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>n = 8 · T = 10</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>1.7203435</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>n = 8 · T = 20</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>1.72473775</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>n = 8 · T = 30</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1.717414</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>n = 8 · T = 40</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>1.723273</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>n = 8 · T = 50</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>1.7203435</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>n = 10 · T = 10</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>1.723273</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>n = 10 · T = 20</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>1.723273</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>n = 10 · T = 30</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>1.717414</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>n = 10 · T = 40</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>1.71594925</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>n = 10 · T = 50</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>1.72180825</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1.734991</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Distribución del radio hallado sobre todas las corridas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>r óptimo</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Corridas</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>% del total</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Fo media</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>228</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>1.734991000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>1.707809</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>1.697021</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>1.670449</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>1.698023</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>1.698509</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>1.699016</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1.70025</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>1.702672</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1.703874</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>1.704391</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>257</v>
+      </c>
+      <c r="C44" s="29" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>1.705696</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Lectura sobre 500 corridas (20 repeticiones independientes de cada configuracion): el peso converge al piso del rango en 499 de 500 corridas (99,8 %), y la 1 restante tiene aptitud menor que el maximo (1,6704 contra 1,7350): son fallas de convergencia del enjambre —la peor es n = 2, T = 10, la configuracion con menos evaluaciones— y no optimos alternativos, de modo que el piso sigue siendo el maximo. El radio, en cambio, se reparte entre los dos bordes: r = 1 en el 45,6 % de las corridas y r = 25 en el 51,4 %, con un 3,0 % en radios intermedios. Agrandar el enjambre no estabiliza el resultado: el porcentaje que termina en r = 1 va del 37 % al 53 % segun el numero de particulas, sin tendencia. Y el radio mas frecuente (r = 25) no es el de mejor aptitud (r = 1), de modo que la frecuencia con que el enjambre devuelve un radio no mide su calidad. La optimizacion no identifica un radio estable, y el r = 25 adoptado proviene de la bateria de evaluacion (H5).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1740,43 +2651,55 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Óptimo global hallado</t>
+          <t>Argmax de la aptitud</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>r* = 25 · m* = 0,30 (el peso al que convergen las 25 configuraciones con el rango publicado)</t>
+          <t>r = 1 · m = 0,30 (el maximo de Fo dentro del rango publicado)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Aptitud alcanzada</t>
+          <t>Configuración adoptada</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Fo = 1.7350</t>
+          <t>r = 25 · m = 0,30 — el radio lo elige el bloque de actividad de la batería de evaluación, NO la optimización (H5)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Aptitud alcanzada</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Fo = 1.7350</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>Estado guardado en</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>metrics_reports/pso_grid_search_fo_propuesta.csv</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Con la suma de ramas se inyecta más energía de detalle que con el máximo; el enjambre lo compensa con el peso del rango publicado (m = 0,30). El radio se ubica en el tope del rango del libro (r = 25): el operador aprovecha un vecindario amplio para capturar los objetivos térmicos completos.</t>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Con la suma de ramas se inyecta más energía de detalle que con el máximo; el enjambre lo compensa con el peso del piso del rango publicado (m = 0,30). Conviene no confundir dos cosas: el argmax de la aptitud dentro del rango es r = 1, y el radio adoptado (r = 25) lo elige el bloque de actividad de la batería de evaluación —a igual peso supera a r = 1 en entropía, contraste, eficiencia de fusión, gradiente medio y frecuencia espacial— y no la optimización. Esa distinción es la hipótesis H5 del trabajo.</t>
         </is>
       </c>
     </row>
@@ -2581,7 +3504,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Lectura: n = 2 cae en el óptimo local r = 1 en 2 de 5 corridas; con n = 10 y T &gt;= 30 el óptimo global (r = 25, m ≈ 0,07) se alcanza de forma consistente.</t>
+          <t>Lectura sobre 500 corridas (20 repeticiones independientes de cada configuracion): el peso converge al piso del rango en 499 de 500 corridas (99,8 %), y la 1 restante tiene aptitud menor que el maximo (1,6704 contra 1,7350): son fallas de convergencia del enjambre —la peor es n = 2, T = 10, la configuracion con menos evaluaciones— y no optimos alternativos, de modo que el piso sigue siendo el maximo. El radio, en cambio, se reparte entre los dos bordes: r = 1 en el 45,6 % de las corridas y r = 25 en el 51,4 %, con un 3,0 % en radios intermedios. Agrandar el enjambre no estabiliza el resultado: el porcentaje que termina en r = 1 va del 37 % al 53 % segun el numero de particulas, sin tendencia. Y el radio mas frecuente (r = 25) no es el de mejor aptitud (r = 1), de modo que la frecuencia con que el enjambre devuelve un radio no mide su calidad. La optimizacion no identifica un radio estable, y el r = 25 adoptado proviene de la bateria de evaluacion (H5).</t>
         </is>
       </c>
     </row>
